--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_설계팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_설계팀_입력_2026.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,8 +59,14 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="002E7D32"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -112,8 +118,13 @@
         <fgColor rgb="008B1E22"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B08F36"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -179,11 +190,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -351,6 +376,24 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -581,11 +624,32 @@
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
+        <t>▣ 제안서
+완료일
+(직접 입력)</t>
+      </text>
+    </comment>
+    <comment ref="Q4" authorId="0" shapeId="0">
+      <text>
+        <t>▣ 설계
+완료일
+(직접 입력)</t>
+      </text>
+    </comment>
+    <comment ref="R4" authorId="0" shapeId="0">
+      <text>
+        <t>▣ 가공의뢰
+입고일
+(직접 입력)</t>
+      </text>
+    </comment>
+    <comment ref="S4" authorId="0" shapeId="0">
+      <text>
         <t>▣ 상태
 (직접 입력)</t>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0" shapeId="0">
+    <comment ref="T4" authorId="0" shapeId="0">
       <text>
         <t>▣ 메모
 (직접 입력)</t>
@@ -885,7 +949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q140"/>
+  <dimension ref="A1:T140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -903,12 +967,15 @@
     <col width="11" customWidth="1" style="43" min="13" max="13"/>
     <col width="9" customWidth="1" style="43" min="14" max="14"/>
     <col width="10" customWidth="1" style="43" min="15" max="15"/>
-    <col width="10" customWidth="1" style="43" min="16" max="16"/>
-    <col width="28" customWidth="1" style="43" min="17" max="17"/>
+    <col width="12" customWidth="1" style="43" min="16" max="16"/>
+    <col width="12" customWidth="1" style="43" min="17" max="17"/>
+    <col width="12" customWidth="1" style="43" min="18" max="18"/>
+    <col width="10" customWidth="1" style="43" min="19" max="19"/>
+    <col width="28" customWidth="1" style="43" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="58" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 설계팀 │ 2026</t>
         </is>
@@ -928,10 +995,13 @@
       <c r="N1" s="16" t="n"/>
       <c r="O1" s="16" t="n"/>
       <c r="P1" s="16" t="n"/>
-      <c r="Q1" s="17" t="n"/>
+      <c r="Q1" s="16" t="n"/>
+      <c r="R1" s="16" t="n"/>
+      <c r="S1" s="16" t="n"/>
+      <c r="T1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="54" t="inlineStr">
+      <c r="A2" s="59" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 설계팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -950,10 +1020,13 @@
       <c r="M2" s="16" t="n"/>
       <c r="N2" s="16" t="n"/>
       <c r="O2" s="16" t="n"/>
-      <c r="P2" s="17" t="n"/>
-      <c r="Q2" s="55" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-02 01:43</t>
+      <c r="P2" s="16" t="n"/>
+      <c r="Q2" s="16" t="n"/>
+      <c r="R2" s="16" t="n"/>
+      <c r="S2" s="17" t="n"/>
+      <c r="T2" s="60" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 00:44</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1106,27 @@
           <t>✏입력</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>✏선택▼</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>✏메모</t>
         </is>
@@ -1120,12 +1208,30 @@
           <t>가공발주</t>
         </is>
       </c>
-      <c r="P4" s="7" t="inlineStr">
+      <c r="P4" s="61" t="inlineStr">
+        <is>
+          <t>제안서
+완료일</t>
+        </is>
+      </c>
+      <c r="Q4" s="61" t="inlineStr">
+        <is>
+          <t>설계
+완료일</t>
+        </is>
+      </c>
+      <c r="R4" s="61" t="inlineStr">
+        <is>
+          <t>가공의뢰
+입고일</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="Q4" s="7" t="inlineStr">
+      <c r="T4" s="7" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -1182,7 +1288,10 @@
       <c r="N5" s="11" t="n"/>
       <c r="O5" s="11" t="n"/>
       <c r="P5" s="9" t="n"/>
-      <c r="Q5" s="22" t="n"/>
+      <c r="Q5" s="9" t="n"/>
+      <c r="R5" s="9" t="n"/>
+      <c r="S5" s="9" t="n"/>
+      <c r="T5" s="22" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="12" t="n">
@@ -1235,7 +1344,10 @@
       <c r="N6" s="15" t="n"/>
       <c r="O6" s="15" t="n"/>
       <c r="P6" s="13" t="n"/>
-      <c r="Q6" s="24" t="n"/>
+      <c r="Q6" s="13" t="n"/>
+      <c r="R6" s="13" t="n"/>
+      <c r="S6" s="13" t="n"/>
+      <c r="T6" s="24" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="n">
@@ -1288,7 +1400,10 @@
       <c r="N7" s="11" t="n"/>
       <c r="O7" s="11" t="n"/>
       <c r="P7" s="9" t="n"/>
-      <c r="Q7" s="22" t="n"/>
+      <c r="Q7" s="9" t="n"/>
+      <c r="R7" s="9" t="n"/>
+      <c r="S7" s="9" t="n"/>
+      <c r="T7" s="22" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="12" t="n">
@@ -1341,7 +1456,10 @@
       <c r="N8" s="15" t="n"/>
       <c r="O8" s="15" t="n"/>
       <c r="P8" s="13" t="n"/>
-      <c r="Q8" s="24" t="n"/>
+      <c r="Q8" s="13" t="n"/>
+      <c r="R8" s="13" t="n"/>
+      <c r="S8" s="13" t="n"/>
+      <c r="T8" s="24" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="8" t="n">
@@ -1394,7 +1512,10 @@
       <c r="N9" s="11" t="n"/>
       <c r="O9" s="11" t="n"/>
       <c r="P9" s="9" t="n"/>
-      <c r="Q9" s="22" t="n"/>
+      <c r="Q9" s="9" t="n"/>
+      <c r="R9" s="9" t="n"/>
+      <c r="S9" s="9" t="n"/>
+      <c r="T9" s="22" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="12" t="n">
@@ -1447,7 +1568,10 @@
       <c r="N10" s="15" t="n"/>
       <c r="O10" s="15" t="n"/>
       <c r="P10" s="13" t="n"/>
-      <c r="Q10" s="24" t="n"/>
+      <c r="Q10" s="13" t="n"/>
+      <c r="R10" s="13" t="n"/>
+      <c r="S10" s="13" t="n"/>
+      <c r="T10" s="24" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="8" t="n">
@@ -1500,7 +1624,10 @@
       <c r="N11" s="11" t="n"/>
       <c r="O11" s="11" t="n"/>
       <c r="P11" s="9" t="n"/>
-      <c r="Q11" s="22" t="n"/>
+      <c r="Q11" s="9" t="n"/>
+      <c r="R11" s="9" t="n"/>
+      <c r="S11" s="9" t="n"/>
+      <c r="T11" s="22" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="12" t="n">
@@ -1553,7 +1680,10 @@
       <c r="N12" s="15" t="n"/>
       <c r="O12" s="15" t="n"/>
       <c r="P12" s="13" t="n"/>
-      <c r="Q12" s="24" t="n"/>
+      <c r="Q12" s="13" t="n"/>
+      <c r="R12" s="13" t="n"/>
+      <c r="S12" s="13" t="n"/>
+      <c r="T12" s="24" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="8" t="n">
@@ -1606,7 +1736,10 @@
       <c r="N13" s="11" t="n"/>
       <c r="O13" s="11" t="n"/>
       <c r="P13" s="9" t="n"/>
-      <c r="Q13" s="22" t="n"/>
+      <c r="Q13" s="9" t="n"/>
+      <c r="R13" s="9" t="n"/>
+      <c r="S13" s="9" t="n"/>
+      <c r="T13" s="22" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="12" t="n">
@@ -1659,7 +1792,10 @@
       <c r="N14" s="15" t="n"/>
       <c r="O14" s="15" t="n"/>
       <c r="P14" s="13" t="n"/>
-      <c r="Q14" s="24" t="n"/>
+      <c r="Q14" s="13" t="n"/>
+      <c r="R14" s="13" t="n"/>
+      <c r="S14" s="13" t="n"/>
+      <c r="T14" s="24" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="8" t="n">
@@ -1712,7 +1848,10 @@
       <c r="N15" s="11" t="n"/>
       <c r="O15" s="11" t="n"/>
       <c r="P15" s="9" t="n"/>
-      <c r="Q15" s="22" t="n"/>
+      <c r="Q15" s="9" t="n"/>
+      <c r="R15" s="9" t="n"/>
+      <c r="S15" s="9" t="n"/>
+      <c r="T15" s="22" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="12" t="n">
@@ -1765,7 +1904,10 @@
       <c r="N16" s="15" t="n"/>
       <c r="O16" s="15" t="n"/>
       <c r="P16" s="13" t="n"/>
-      <c r="Q16" s="24" t="n"/>
+      <c r="Q16" s="13" t="n"/>
+      <c r="R16" s="13" t="n"/>
+      <c r="S16" s="13" t="n"/>
+      <c r="T16" s="24" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="8" t="n">
@@ -1818,7 +1960,10 @@
       <c r="N17" s="11" t="n"/>
       <c r="O17" s="11" t="n"/>
       <c r="P17" s="9" t="n"/>
-      <c r="Q17" s="22" t="n"/>
+      <c r="Q17" s="9" t="n"/>
+      <c r="R17" s="9" t="n"/>
+      <c r="S17" s="9" t="n"/>
+      <c r="T17" s="22" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="12" t="n">
@@ -1871,7 +2016,10 @@
       <c r="N18" s="15" t="n"/>
       <c r="O18" s="15" t="n"/>
       <c r="P18" s="13" t="n"/>
-      <c r="Q18" s="24" t="n"/>
+      <c r="Q18" s="13" t="n"/>
+      <c r="R18" s="13" t="n"/>
+      <c r="S18" s="13" t="n"/>
+      <c r="T18" s="24" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="8" t="n">
@@ -1924,7 +2072,10 @@
       <c r="N19" s="11" t="n"/>
       <c r="O19" s="11" t="n"/>
       <c r="P19" s="9" t="n"/>
-      <c r="Q19" s="22" t="n"/>
+      <c r="Q19" s="9" t="n"/>
+      <c r="R19" s="9" t="n"/>
+      <c r="S19" s="9" t="n"/>
+      <c r="T19" s="22" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="12" t="n">
@@ -1977,7 +2128,10 @@
       <c r="N20" s="15" t="n"/>
       <c r="O20" s="15" t="n"/>
       <c r="P20" s="13" t="n"/>
-      <c r="Q20" s="24" t="n"/>
+      <c r="Q20" s="13" t="n"/>
+      <c r="R20" s="13" t="n"/>
+      <c r="S20" s="13" t="n"/>
+      <c r="T20" s="24" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="8" t="n">
@@ -2030,7 +2184,10 @@
       <c r="N21" s="11" t="n"/>
       <c r="O21" s="11" t="n"/>
       <c r="P21" s="9" t="n"/>
-      <c r="Q21" s="22" t="n"/>
+      <c r="Q21" s="9" t="n"/>
+      <c r="R21" s="9" t="n"/>
+      <c r="S21" s="9" t="n"/>
+      <c r="T21" s="22" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="12" t="n">
@@ -2083,7 +2240,10 @@
       <c r="N22" s="15" t="n"/>
       <c r="O22" s="15" t="n"/>
       <c r="P22" s="13" t="n"/>
-      <c r="Q22" s="24" t="n"/>
+      <c r="Q22" s="13" t="n"/>
+      <c r="R22" s="13" t="n"/>
+      <c r="S22" s="13" t="n"/>
+      <c r="T22" s="24" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="8" t="n">
@@ -2136,7 +2296,10 @@
       <c r="N23" s="11" t="n"/>
       <c r="O23" s="11" t="n"/>
       <c r="P23" s="9" t="n"/>
-      <c r="Q23" s="22" t="n"/>
+      <c r="Q23" s="9" t="n"/>
+      <c r="R23" s="9" t="n"/>
+      <c r="S23" s="9" t="n"/>
+      <c r="T23" s="22" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="12" t="n">
@@ -2189,7 +2352,10 @@
       <c r="N24" s="15" t="n"/>
       <c r="O24" s="15" t="n"/>
       <c r="P24" s="13" t="n"/>
-      <c r="Q24" s="24" t="n"/>
+      <c r="Q24" s="13" t="n"/>
+      <c r="R24" s="13" t="n"/>
+      <c r="S24" s="13" t="n"/>
+      <c r="T24" s="24" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="8" t="n">
@@ -2242,7 +2408,10 @@
       <c r="N25" s="11" t="n"/>
       <c r="O25" s="11" t="n"/>
       <c r="P25" s="9" t="n"/>
-      <c r="Q25" s="22" t="n"/>
+      <c r="Q25" s="9" t="n"/>
+      <c r="R25" s="9" t="n"/>
+      <c r="S25" s="9" t="n"/>
+      <c r="T25" s="22" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="12" t="n">
@@ -2295,7 +2464,10 @@
       <c r="N26" s="15" t="n"/>
       <c r="O26" s="15" t="n"/>
       <c r="P26" s="13" t="n"/>
-      <c r="Q26" s="24" t="n"/>
+      <c r="Q26" s="13" t="n"/>
+      <c r="R26" s="13" t="n"/>
+      <c r="S26" s="13" t="n"/>
+      <c r="T26" s="24" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="8" t="n">
@@ -2348,7 +2520,10 @@
       <c r="N27" s="11" t="n"/>
       <c r="O27" s="11" t="n"/>
       <c r="P27" s="9" t="n"/>
-      <c r="Q27" s="22" t="n"/>
+      <c r="Q27" s="9" t="n"/>
+      <c r="R27" s="9" t="n"/>
+      <c r="S27" s="9" t="n"/>
+      <c r="T27" s="22" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="12" t="n">
@@ -2401,7 +2576,10 @@
       <c r="N28" s="15" t="n"/>
       <c r="O28" s="15" t="n"/>
       <c r="P28" s="13" t="n"/>
-      <c r="Q28" s="24" t="n"/>
+      <c r="Q28" s="13" t="n"/>
+      <c r="R28" s="13" t="n"/>
+      <c r="S28" s="13" t="n"/>
+      <c r="T28" s="24" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="8" t="n">
@@ -2454,7 +2632,10 @@
       <c r="N29" s="11" t="n"/>
       <c r="O29" s="11" t="n"/>
       <c r="P29" s="9" t="n"/>
-      <c r="Q29" s="22" t="n"/>
+      <c r="Q29" s="9" t="n"/>
+      <c r="R29" s="9" t="n"/>
+      <c r="S29" s="9" t="n"/>
+      <c r="T29" s="22" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="12" t="n">
@@ -2507,7 +2688,10 @@
       <c r="N30" s="15" t="n"/>
       <c r="O30" s="15" t="n"/>
       <c r="P30" s="13" t="n"/>
-      <c r="Q30" s="24" t="n"/>
+      <c r="Q30" s="13" t="n"/>
+      <c r="R30" s="13" t="n"/>
+      <c r="S30" s="13" t="n"/>
+      <c r="T30" s="24" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="8" t="n">
@@ -2560,7 +2744,10 @@
       <c r="N31" s="11" t="n"/>
       <c r="O31" s="11" t="n"/>
       <c r="P31" s="9" t="n"/>
-      <c r="Q31" s="22" t="n"/>
+      <c r="Q31" s="9" t="n"/>
+      <c r="R31" s="9" t="n"/>
+      <c r="S31" s="9" t="n"/>
+      <c r="T31" s="22" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="12" t="n">
@@ -2613,7 +2800,10 @@
       <c r="N32" s="15" t="n"/>
       <c r="O32" s="15" t="n"/>
       <c r="P32" s="13" t="n"/>
-      <c r="Q32" s="24" t="n"/>
+      <c r="Q32" s="13" t="n"/>
+      <c r="R32" s="13" t="n"/>
+      <c r="S32" s="13" t="n"/>
+      <c r="T32" s="24" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="8" t="n">
@@ -2666,7 +2856,10 @@
       <c r="N33" s="11" t="n"/>
       <c r="O33" s="11" t="n"/>
       <c r="P33" s="9" t="n"/>
-      <c r="Q33" s="22" t="n"/>
+      <c r="Q33" s="9" t="n"/>
+      <c r="R33" s="9" t="n"/>
+      <c r="S33" s="9" t="n"/>
+      <c r="T33" s="22" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="12" t="n">
@@ -2719,7 +2912,10 @@
       <c r="N34" s="15" t="n"/>
       <c r="O34" s="15" t="n"/>
       <c r="P34" s="13" t="n"/>
-      <c r="Q34" s="24" t="n"/>
+      <c r="Q34" s="13" t="n"/>
+      <c r="R34" s="13" t="n"/>
+      <c r="S34" s="13" t="n"/>
+      <c r="T34" s="24" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="8" t="n">
@@ -2772,7 +2968,10 @@
       <c r="N35" s="11" t="n"/>
       <c r="O35" s="11" t="n"/>
       <c r="P35" s="9" t="n"/>
-      <c r="Q35" s="22" t="n"/>
+      <c r="Q35" s="9" t="n"/>
+      <c r="R35" s="9" t="n"/>
+      <c r="S35" s="9" t="n"/>
+      <c r="T35" s="22" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="12" t="n">
@@ -2825,7 +3024,10 @@
       <c r="N36" s="15" t="n"/>
       <c r="O36" s="15" t="n"/>
       <c r="P36" s="13" t="n"/>
-      <c r="Q36" s="24" t="n"/>
+      <c r="Q36" s="13" t="n"/>
+      <c r="R36" s="13" t="n"/>
+      <c r="S36" s="13" t="n"/>
+      <c r="T36" s="24" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="8" t="n">
@@ -2878,7 +3080,10 @@
       <c r="N37" s="11" t="n"/>
       <c r="O37" s="11" t="n"/>
       <c r="P37" s="9" t="n"/>
-      <c r="Q37" s="22" t="n"/>
+      <c r="Q37" s="9" t="n"/>
+      <c r="R37" s="9" t="n"/>
+      <c r="S37" s="9" t="n"/>
+      <c r="T37" s="22" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="12" t="n">
@@ -2931,7 +3136,10 @@
       <c r="N38" s="15" t="n"/>
       <c r="O38" s="15" t="n"/>
       <c r="P38" s="13" t="n"/>
-      <c r="Q38" s="24" t="n"/>
+      <c r="Q38" s="13" t="n"/>
+      <c r="R38" s="13" t="n"/>
+      <c r="S38" s="13" t="n"/>
+      <c r="T38" s="24" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="8" t="n">
@@ -2984,7 +3192,10 @@
       <c r="N39" s="11" t="n"/>
       <c r="O39" s="11" t="n"/>
       <c r="P39" s="9" t="n"/>
-      <c r="Q39" s="22" t="n"/>
+      <c r="Q39" s="9" t="n"/>
+      <c r="R39" s="9" t="n"/>
+      <c r="S39" s="9" t="n"/>
+      <c r="T39" s="22" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="12" t="n">
@@ -3037,7 +3248,10 @@
       <c r="N40" s="15" t="n"/>
       <c r="O40" s="15" t="n"/>
       <c r="P40" s="13" t="n"/>
-      <c r="Q40" s="24" t="n"/>
+      <c r="Q40" s="13" t="n"/>
+      <c r="R40" s="13" t="n"/>
+      <c r="S40" s="13" t="n"/>
+      <c r="T40" s="24" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="8" t="n">
@@ -3090,7 +3304,10 @@
       <c r="N41" s="11" t="n"/>
       <c r="O41" s="11" t="n"/>
       <c r="P41" s="9" t="n"/>
-      <c r="Q41" s="22" t="n"/>
+      <c r="Q41" s="9" t="n"/>
+      <c r="R41" s="9" t="n"/>
+      <c r="S41" s="9" t="n"/>
+      <c r="T41" s="22" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="12" t="n">
@@ -3143,7 +3360,10 @@
       <c r="N42" s="15" t="n"/>
       <c r="O42" s="15" t="n"/>
       <c r="P42" s="13" t="n"/>
-      <c r="Q42" s="24" t="n"/>
+      <c r="Q42" s="13" t="n"/>
+      <c r="R42" s="13" t="n"/>
+      <c r="S42" s="13" t="n"/>
+      <c r="T42" s="24" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="8" t="n">
@@ -3196,7 +3416,10 @@
       <c r="N43" s="11" t="n"/>
       <c r="O43" s="11" t="n"/>
       <c r="P43" s="9" t="n"/>
-      <c r="Q43" s="22" t="n"/>
+      <c r="Q43" s="9" t="n"/>
+      <c r="R43" s="9" t="n"/>
+      <c r="S43" s="9" t="n"/>
+      <c r="T43" s="22" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="12" t="n">
@@ -3249,7 +3472,10 @@
       <c r="N44" s="15" t="n"/>
       <c r="O44" s="15" t="n"/>
       <c r="P44" s="13" t="n"/>
-      <c r="Q44" s="24" t="n"/>
+      <c r="Q44" s="13" t="n"/>
+      <c r="R44" s="13" t="n"/>
+      <c r="S44" s="13" t="n"/>
+      <c r="T44" s="24" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="8" t="n">
@@ -3302,7 +3528,10 @@
       <c r="N45" s="11" t="n"/>
       <c r="O45" s="11" t="n"/>
       <c r="P45" s="9" t="n"/>
-      <c r="Q45" s="22" t="n"/>
+      <c r="Q45" s="9" t="n"/>
+      <c r="R45" s="9" t="n"/>
+      <c r="S45" s="9" t="n"/>
+      <c r="T45" s="22" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="12" t="n">
@@ -3355,7 +3584,10 @@
       <c r="N46" s="15" t="n"/>
       <c r="O46" s="15" t="n"/>
       <c r="P46" s="13" t="n"/>
-      <c r="Q46" s="24" t="n"/>
+      <c r="Q46" s="13" t="n"/>
+      <c r="R46" s="13" t="n"/>
+      <c r="S46" s="13" t="n"/>
+      <c r="T46" s="24" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="8" t="n">
@@ -3408,7 +3640,10 @@
       <c r="N47" s="11" t="n"/>
       <c r="O47" s="11" t="n"/>
       <c r="P47" s="9" t="n"/>
-      <c r="Q47" s="22" t="n"/>
+      <c r="Q47" s="9" t="n"/>
+      <c r="R47" s="9" t="n"/>
+      <c r="S47" s="9" t="n"/>
+      <c r="T47" s="22" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="12" t="n">
@@ -3461,7 +3696,10 @@
       <c r="N48" s="15" t="n"/>
       <c r="O48" s="15" t="n"/>
       <c r="P48" s="13" t="n"/>
-      <c r="Q48" s="24" t="n"/>
+      <c r="Q48" s="13" t="n"/>
+      <c r="R48" s="13" t="n"/>
+      <c r="S48" s="13" t="n"/>
+      <c r="T48" s="24" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="8" t="n">
@@ -3514,7 +3752,10 @@
       <c r="N49" s="11" t="n"/>
       <c r="O49" s="11" t="n"/>
       <c r="P49" s="9" t="n"/>
-      <c r="Q49" s="22" t="n"/>
+      <c r="Q49" s="9" t="n"/>
+      <c r="R49" s="9" t="n"/>
+      <c r="S49" s="9" t="n"/>
+      <c r="T49" s="22" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="12" t="n">
@@ -3567,7 +3808,10 @@
       <c r="N50" s="15" t="n"/>
       <c r="O50" s="15" t="n"/>
       <c r="P50" s="13" t="n"/>
-      <c r="Q50" s="24" t="n"/>
+      <c r="Q50" s="13" t="n"/>
+      <c r="R50" s="13" t="n"/>
+      <c r="S50" s="13" t="n"/>
+      <c r="T50" s="24" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="8" t="n">
@@ -3620,7 +3864,10 @@
       <c r="N51" s="11" t="n"/>
       <c r="O51" s="11" t="n"/>
       <c r="P51" s="9" t="n"/>
-      <c r="Q51" s="22" t="n"/>
+      <c r="Q51" s="9" t="n"/>
+      <c r="R51" s="9" t="n"/>
+      <c r="S51" s="9" t="n"/>
+      <c r="T51" s="22" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="12" t="n">
@@ -3673,7 +3920,10 @@
       <c r="N52" s="15" t="n"/>
       <c r="O52" s="15" t="n"/>
       <c r="P52" s="13" t="n"/>
-      <c r="Q52" s="24" t="n"/>
+      <c r="Q52" s="13" t="n"/>
+      <c r="R52" s="13" t="n"/>
+      <c r="S52" s="13" t="n"/>
+      <c r="T52" s="24" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="8" t="n">
@@ -3726,7 +3976,10 @@
       <c r="N53" s="11" t="n"/>
       <c r="O53" s="11" t="n"/>
       <c r="P53" s="9" t="n"/>
-      <c r="Q53" s="22" t="n"/>
+      <c r="Q53" s="9" t="n"/>
+      <c r="R53" s="9" t="n"/>
+      <c r="S53" s="9" t="n"/>
+      <c r="T53" s="22" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="12" t="n">
@@ -3779,7 +4032,10 @@
       <c r="N54" s="15" t="n"/>
       <c r="O54" s="15" t="n"/>
       <c r="P54" s="13" t="n"/>
-      <c r="Q54" s="24" t="n"/>
+      <c r="Q54" s="13" t="n"/>
+      <c r="R54" s="13" t="n"/>
+      <c r="S54" s="13" t="n"/>
+      <c r="T54" s="24" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="8" t="n">
@@ -3832,7 +4088,10 @@
       <c r="N55" s="11" t="n"/>
       <c r="O55" s="11" t="n"/>
       <c r="P55" s="9" t="n"/>
-      <c r="Q55" s="22" t="n"/>
+      <c r="Q55" s="9" t="n"/>
+      <c r="R55" s="9" t="n"/>
+      <c r="S55" s="9" t="n"/>
+      <c r="T55" s="22" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="12" t="n">
@@ -3885,7 +4144,10 @@
       <c r="N56" s="15" t="n"/>
       <c r="O56" s="15" t="n"/>
       <c r="P56" s="13" t="n"/>
-      <c r="Q56" s="24" t="n"/>
+      <c r="Q56" s="13" t="n"/>
+      <c r="R56" s="13" t="n"/>
+      <c r="S56" s="13" t="n"/>
+      <c r="T56" s="24" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="8" t="n">
@@ -3938,7 +4200,10 @@
       <c r="N57" s="11" t="n"/>
       <c r="O57" s="11" t="n"/>
       <c r="P57" s="9" t="n"/>
-      <c r="Q57" s="22" t="n"/>
+      <c r="Q57" s="9" t="n"/>
+      <c r="R57" s="9" t="n"/>
+      <c r="S57" s="9" t="n"/>
+      <c r="T57" s="22" t="n"/>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="12" t="n">
@@ -3991,7 +4256,10 @@
       <c r="N58" s="15" t="n"/>
       <c r="O58" s="15" t="n"/>
       <c r="P58" s="13" t="n"/>
-      <c r="Q58" s="24" t="n"/>
+      <c r="Q58" s="13" t="n"/>
+      <c r="R58" s="13" t="n"/>
+      <c r="S58" s="13" t="n"/>
+      <c r="T58" s="24" t="n"/>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="8" t="n">
@@ -4044,7 +4312,10 @@
       <c r="N59" s="11" t="n"/>
       <c r="O59" s="11" t="n"/>
       <c r="P59" s="9" t="n"/>
-      <c r="Q59" s="22" t="n"/>
+      <c r="Q59" s="9" t="n"/>
+      <c r="R59" s="9" t="n"/>
+      <c r="S59" s="9" t="n"/>
+      <c r="T59" s="22" t="n"/>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="12" t="n">
@@ -4097,7 +4368,10 @@
       <c r="N60" s="15" t="n"/>
       <c r="O60" s="15" t="n"/>
       <c r="P60" s="13" t="n"/>
-      <c r="Q60" s="24" t="n"/>
+      <c r="Q60" s="13" t="n"/>
+      <c r="R60" s="13" t="n"/>
+      <c r="S60" s="13" t="n"/>
+      <c r="T60" s="24" t="n"/>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="8" t="n">
@@ -4150,7 +4424,10 @@
       <c r="N61" s="11" t="n"/>
       <c r="O61" s="11" t="n"/>
       <c r="P61" s="9" t="n"/>
-      <c r="Q61" s="22" t="n"/>
+      <c r="Q61" s="9" t="n"/>
+      <c r="R61" s="9" t="n"/>
+      <c r="S61" s="9" t="n"/>
+      <c r="T61" s="22" t="n"/>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="12" t="n">
@@ -4203,7 +4480,10 @@
       <c r="N62" s="15" t="n"/>
       <c r="O62" s="15" t="n"/>
       <c r="P62" s="13" t="n"/>
-      <c r="Q62" s="24" t="n"/>
+      <c r="Q62" s="13" t="n"/>
+      <c r="R62" s="13" t="n"/>
+      <c r="S62" s="13" t="n"/>
+      <c r="T62" s="24" t="n"/>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="8" t="n">
@@ -4256,7 +4536,10 @@
       <c r="N63" s="11" t="n"/>
       <c r="O63" s="11" t="n"/>
       <c r="P63" s="9" t="n"/>
-      <c r="Q63" s="22" t="n"/>
+      <c r="Q63" s="9" t="n"/>
+      <c r="R63" s="9" t="n"/>
+      <c r="S63" s="9" t="n"/>
+      <c r="T63" s="22" t="n"/>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="12" t="n">
@@ -4309,7 +4592,10 @@
       <c r="N64" s="15" t="n"/>
       <c r="O64" s="15" t="n"/>
       <c r="P64" s="13" t="n"/>
-      <c r="Q64" s="24" t="n"/>
+      <c r="Q64" s="13" t="n"/>
+      <c r="R64" s="13" t="n"/>
+      <c r="S64" s="13" t="n"/>
+      <c r="T64" s="24" t="n"/>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="8" t="n">
@@ -4362,7 +4648,10 @@
       <c r="N65" s="11" t="n"/>
       <c r="O65" s="11" t="n"/>
       <c r="P65" s="9" t="n"/>
-      <c r="Q65" s="22" t="n"/>
+      <c r="Q65" s="9" t="n"/>
+      <c r="R65" s="9" t="n"/>
+      <c r="S65" s="9" t="n"/>
+      <c r="T65" s="22" t="n"/>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="12" t="n">
@@ -4415,7 +4704,10 @@
       <c r="N66" s="15" t="n"/>
       <c r="O66" s="15" t="n"/>
       <c r="P66" s="13" t="n"/>
-      <c r="Q66" s="24" t="n"/>
+      <c r="Q66" s="13" t="n"/>
+      <c r="R66" s="13" t="n"/>
+      <c r="S66" s="13" t="n"/>
+      <c r="T66" s="24" t="n"/>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="8" t="n">
@@ -4468,7 +4760,10 @@
       <c r="N67" s="11" t="n"/>
       <c r="O67" s="11" t="n"/>
       <c r="P67" s="9" t="n"/>
-      <c r="Q67" s="22" t="n"/>
+      <c r="Q67" s="9" t="n"/>
+      <c r="R67" s="9" t="n"/>
+      <c r="S67" s="9" t="n"/>
+      <c r="T67" s="22" t="n"/>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="12" t="n">
@@ -4521,7 +4816,10 @@
       <c r="N68" s="15" t="n"/>
       <c r="O68" s="15" t="n"/>
       <c r="P68" s="13" t="n"/>
-      <c r="Q68" s="24" t="n"/>
+      <c r="Q68" s="13" t="n"/>
+      <c r="R68" s="13" t="n"/>
+      <c r="S68" s="13" t="n"/>
+      <c r="T68" s="24" t="n"/>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="8" t="n">
@@ -4574,7 +4872,10 @@
       <c r="N69" s="11" t="n"/>
       <c r="O69" s="11" t="n"/>
       <c r="P69" s="9" t="n"/>
-      <c r="Q69" s="22" t="n"/>
+      <c r="Q69" s="9" t="n"/>
+      <c r="R69" s="9" t="n"/>
+      <c r="S69" s="9" t="n"/>
+      <c r="T69" s="22" t="n"/>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="12" t="n">
@@ -4627,7 +4928,10 @@
       <c r="N70" s="15" t="n"/>
       <c r="O70" s="15" t="n"/>
       <c r="P70" s="13" t="n"/>
-      <c r="Q70" s="24" t="n"/>
+      <c r="Q70" s="13" t="n"/>
+      <c r="R70" s="13" t="n"/>
+      <c r="S70" s="13" t="n"/>
+      <c r="T70" s="24" t="n"/>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="8" t="n">
@@ -4680,7 +4984,10 @@
       <c r="N71" s="11" t="n"/>
       <c r="O71" s="11" t="n"/>
       <c r="P71" s="9" t="n"/>
-      <c r="Q71" s="22" t="n"/>
+      <c r="Q71" s="9" t="n"/>
+      <c r="R71" s="9" t="n"/>
+      <c r="S71" s="9" t="n"/>
+      <c r="T71" s="22" t="n"/>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="12" t="n">
@@ -4733,7 +5040,10 @@
       <c r="N72" s="15" t="n"/>
       <c r="O72" s="15" t="n"/>
       <c r="P72" s="13" t="n"/>
-      <c r="Q72" s="24" t="n"/>
+      <c r="Q72" s="13" t="n"/>
+      <c r="R72" s="13" t="n"/>
+      <c r="S72" s="13" t="n"/>
+      <c r="T72" s="24" t="n"/>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="8" t="n">
@@ -4786,7 +5096,10 @@
       <c r="N73" s="11" t="n"/>
       <c r="O73" s="11" t="n"/>
       <c r="P73" s="9" t="n"/>
-      <c r="Q73" s="22" t="n"/>
+      <c r="Q73" s="9" t="n"/>
+      <c r="R73" s="9" t="n"/>
+      <c r="S73" s="9" t="n"/>
+      <c r="T73" s="22" t="n"/>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="12" t="n">
@@ -4839,7 +5152,10 @@
       <c r="N74" s="15" t="n"/>
       <c r="O74" s="15" t="n"/>
       <c r="P74" s="13" t="n"/>
-      <c r="Q74" s="24" t="n"/>
+      <c r="Q74" s="13" t="n"/>
+      <c r="R74" s="13" t="n"/>
+      <c r="S74" s="13" t="n"/>
+      <c r="T74" s="24" t="n"/>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="8" t="n">
@@ -4892,7 +5208,10 @@
       <c r="N75" s="11" t="n"/>
       <c r="O75" s="11" t="n"/>
       <c r="P75" s="9" t="n"/>
-      <c r="Q75" s="22" t="n"/>
+      <c r="Q75" s="9" t="n"/>
+      <c r="R75" s="9" t="n"/>
+      <c r="S75" s="9" t="n"/>
+      <c r="T75" s="22" t="n"/>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="12" t="n">
@@ -4945,7 +5264,10 @@
       <c r="N76" s="15" t="n"/>
       <c r="O76" s="15" t="n"/>
       <c r="P76" s="13" t="n"/>
-      <c r="Q76" s="24" t="n"/>
+      <c r="Q76" s="13" t="n"/>
+      <c r="R76" s="13" t="n"/>
+      <c r="S76" s="13" t="n"/>
+      <c r="T76" s="24" t="n"/>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="8" t="n">
@@ -4998,7 +5320,10 @@
       <c r="N77" s="11" t="n"/>
       <c r="O77" s="11" t="n"/>
       <c r="P77" s="9" t="n"/>
-      <c r="Q77" s="22" t="n"/>
+      <c r="Q77" s="9" t="n"/>
+      <c r="R77" s="9" t="n"/>
+      <c r="S77" s="9" t="n"/>
+      <c r="T77" s="22" t="n"/>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="12" t="n">
@@ -5051,7 +5376,10 @@
       <c r="N78" s="15" t="n"/>
       <c r="O78" s="15" t="n"/>
       <c r="P78" s="13" t="n"/>
-      <c r="Q78" s="24" t="n"/>
+      <c r="Q78" s="13" t="n"/>
+      <c r="R78" s="13" t="n"/>
+      <c r="S78" s="13" t="n"/>
+      <c r="T78" s="24" t="n"/>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="8" t="n">
@@ -5104,7 +5432,10 @@
       <c r="N79" s="11" t="n"/>
       <c r="O79" s="11" t="n"/>
       <c r="P79" s="9" t="n"/>
-      <c r="Q79" s="22" t="n"/>
+      <c r="Q79" s="9" t="n"/>
+      <c r="R79" s="9" t="n"/>
+      <c r="S79" s="9" t="n"/>
+      <c r="T79" s="22" t="n"/>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="12" t="n">
@@ -5157,7 +5488,10 @@
       <c r="N80" s="15" t="n"/>
       <c r="O80" s="15" t="n"/>
       <c r="P80" s="13" t="n"/>
-      <c r="Q80" s="24" t="n"/>
+      <c r="Q80" s="13" t="n"/>
+      <c r="R80" s="13" t="n"/>
+      <c r="S80" s="13" t="n"/>
+      <c r="T80" s="24" t="n"/>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="8" t="n">
@@ -5210,7 +5544,10 @@
       <c r="N81" s="11" t="n"/>
       <c r="O81" s="11" t="n"/>
       <c r="P81" s="9" t="n"/>
-      <c r="Q81" s="22" t="n"/>
+      <c r="Q81" s="9" t="n"/>
+      <c r="R81" s="9" t="n"/>
+      <c r="S81" s="9" t="n"/>
+      <c r="T81" s="22" t="n"/>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="12" t="n">
@@ -5263,7 +5600,10 @@
       <c r="N82" s="15" t="n"/>
       <c r="O82" s="15" t="n"/>
       <c r="P82" s="13" t="n"/>
-      <c r="Q82" s="24" t="n"/>
+      <c r="Q82" s="13" t="n"/>
+      <c r="R82" s="13" t="n"/>
+      <c r="S82" s="13" t="n"/>
+      <c r="T82" s="24" t="n"/>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="8" t="n">
@@ -5316,7 +5656,10 @@
       <c r="N83" s="11" t="n"/>
       <c r="O83" s="11" t="n"/>
       <c r="P83" s="9" t="n"/>
-      <c r="Q83" s="22" t="n"/>
+      <c r="Q83" s="9" t="n"/>
+      <c r="R83" s="9" t="n"/>
+      <c r="S83" s="9" t="n"/>
+      <c r="T83" s="22" t="n"/>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="12" t="n">
@@ -5369,7 +5712,10 @@
       <c r="N84" s="15" t="n"/>
       <c r="O84" s="15" t="n"/>
       <c r="P84" s="13" t="n"/>
-      <c r="Q84" s="24" t="n"/>
+      <c r="Q84" s="13" t="n"/>
+      <c r="R84" s="13" t="n"/>
+      <c r="S84" s="13" t="n"/>
+      <c r="T84" s="24" t="n"/>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="8" t="n">
@@ -5422,7 +5768,10 @@
       <c r="N85" s="11" t="n"/>
       <c r="O85" s="11" t="n"/>
       <c r="P85" s="9" t="n"/>
-      <c r="Q85" s="22" t="n"/>
+      <c r="Q85" s="9" t="n"/>
+      <c r="R85" s="9" t="n"/>
+      <c r="S85" s="9" t="n"/>
+      <c r="T85" s="22" t="n"/>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="12" t="n">
@@ -5475,7 +5824,10 @@
       <c r="N86" s="15" t="n"/>
       <c r="O86" s="15" t="n"/>
       <c r="P86" s="13" t="n"/>
-      <c r="Q86" s="24" t="n"/>
+      <c r="Q86" s="13" t="n"/>
+      <c r="R86" s="13" t="n"/>
+      <c r="S86" s="13" t="n"/>
+      <c r="T86" s="24" t="n"/>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="8" t="n">
@@ -5528,7 +5880,10 @@
       <c r="N87" s="11" t="n"/>
       <c r="O87" s="11" t="n"/>
       <c r="P87" s="9" t="n"/>
-      <c r="Q87" s="22" t="n"/>
+      <c r="Q87" s="9" t="n"/>
+      <c r="R87" s="9" t="n"/>
+      <c r="S87" s="9" t="n"/>
+      <c r="T87" s="22" t="n"/>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="12" t="n">
@@ -5581,7 +5936,10 @@
       <c r="N88" s="15" t="n"/>
       <c r="O88" s="15" t="n"/>
       <c r="P88" s="13" t="n"/>
-      <c r="Q88" s="24" t="n"/>
+      <c r="Q88" s="13" t="n"/>
+      <c r="R88" s="13" t="n"/>
+      <c r="S88" s="13" t="n"/>
+      <c r="T88" s="24" t="n"/>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="8" t="n">
@@ -5634,7 +5992,10 @@
       <c r="N89" s="11" t="n"/>
       <c r="O89" s="11" t="n"/>
       <c r="P89" s="9" t="n"/>
-      <c r="Q89" s="22" t="n"/>
+      <c r="Q89" s="9" t="n"/>
+      <c r="R89" s="9" t="n"/>
+      <c r="S89" s="9" t="n"/>
+      <c r="T89" s="22" t="n"/>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="12" t="n">
@@ -5687,7 +6048,10 @@
       <c r="N90" s="15" t="n"/>
       <c r="O90" s="15" t="n"/>
       <c r="P90" s="13" t="n"/>
-      <c r="Q90" s="24" t="n"/>
+      <c r="Q90" s="13" t="n"/>
+      <c r="R90" s="13" t="n"/>
+      <c r="S90" s="13" t="n"/>
+      <c r="T90" s="24" t="n"/>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="8" t="n">
@@ -5740,7 +6104,10 @@
       <c r="N91" s="11" t="n"/>
       <c r="O91" s="11" t="n"/>
       <c r="P91" s="9" t="n"/>
-      <c r="Q91" s="22" t="n"/>
+      <c r="Q91" s="9" t="n"/>
+      <c r="R91" s="9" t="n"/>
+      <c r="S91" s="9" t="n"/>
+      <c r="T91" s="22" t="n"/>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="12" t="n">
@@ -5793,7 +6160,10 @@
       <c r="N92" s="15" t="n"/>
       <c r="O92" s="15" t="n"/>
       <c r="P92" s="13" t="n"/>
-      <c r="Q92" s="24" t="n"/>
+      <c r="Q92" s="13" t="n"/>
+      <c r="R92" s="13" t="n"/>
+      <c r="S92" s="13" t="n"/>
+      <c r="T92" s="24" t="n"/>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="8" t="n">
@@ -5846,7 +6216,10 @@
       <c r="N93" s="11" t="n"/>
       <c r="O93" s="11" t="n"/>
       <c r="P93" s="9" t="n"/>
-      <c r="Q93" s="22" t="n"/>
+      <c r="Q93" s="9" t="n"/>
+      <c r="R93" s="9" t="n"/>
+      <c r="S93" s="9" t="n"/>
+      <c r="T93" s="22" t="n"/>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="12" t="n">
@@ -5899,7 +6272,10 @@
       <c r="N94" s="15" t="n"/>
       <c r="O94" s="15" t="n"/>
       <c r="P94" s="13" t="n"/>
-      <c r="Q94" s="24" t="n"/>
+      <c r="Q94" s="13" t="n"/>
+      <c r="R94" s="13" t="n"/>
+      <c r="S94" s="13" t="n"/>
+      <c r="T94" s="24" t="n"/>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="8" t="n">
@@ -5952,7 +6328,10 @@
       <c r="N95" s="11" t="n"/>
       <c r="O95" s="11" t="n"/>
       <c r="P95" s="9" t="n"/>
-      <c r="Q95" s="22" t="n"/>
+      <c r="Q95" s="9" t="n"/>
+      <c r="R95" s="9" t="n"/>
+      <c r="S95" s="9" t="n"/>
+      <c r="T95" s="22" t="n"/>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="12" t="n">
@@ -6005,7 +6384,10 @@
       <c r="N96" s="15" t="n"/>
       <c r="O96" s="15" t="n"/>
       <c r="P96" s="13" t="n"/>
-      <c r="Q96" s="24" t="n"/>
+      <c r="Q96" s="13" t="n"/>
+      <c r="R96" s="13" t="n"/>
+      <c r="S96" s="13" t="n"/>
+      <c r="T96" s="24" t="n"/>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="8" t="n">
@@ -6058,7 +6440,10 @@
       <c r="N97" s="11" t="n"/>
       <c r="O97" s="11" t="n"/>
       <c r="P97" s="9" t="n"/>
-      <c r="Q97" s="22" t="n"/>
+      <c r="Q97" s="9" t="n"/>
+      <c r="R97" s="9" t="n"/>
+      <c r="S97" s="9" t="n"/>
+      <c r="T97" s="22" t="n"/>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="12" t="n">
@@ -6111,7 +6496,10 @@
       <c r="N98" s="15" t="n"/>
       <c r="O98" s="15" t="n"/>
       <c r="P98" s="13" t="n"/>
-      <c r="Q98" s="24" t="n"/>
+      <c r="Q98" s="13" t="n"/>
+      <c r="R98" s="13" t="n"/>
+      <c r="S98" s="13" t="n"/>
+      <c r="T98" s="24" t="n"/>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="8" t="n">
@@ -6164,7 +6552,10 @@
       <c r="N99" s="11" t="n"/>
       <c r="O99" s="11" t="n"/>
       <c r="P99" s="9" t="n"/>
-      <c r="Q99" s="22" t="n"/>
+      <c r="Q99" s="9" t="n"/>
+      <c r="R99" s="9" t="n"/>
+      <c r="S99" s="9" t="n"/>
+      <c r="T99" s="22" t="n"/>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="12" t="n">
@@ -6217,7 +6608,10 @@
       <c r="N100" s="15" t="n"/>
       <c r="O100" s="15" t="n"/>
       <c r="P100" s="13" t="n"/>
-      <c r="Q100" s="24" t="n"/>
+      <c r="Q100" s="13" t="n"/>
+      <c r="R100" s="13" t="n"/>
+      <c r="S100" s="13" t="n"/>
+      <c r="T100" s="24" t="n"/>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="8" t="n">
@@ -6270,7 +6664,10 @@
       <c r="N101" s="11" t="n"/>
       <c r="O101" s="11" t="n"/>
       <c r="P101" s="9" t="n"/>
-      <c r="Q101" s="22" t="n"/>
+      <c r="Q101" s="9" t="n"/>
+      <c r="R101" s="9" t="n"/>
+      <c r="S101" s="9" t="n"/>
+      <c r="T101" s="22" t="n"/>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="12" t="n">
@@ -6323,7 +6720,10 @@
       <c r="N102" s="15" t="n"/>
       <c r="O102" s="15" t="n"/>
       <c r="P102" s="13" t="n"/>
-      <c r="Q102" s="24" t="n"/>
+      <c r="Q102" s="13" t="n"/>
+      <c r="R102" s="13" t="n"/>
+      <c r="S102" s="13" t="n"/>
+      <c r="T102" s="24" t="n"/>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="8" t="n">
@@ -6376,7 +6776,10 @@
       <c r="N103" s="11" t="n"/>
       <c r="O103" s="11" t="n"/>
       <c r="P103" s="9" t="n"/>
-      <c r="Q103" s="22" t="n"/>
+      <c r="Q103" s="9" t="n"/>
+      <c r="R103" s="9" t="n"/>
+      <c r="S103" s="9" t="n"/>
+      <c r="T103" s="22" t="n"/>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="12" t="n">
@@ -6429,7 +6832,10 @@
       <c r="N104" s="15" t="n"/>
       <c r="O104" s="15" t="n"/>
       <c r="P104" s="13" t="n"/>
-      <c r="Q104" s="24" t="n"/>
+      <c r="Q104" s="13" t="n"/>
+      <c r="R104" s="13" t="n"/>
+      <c r="S104" s="13" t="n"/>
+      <c r="T104" s="24" t="n"/>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="8" t="n">
@@ -6482,7 +6888,10 @@
       <c r="N105" s="11" t="n"/>
       <c r="O105" s="11" t="n"/>
       <c r="P105" s="9" t="n"/>
-      <c r="Q105" s="22" t="n"/>
+      <c r="Q105" s="9" t="n"/>
+      <c r="R105" s="9" t="n"/>
+      <c r="S105" s="9" t="n"/>
+      <c r="T105" s="22" t="n"/>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="12" t="n">
@@ -6535,7 +6944,10 @@
       <c r="N106" s="15" t="n"/>
       <c r="O106" s="15" t="n"/>
       <c r="P106" s="13" t="n"/>
-      <c r="Q106" s="24" t="n"/>
+      <c r="Q106" s="13" t="n"/>
+      <c r="R106" s="13" t="n"/>
+      <c r="S106" s="13" t="n"/>
+      <c r="T106" s="24" t="n"/>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="8" t="n">
@@ -6588,7 +7000,10 @@
       <c r="N107" s="11" t="n"/>
       <c r="O107" s="11" t="n"/>
       <c r="P107" s="9" t="n"/>
-      <c r="Q107" s="22" t="n"/>
+      <c r="Q107" s="9" t="n"/>
+      <c r="R107" s="9" t="n"/>
+      <c r="S107" s="9" t="n"/>
+      <c r="T107" s="22" t="n"/>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="12" t="n">
@@ -6641,7 +7056,10 @@
       <c r="N108" s="15" t="n"/>
       <c r="O108" s="15" t="n"/>
       <c r="P108" s="13" t="n"/>
-      <c r="Q108" s="24" t="n"/>
+      <c r="Q108" s="13" t="n"/>
+      <c r="R108" s="13" t="n"/>
+      <c r="S108" s="13" t="n"/>
+      <c r="T108" s="24" t="n"/>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="8" t="n">
@@ -6690,7 +7108,10 @@
       <c r="N109" s="9" t="n"/>
       <c r="O109" s="9" t="n"/>
       <c r="P109" s="9" t="n"/>
-      <c r="Q109" s="22" t="n"/>
+      <c r="Q109" s="9" t="n"/>
+      <c r="R109" s="9" t="n"/>
+      <c r="S109" s="9" t="n"/>
+      <c r="T109" s="22" t="n"/>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="12" t="n">
@@ -6731,7 +7152,10 @@
       <c r="N110" s="13" t="n"/>
       <c r="O110" s="13" t="n"/>
       <c r="P110" s="13" t="n"/>
-      <c r="Q110" s="24" t="n"/>
+      <c r="Q110" s="13" t="n"/>
+      <c r="R110" s="13" t="n"/>
+      <c r="S110" s="13" t="n"/>
+      <c r="T110" s="24" t="n"/>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="8" t="n"/>
@@ -6750,7 +7174,10 @@
       <c r="N111" s="9" t="n"/>
       <c r="O111" s="9" t="n"/>
       <c r="P111" s="9" t="n"/>
-      <c r="Q111" s="22" t="n"/>
+      <c r="Q111" s="9" t="n"/>
+      <c r="R111" s="9" t="n"/>
+      <c r="S111" s="9" t="n"/>
+      <c r="T111" s="22" t="n"/>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="12" t="n"/>
@@ -6769,7 +7196,10 @@
       <c r="N112" s="13" t="n"/>
       <c r="O112" s="13" t="n"/>
       <c r="P112" s="13" t="n"/>
-      <c r="Q112" s="24" t="n"/>
+      <c r="Q112" s="13" t="n"/>
+      <c r="R112" s="13" t="n"/>
+      <c r="S112" s="13" t="n"/>
+      <c r="T112" s="24" t="n"/>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="8" t="n"/>
@@ -6788,7 +7218,10 @@
       <c r="N113" s="9" t="n"/>
       <c r="O113" s="9" t="n"/>
       <c r="P113" s="9" t="n"/>
-      <c r="Q113" s="22" t="n"/>
+      <c r="Q113" s="9" t="n"/>
+      <c r="R113" s="9" t="n"/>
+      <c r="S113" s="9" t="n"/>
+      <c r="T113" s="22" t="n"/>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="12" t="n"/>
@@ -6807,7 +7240,10 @@
       <c r="N114" s="13" t="n"/>
       <c r="O114" s="13" t="n"/>
       <c r="P114" s="13" t="n"/>
-      <c r="Q114" s="24" t="n"/>
+      <c r="Q114" s="13" t="n"/>
+      <c r="R114" s="13" t="n"/>
+      <c r="S114" s="13" t="n"/>
+      <c r="T114" s="24" t="n"/>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="8" t="n"/>
@@ -6826,7 +7262,10 @@
       <c r="N115" s="9" t="n"/>
       <c r="O115" s="9" t="n"/>
       <c r="P115" s="9" t="n"/>
-      <c r="Q115" s="22" t="n"/>
+      <c r="Q115" s="9" t="n"/>
+      <c r="R115" s="9" t="n"/>
+      <c r="S115" s="9" t="n"/>
+      <c r="T115" s="22" t="n"/>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="12" t="n"/>
@@ -6845,7 +7284,10 @@
       <c r="N116" s="13" t="n"/>
       <c r="O116" s="13" t="n"/>
       <c r="P116" s="13" t="n"/>
-      <c r="Q116" s="24" t="n"/>
+      <c r="Q116" s="13" t="n"/>
+      <c r="R116" s="13" t="n"/>
+      <c r="S116" s="13" t="n"/>
+      <c r="T116" s="24" t="n"/>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="8" t="n"/>
@@ -6864,7 +7306,10 @@
       <c r="N117" s="9" t="n"/>
       <c r="O117" s="9" t="n"/>
       <c r="P117" s="9" t="n"/>
-      <c r="Q117" s="22" t="n"/>
+      <c r="Q117" s="9" t="n"/>
+      <c r="R117" s="9" t="n"/>
+      <c r="S117" s="9" t="n"/>
+      <c r="T117" s="22" t="n"/>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="12" t="n"/>
@@ -6883,7 +7328,10 @@
       <c r="N118" s="13" t="n"/>
       <c r="O118" s="13" t="n"/>
       <c r="P118" s="13" t="n"/>
-      <c r="Q118" s="24" t="n"/>
+      <c r="Q118" s="13" t="n"/>
+      <c r="R118" s="13" t="n"/>
+      <c r="S118" s="13" t="n"/>
+      <c r="T118" s="24" t="n"/>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="8" t="n"/>
@@ -6902,7 +7350,10 @@
       <c r="N119" s="9" t="n"/>
       <c r="O119" s="9" t="n"/>
       <c r="P119" s="9" t="n"/>
-      <c r="Q119" s="22" t="n"/>
+      <c r="Q119" s="9" t="n"/>
+      <c r="R119" s="9" t="n"/>
+      <c r="S119" s="9" t="n"/>
+      <c r="T119" s="22" t="n"/>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="12" t="n"/>
@@ -6921,7 +7372,10 @@
       <c r="N120" s="13" t="n"/>
       <c r="O120" s="13" t="n"/>
       <c r="P120" s="13" t="n"/>
-      <c r="Q120" s="24" t="n"/>
+      <c r="Q120" s="13" t="n"/>
+      <c r="R120" s="13" t="n"/>
+      <c r="S120" s="13" t="n"/>
+      <c r="T120" s="24" t="n"/>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="8" t="n"/>
@@ -6940,7 +7394,10 @@
       <c r="N121" s="9" t="n"/>
       <c r="O121" s="9" t="n"/>
       <c r="P121" s="9" t="n"/>
-      <c r="Q121" s="22" t="n"/>
+      <c r="Q121" s="9" t="n"/>
+      <c r="R121" s="9" t="n"/>
+      <c r="S121" s="9" t="n"/>
+      <c r="T121" s="22" t="n"/>
     </row>
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="12" t="n"/>
@@ -6959,7 +7416,10 @@
       <c r="N122" s="13" t="n"/>
       <c r="O122" s="13" t="n"/>
       <c r="P122" s="13" t="n"/>
-      <c r="Q122" s="24" t="n"/>
+      <c r="Q122" s="13" t="n"/>
+      <c r="R122" s="13" t="n"/>
+      <c r="S122" s="13" t="n"/>
+      <c r="T122" s="24" t="n"/>
     </row>
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="8" t="n"/>
@@ -6978,7 +7438,10 @@
       <c r="N123" s="9" t="n"/>
       <c r="O123" s="9" t="n"/>
       <c r="P123" s="9" t="n"/>
-      <c r="Q123" s="22" t="n"/>
+      <c r="Q123" s="9" t="n"/>
+      <c r="R123" s="9" t="n"/>
+      <c r="S123" s="9" t="n"/>
+      <c r="T123" s="22" t="n"/>
     </row>
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="12" t="n"/>
@@ -6997,7 +7460,10 @@
       <c r="N124" s="13" t="n"/>
       <c r="O124" s="13" t="n"/>
       <c r="P124" s="13" t="n"/>
-      <c r="Q124" s="24" t="n"/>
+      <c r="Q124" s="13" t="n"/>
+      <c r="R124" s="13" t="n"/>
+      <c r="S124" s="13" t="n"/>
+      <c r="T124" s="24" t="n"/>
     </row>
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="8" t="n"/>
@@ -7016,7 +7482,10 @@
       <c r="N125" s="9" t="n"/>
       <c r="O125" s="9" t="n"/>
       <c r="P125" s="9" t="n"/>
-      <c r="Q125" s="22" t="n"/>
+      <c r="Q125" s="9" t="n"/>
+      <c r="R125" s="9" t="n"/>
+      <c r="S125" s="9" t="n"/>
+      <c r="T125" s="22" t="n"/>
     </row>
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="12" t="n"/>
@@ -7035,7 +7504,10 @@
       <c r="N126" s="13" t="n"/>
       <c r="O126" s="13" t="n"/>
       <c r="P126" s="13" t="n"/>
-      <c r="Q126" s="24" t="n"/>
+      <c r="Q126" s="13" t="n"/>
+      <c r="R126" s="13" t="n"/>
+      <c r="S126" s="13" t="n"/>
+      <c r="T126" s="24" t="n"/>
     </row>
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="8" t="n"/>
@@ -7054,7 +7526,10 @@
       <c r="N127" s="9" t="n"/>
       <c r="O127" s="9" t="n"/>
       <c r="P127" s="9" t="n"/>
-      <c r="Q127" s="22" t="n"/>
+      <c r="Q127" s="9" t="n"/>
+      <c r="R127" s="9" t="n"/>
+      <c r="S127" s="9" t="n"/>
+      <c r="T127" s="22" t="n"/>
     </row>
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="12" t="n"/>
@@ -7073,7 +7548,10 @@
       <c r="N128" s="13" t="n"/>
       <c r="O128" s="13" t="n"/>
       <c r="P128" s="13" t="n"/>
-      <c r="Q128" s="24" t="n"/>
+      <c r="Q128" s="13" t="n"/>
+      <c r="R128" s="13" t="n"/>
+      <c r="S128" s="13" t="n"/>
+      <c r="T128" s="24" t="n"/>
     </row>
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="8" t="n"/>
@@ -7092,7 +7570,10 @@
       <c r="N129" s="9" t="n"/>
       <c r="O129" s="9" t="n"/>
       <c r="P129" s="9" t="n"/>
-      <c r="Q129" s="22" t="n"/>
+      <c r="Q129" s="9" t="n"/>
+      <c r="R129" s="9" t="n"/>
+      <c r="S129" s="9" t="n"/>
+      <c r="T129" s="22" t="n"/>
     </row>
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="12" t="n"/>
@@ -7111,7 +7592,10 @@
       <c r="N130" s="13" t="n"/>
       <c r="O130" s="13" t="n"/>
       <c r="P130" s="13" t="n"/>
-      <c r="Q130" s="24" t="n"/>
+      <c r="Q130" s="13" t="n"/>
+      <c r="R130" s="13" t="n"/>
+      <c r="S130" s="13" t="n"/>
+      <c r="T130" s="24" t="n"/>
     </row>
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="8" t="n"/>
@@ -7130,7 +7614,10 @@
       <c r="N131" s="9" t="n"/>
       <c r="O131" s="9" t="n"/>
       <c r="P131" s="9" t="n"/>
-      <c r="Q131" s="22" t="n"/>
+      <c r="Q131" s="9" t="n"/>
+      <c r="R131" s="9" t="n"/>
+      <c r="S131" s="9" t="n"/>
+      <c r="T131" s="22" t="n"/>
     </row>
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="12" t="n"/>
@@ -7149,7 +7636,10 @@
       <c r="N132" s="13" t="n"/>
       <c r="O132" s="13" t="n"/>
       <c r="P132" s="13" t="n"/>
-      <c r="Q132" s="24" t="n"/>
+      <c r="Q132" s="13" t="n"/>
+      <c r="R132" s="13" t="n"/>
+      <c r="S132" s="13" t="n"/>
+      <c r="T132" s="24" t="n"/>
     </row>
     <row r="133" ht="22" customHeight="1">
       <c r="A133" s="8" t="n"/>
@@ -7168,7 +7658,10 @@
       <c r="N133" s="9" t="n"/>
       <c r="O133" s="9" t="n"/>
       <c r="P133" s="9" t="n"/>
-      <c r="Q133" s="22" t="n"/>
+      <c r="Q133" s="9" t="n"/>
+      <c r="R133" s="9" t="n"/>
+      <c r="S133" s="9" t="n"/>
+      <c r="T133" s="22" t="n"/>
     </row>
     <row r="134" ht="22" customHeight="1">
       <c r="A134" s="12" t="n"/>
@@ -7187,7 +7680,10 @@
       <c r="N134" s="13" t="n"/>
       <c r="O134" s="13" t="n"/>
       <c r="P134" s="13" t="n"/>
-      <c r="Q134" s="24" t="n"/>
+      <c r="Q134" s="13" t="n"/>
+      <c r="R134" s="13" t="n"/>
+      <c r="S134" s="13" t="n"/>
+      <c r="T134" s="24" t="n"/>
     </row>
     <row r="135" ht="22" customHeight="1">
       <c r="A135" s="8" t="n"/>
@@ -7206,7 +7702,10 @@
       <c r="N135" s="9" t="n"/>
       <c r="O135" s="9" t="n"/>
       <c r="P135" s="9" t="n"/>
-      <c r="Q135" s="22" t="n"/>
+      <c r="Q135" s="9" t="n"/>
+      <c r="R135" s="9" t="n"/>
+      <c r="S135" s="9" t="n"/>
+      <c r="T135" s="22" t="n"/>
     </row>
     <row r="136" ht="22" customHeight="1">
       <c r="A136" s="12" t="n"/>
@@ -7225,7 +7724,10 @@
       <c r="N136" s="13" t="n"/>
       <c r="O136" s="13" t="n"/>
       <c r="P136" s="13" t="n"/>
-      <c r="Q136" s="24" t="n"/>
+      <c r="Q136" s="13" t="n"/>
+      <c r="R136" s="13" t="n"/>
+      <c r="S136" s="13" t="n"/>
+      <c r="T136" s="24" t="n"/>
     </row>
     <row r="137" ht="22" customHeight="1">
       <c r="A137" s="8" t="n"/>
@@ -7244,7 +7746,10 @@
       <c r="N137" s="9" t="n"/>
       <c r="O137" s="9" t="n"/>
       <c r="P137" s="9" t="n"/>
-      <c r="Q137" s="22" t="n"/>
+      <c r="Q137" s="9" t="n"/>
+      <c r="R137" s="9" t="n"/>
+      <c r="S137" s="9" t="n"/>
+      <c r="T137" s="22" t="n"/>
     </row>
     <row r="138" ht="22" customHeight="1">
       <c r="A138" s="12" t="n"/>
@@ -7263,7 +7768,10 @@
       <c r="N138" s="13" t="n"/>
       <c r="O138" s="13" t="n"/>
       <c r="P138" s="13" t="n"/>
-      <c r="Q138" s="24" t="n"/>
+      <c r="Q138" s="13" t="n"/>
+      <c r="R138" s="13" t="n"/>
+      <c r="S138" s="13" t="n"/>
+      <c r="T138" s="24" t="n"/>
     </row>
     <row r="139" ht="22" customHeight="1">
       <c r="A139" s="8" t="n"/>
@@ -7282,7 +7790,10 @@
       <c r="N139" s="9" t="n"/>
       <c r="O139" s="9" t="n"/>
       <c r="P139" s="9" t="n"/>
-      <c r="Q139" s="22" t="n"/>
+      <c r="Q139" s="9" t="n"/>
+      <c r="R139" s="9" t="n"/>
+      <c r="S139" s="9" t="n"/>
+      <c r="T139" s="22" t="n"/>
     </row>
     <row r="140" ht="22" customHeight="1">
       <c r="A140" s="12" t="n"/>
@@ -7301,13 +7812,16 @@
       <c r="N140" s="13" t="n"/>
       <c r="O140" s="13" t="n"/>
       <c r="P140" s="13" t="n"/>
-      <c r="Q140" s="24" t="n"/>
+      <c r="Q140" s="13" t="n"/>
+      <c r="R140" s="13" t="n"/>
+      <c r="S140" s="13" t="n"/>
+      <c r="T140" s="24" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A2:S2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="P5:P109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_설계팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_설계팀_입력_2026.xlsx
@@ -208,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -394,6 +394,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -585,8 +603,11 @@
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 담당자
-(직접 입력)</t>
+        <t>▣ 부서 담당자
+• 부서 내 실제 담당자 이름 입력
+  예: 정민규, 한재운, 이찬
+• 입력 시: PMS에도 자동 반영
+• 빈 칸: 부서 참여 확정, 담당자 미정</t>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
@@ -600,59 +621,100 @@
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 설계검토
-(직접 입력)</t>
+        <t>▣ 설계검토 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 3D/2D설계
-(직접 입력)</t>
+        <t>▣ 3D/2D설계 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ BOM작성
-(직접 입력)</t>
+        <t>▣ BOM작성 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 가공발주
-(직접 입력)</t>
+        <t>▣ 가공발주 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 제안서
-완료일
-(직접 입력)</t>
+        <t>▣ 제안서 완료일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-05-15
+• 허용: 26-5-15, 260515, 2026.5.15 (자동 정규화)
+• 실제 제안서 작성·제출 완료된 날짜 기입
+• 비워두면 미완료 상태
+• 예정일이 아닌 ★실제 완료일★ 만 입력</t>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 설계
-완료일
-(직접 입력)</t>
+        <t>▣ 설계 완료일 (3D/2D 설계 완료)
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-06-30
+• 3D/2D 설계가 실제로 완료된 날짜
+• 비워두면 미완료
+• 예정일 아닌 실제 완료일</t>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 가공의뢰
-입고일
-(직접 입력)</t>
+        <t>▣ 가공의뢰 입고일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-10
+• 가공팀 의뢰분 또는 외주 가공품의
+  ★실제 입고된 날짜★ 기입 (내부·외주 무관)
+• 비워두면: 대시보드 외주현황에 '진행중' 표시
+• 입고일 입력 시: '입고완료'로 자동 분류</t>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 상태
-(직접 입력)</t>
+        <t>▣ 부서 작업 상태
+• 드롭다운 선택:
+  미착수 — 작업 시작 안 함
+  진행중 — 작업 진행 중
+  완료   — 부서 작업 완료
+  N/A    — 해당 부서 무관 프로젝트
+• 부서장이 매주 상태 갱신 권장</t>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메모
-(직접 입력)</t>
+        <t>▣ 메모 (부서 자유 입력)
+• 자유 텍스트 입력
+• 활용:
+  - 이슈사항 (예: 자재 결품, 외주 지연)
+  - 변경 요청 (예: 사양 변경, 납기 조정)
+  - 다른 부서·PM에게 공유할 정보
+• 대시보드 집계에는 미포함</t>
       </text>
     </comment>
   </commentList>
@@ -975,7 +1037,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="58" t="inlineStr">
+      <c r="A1" s="65" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 설계팀 │ 2026</t>
         </is>
@@ -1001,7 +1063,7 @@
       <c r="T1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="59" t="inlineStr">
+      <c r="A2" s="66" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 설계팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1024,9 +1086,9 @@
       <c r="Q2" s="16" t="n"/>
       <c r="R2" s="16" t="n"/>
       <c r="S2" s="17" t="n"/>
-      <c r="T2" s="60" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 00:44</t>
+      <c r="T2" s="67" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 01:06</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_설계팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_설계팀_입력_2026.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,6 +63,12 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="002E7D32"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00E65100"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -208,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -394,6 +400,48 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -621,70 +669,32 @@
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 설계검토 (세부항목 진척률)
-★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        <t>▣ 부서 시작일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-05-10
+• 허용: 26-5-10, 260510, 2026.5.10 (자동 정규화)
+• 부서가 ★실제로 작업을 시작한 날짜★ 기입
+• PO 후 작업 착수일 (지시 받은 날 아님)
+• 비워두면: 미착수 상태
+• v3.1 검사기 운영: 진척률 % 대신 시작·완료일로 추적
+  (2주 단위 빠른 작업 사이클이라 % 입력이 비효율)</t>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 3D/2D설계 (세부항목 진척률)
-★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        <t>▣ 부서 완료일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-05-24
+• 허용: 26-5-24, 260524, 2026.5.24 (자동 정규화)
+• 부서 작업이 ★실제로 완료된 날짜★ 기입
+• 예정일 아닌 ★실제 완료일★ 만 입력
+• 비워두면: PMS 진행현황에서 '미완료'로 집계
+• 입력 시: PMS 2_진행현황에 자동 표시 +
+  전체 진척률 = (완료 부서 수) / (참여 부서 수) 자동 계산
+• '제외' 부서는 분모에서 제외됨</t>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ BOM작성 (세부항목 진척률)
-★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-      </text>
-    </comment>
-    <comment ref="O4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 가공발주 (세부항목 진척률)
-★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-      </text>
-    </comment>
-    <comment ref="P4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 제안서 완료일
-★ 날짜 입력 (% 아님 ⚠️)
-• 형식: YYYY-MM-DD  예: 2026-05-15
-• 허용: 26-5-15, 260515, 2026.5.15 (자동 정규화)
-• 실제 제안서 작성·제출 완료된 날짜 기입
-• 비워두면 미완료 상태
-• 예정일이 아닌 ★실제 완료일★ 만 입력</t>
-      </text>
-    </comment>
-    <comment ref="Q4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 설계 완료일 (3D/2D 설계 완료)
-★ 날짜 입력 (% 아님 ⚠️)
-• 형식: YYYY-MM-DD  예: 2026-06-30
-• 3D/2D 설계가 실제로 완료된 날짜
-• 비워두면 미완료
-• 예정일 아닌 실제 완료일</t>
-      </text>
-    </comment>
-    <comment ref="R4" authorId="0" shapeId="0">
       <text>
         <t>▣ 가공의뢰 입고일
 ★ 날짜 입력 (% 아님 ⚠️)
@@ -695,7 +705,7 @@
 • 입고일 입력 시: '입고완료'로 자동 분류</t>
       </text>
     </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
+    <comment ref="O4" authorId="0" shapeId="0">
       <text>
         <t>▣ 부서 작업 상태
 • 드롭다운 선택:
@@ -706,7 +716,7 @@
 • 부서장이 매주 상태 갱신 권장</t>
       </text>
     </comment>
-    <comment ref="T4" authorId="0" shapeId="0">
+    <comment ref="P4" authorId="0" shapeId="0">
       <text>
         <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
@@ -1011,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T140"/>
+  <dimension ref="A1:P140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1025,11 +1035,11 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" style="43" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" style="43" min="12" max="12"/>
-    <col width="11" customWidth="1" style="43" min="13" max="13"/>
-    <col width="9" customWidth="1" style="43" min="14" max="14"/>
+    <col width="12" customWidth="1" style="43" min="12" max="12"/>
+    <col width="12" customWidth="1" style="43" min="13" max="13"/>
+    <col width="12" customWidth="1" style="43" min="14" max="14"/>
     <col width="10" customWidth="1" style="43" min="15" max="15"/>
-    <col width="12" customWidth="1" style="43" min="16" max="16"/>
+    <col width="28" customWidth="1" style="43" min="16" max="16"/>
     <col width="12" customWidth="1" style="43" min="17" max="17"/>
     <col width="12" customWidth="1" style="43" min="18" max="18"/>
     <col width="10" customWidth="1" style="43" min="19" max="19"/>
@@ -1037,7 +1047,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="65" t="inlineStr">
+      <c r="A1" s="79" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 설계팀 │ 2026</t>
         </is>
@@ -1056,14 +1066,10 @@
       <c r="M1" s="16" t="n"/>
       <c r="N1" s="16" t="n"/>
       <c r="O1" s="16" t="n"/>
-      <c r="P1" s="16" t="n"/>
-      <c r="Q1" s="16" t="n"/>
-      <c r="R1" s="16" t="n"/>
-      <c r="S1" s="16" t="n"/>
-      <c r="T1" s="17" t="n"/>
+      <c r="P1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="66" t="inlineStr">
+      <c r="A2" s="80" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 설계팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1081,14 +1087,10 @@
       <c r="L2" s="16" t="n"/>
       <c r="M2" s="16" t="n"/>
       <c r="N2" s="16" t="n"/>
-      <c r="O2" s="16" t="n"/>
-      <c r="P2" s="16" t="n"/>
-      <c r="Q2" s="16" t="n"/>
-      <c r="R2" s="16" t="n"/>
-      <c r="S2" s="17" t="n"/>
-      <c r="T2" s="67" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 01:06</t>
+      <c r="O2" s="17" t="n"/>
+      <c r="P2" s="81" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 02:00</t>
         </is>
       </c>
     </row>
@@ -1148,47 +1150,27 @@
           <t>🔒자동</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>✏입력</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>✏입력</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>✏입력</t>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>✏입력</t>
+          <t>✏선택▼</t>
         </is>
       </c>
       <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>PO후입력</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>PO후입력</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>PO후입력</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>✏선택▼</t>
-        </is>
-      </c>
-      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>✏메모</t>
         </is>
@@ -1250,50 +1232,30 @@
           <t>전체진척률(%)</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>설계검토</t>
-        </is>
-      </c>
-      <c r="M4" s="7" t="inlineStr">
-        <is>
-          <t>3D/2D설계</t>
-        </is>
-      </c>
-      <c r="N4" s="7" t="inlineStr">
-        <is>
-          <t>BOM작성</t>
-        </is>
-      </c>
-      <c r="O4" s="7" t="inlineStr">
-        <is>
-          <t>가공발주</t>
-        </is>
-      </c>
-      <c r="P4" s="61" t="inlineStr">
-        <is>
-          <t>제안서
+      <c r="L4" s="61" t="inlineStr">
+        <is>
+          <t>부서
+시작일</t>
+        </is>
+      </c>
+      <c r="M4" s="61" t="inlineStr">
+        <is>
+          <t>부서
 완료일</t>
         </is>
       </c>
-      <c r="Q4" s="61" t="inlineStr">
-        <is>
-          <t>설계
-완료일</t>
-        </is>
-      </c>
-      <c r="R4" s="61" t="inlineStr">
+      <c r="N4" s="61" t="inlineStr">
         <is>
           <t>가공의뢰
 입고일</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="T4" s="7" t="inlineStr">
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -1345,15 +1307,11 @@
       </c>
       <c r="J5" s="9" t="n"/>
       <c r="K5" s="10" t="inlineStr"/>
-      <c r="L5" s="11" t="n"/>
-      <c r="M5" s="11" t="n"/>
-      <c r="N5" s="11" t="n"/>
-      <c r="O5" s="11" t="n"/>
-      <c r="P5" s="9" t="n"/>
-      <c r="Q5" s="9" t="n"/>
-      <c r="R5" s="9" t="n"/>
-      <c r="S5" s="9" t="n"/>
-      <c r="T5" s="22" t="n"/>
+      <c r="L5" s="9" t="n"/>
+      <c r="M5" s="9" t="n"/>
+      <c r="N5" s="9" t="n"/>
+      <c r="O5" s="9" t="n"/>
+      <c r="P5" s="22" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="12" t="n">
@@ -1401,15 +1359,11 @@
       </c>
       <c r="J6" s="13" t="n"/>
       <c r="K6" s="14" t="inlineStr"/>
-      <c r="L6" s="15" t="n"/>
-      <c r="M6" s="15" t="n"/>
-      <c r="N6" s="15" t="n"/>
-      <c r="O6" s="15" t="n"/>
-      <c r="P6" s="13" t="n"/>
-      <c r="Q6" s="13" t="n"/>
-      <c r="R6" s="13" t="n"/>
-      <c r="S6" s="13" t="n"/>
-      <c r="T6" s="24" t="n"/>
+      <c r="L6" s="13" t="n"/>
+      <c r="M6" s="13" t="n"/>
+      <c r="N6" s="13" t="n"/>
+      <c r="O6" s="13" t="n"/>
+      <c r="P6" s="24" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="n">
@@ -1457,15 +1411,11 @@
       </c>
       <c r="J7" s="9" t="n"/>
       <c r="K7" s="10" t="inlineStr"/>
-      <c r="L7" s="11" t="n"/>
-      <c r="M7" s="11" t="n"/>
-      <c r="N7" s="11" t="n"/>
-      <c r="O7" s="11" t="n"/>
-      <c r="P7" s="9" t="n"/>
-      <c r="Q7" s="9" t="n"/>
-      <c r="R7" s="9" t="n"/>
-      <c r="S7" s="9" t="n"/>
-      <c r="T7" s="22" t="n"/>
+      <c r="L7" s="9" t="n"/>
+      <c r="M7" s="9" t="n"/>
+      <c r="N7" s="9" t="n"/>
+      <c r="O7" s="9" t="n"/>
+      <c r="P7" s="22" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="12" t="n">
@@ -1513,15 +1463,11 @@
       </c>
       <c r="J8" s="13" t="n"/>
       <c r="K8" s="14" t="inlineStr"/>
-      <c r="L8" s="15" t="n"/>
-      <c r="M8" s="15" t="n"/>
-      <c r="N8" s="15" t="n"/>
-      <c r="O8" s="15" t="n"/>
-      <c r="P8" s="13" t="n"/>
-      <c r="Q8" s="13" t="n"/>
-      <c r="R8" s="13" t="n"/>
-      <c r="S8" s="13" t="n"/>
-      <c r="T8" s="24" t="n"/>
+      <c r="L8" s="13" t="n"/>
+      <c r="M8" s="13" t="n"/>
+      <c r="N8" s="13" t="n"/>
+      <c r="O8" s="13" t="n"/>
+      <c r="P8" s="24" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="8" t="n">
@@ -1569,15 +1515,11 @@
       </c>
       <c r="J9" s="9" t="n"/>
       <c r="K9" s="10" t="inlineStr"/>
-      <c r="L9" s="11" t="n"/>
-      <c r="M9" s="11" t="n"/>
-      <c r="N9" s="11" t="n"/>
-      <c r="O9" s="11" t="n"/>
-      <c r="P9" s="9" t="n"/>
-      <c r="Q9" s="9" t="n"/>
-      <c r="R9" s="9" t="n"/>
-      <c r="S9" s="9" t="n"/>
-      <c r="T9" s="22" t="n"/>
+      <c r="L9" s="9" t="n"/>
+      <c r="M9" s="9" t="n"/>
+      <c r="N9" s="9" t="n"/>
+      <c r="O9" s="9" t="n"/>
+      <c r="P9" s="22" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="12" t="n">
@@ -1625,15 +1567,11 @@
       </c>
       <c r="J10" s="13" t="n"/>
       <c r="K10" s="14" t="inlineStr"/>
-      <c r="L10" s="15" t="n"/>
-      <c r="M10" s="15" t="n"/>
-      <c r="N10" s="15" t="n"/>
-      <c r="O10" s="15" t="n"/>
-      <c r="P10" s="13" t="n"/>
-      <c r="Q10" s="13" t="n"/>
-      <c r="R10" s="13" t="n"/>
-      <c r="S10" s="13" t="n"/>
-      <c r="T10" s="24" t="n"/>
+      <c r="L10" s="13" t="n"/>
+      <c r="M10" s="13" t="n"/>
+      <c r="N10" s="13" t="n"/>
+      <c r="O10" s="13" t="n"/>
+      <c r="P10" s="24" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="8" t="n">
@@ -1681,15 +1619,11 @@
       </c>
       <c r="J11" s="9" t="n"/>
       <c r="K11" s="10" t="inlineStr"/>
-      <c r="L11" s="11" t="n"/>
-      <c r="M11" s="11" t="n"/>
-      <c r="N11" s="11" t="n"/>
-      <c r="O11" s="11" t="n"/>
-      <c r="P11" s="9" t="n"/>
-      <c r="Q11" s="9" t="n"/>
-      <c r="R11" s="9" t="n"/>
-      <c r="S11" s="9" t="n"/>
-      <c r="T11" s="22" t="n"/>
+      <c r="L11" s="9" t="n"/>
+      <c r="M11" s="9" t="n"/>
+      <c r="N11" s="9" t="n"/>
+      <c r="O11" s="9" t="n"/>
+      <c r="P11" s="22" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="12" t="n">
@@ -1737,15 +1671,11 @@
       </c>
       <c r="J12" s="13" t="n"/>
       <c r="K12" s="14" t="inlineStr"/>
-      <c r="L12" s="15" t="n"/>
-      <c r="M12" s="15" t="n"/>
-      <c r="N12" s="15" t="n"/>
-      <c r="O12" s="15" t="n"/>
-      <c r="P12" s="13" t="n"/>
-      <c r="Q12" s="13" t="n"/>
-      <c r="R12" s="13" t="n"/>
-      <c r="S12" s="13" t="n"/>
-      <c r="T12" s="24" t="n"/>
+      <c r="L12" s="13" t="n"/>
+      <c r="M12" s="13" t="n"/>
+      <c r="N12" s="13" t="n"/>
+      <c r="O12" s="13" t="n"/>
+      <c r="P12" s="24" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="8" t="n">
@@ -1793,15 +1723,11 @@
       </c>
       <c r="J13" s="9" t="n"/>
       <c r="K13" s="10" t="inlineStr"/>
-      <c r="L13" s="11" t="n"/>
-      <c r="M13" s="11" t="n"/>
-      <c r="N13" s="11" t="n"/>
-      <c r="O13" s="11" t="n"/>
-      <c r="P13" s="9" t="n"/>
-      <c r="Q13" s="9" t="n"/>
-      <c r="R13" s="9" t="n"/>
-      <c r="S13" s="9" t="n"/>
-      <c r="T13" s="22" t="n"/>
+      <c r="L13" s="9" t="n"/>
+      <c r="M13" s="9" t="n"/>
+      <c r="N13" s="9" t="n"/>
+      <c r="O13" s="9" t="n"/>
+      <c r="P13" s="22" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="12" t="n">
@@ -1849,15 +1775,11 @@
       </c>
       <c r="J14" s="13" t="n"/>
       <c r="K14" s="14" t="inlineStr"/>
-      <c r="L14" s="15" t="n"/>
-      <c r="M14" s="15" t="n"/>
-      <c r="N14" s="15" t="n"/>
-      <c r="O14" s="15" t="n"/>
-      <c r="P14" s="13" t="n"/>
-      <c r="Q14" s="13" t="n"/>
-      <c r="R14" s="13" t="n"/>
-      <c r="S14" s="13" t="n"/>
-      <c r="T14" s="24" t="n"/>
+      <c r="L14" s="13" t="n"/>
+      <c r="M14" s="13" t="n"/>
+      <c r="N14" s="13" t="n"/>
+      <c r="O14" s="13" t="n"/>
+      <c r="P14" s="24" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="8" t="n">
@@ -1905,15 +1827,11 @@
       </c>
       <c r="J15" s="9" t="n"/>
       <c r="K15" s="10" t="inlineStr"/>
-      <c r="L15" s="11" t="n"/>
-      <c r="M15" s="11" t="n"/>
-      <c r="N15" s="11" t="n"/>
-      <c r="O15" s="11" t="n"/>
-      <c r="P15" s="9" t="n"/>
-      <c r="Q15" s="9" t="n"/>
-      <c r="R15" s="9" t="n"/>
-      <c r="S15" s="9" t="n"/>
-      <c r="T15" s="22" t="n"/>
+      <c r="L15" s="9" t="n"/>
+      <c r="M15" s="9" t="n"/>
+      <c r="N15" s="9" t="n"/>
+      <c r="O15" s="9" t="n"/>
+      <c r="P15" s="22" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="12" t="n">
@@ -1961,15 +1879,11 @@
       </c>
       <c r="J16" s="13" t="n"/>
       <c r="K16" s="14" t="inlineStr"/>
-      <c r="L16" s="15" t="n"/>
-      <c r="M16" s="15" t="n"/>
-      <c r="N16" s="15" t="n"/>
-      <c r="O16" s="15" t="n"/>
-      <c r="P16" s="13" t="n"/>
-      <c r="Q16" s="13" t="n"/>
-      <c r="R16" s="13" t="n"/>
-      <c r="S16" s="13" t="n"/>
-      <c r="T16" s="24" t="n"/>
+      <c r="L16" s="13" t="n"/>
+      <c r="M16" s="13" t="n"/>
+      <c r="N16" s="13" t="n"/>
+      <c r="O16" s="13" t="n"/>
+      <c r="P16" s="24" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="8" t="n">
@@ -2017,15 +1931,11 @@
       </c>
       <c r="J17" s="9" t="n"/>
       <c r="K17" s="10" t="inlineStr"/>
-      <c r="L17" s="11" t="n"/>
-      <c r="M17" s="11" t="n"/>
-      <c r="N17" s="11" t="n"/>
-      <c r="O17" s="11" t="n"/>
-      <c r="P17" s="9" t="n"/>
-      <c r="Q17" s="9" t="n"/>
-      <c r="R17" s="9" t="n"/>
-      <c r="S17" s="9" t="n"/>
-      <c r="T17" s="22" t="n"/>
+      <c r="L17" s="9" t="n"/>
+      <c r="M17" s="9" t="n"/>
+      <c r="N17" s="9" t="n"/>
+      <c r="O17" s="9" t="n"/>
+      <c r="P17" s="22" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="12" t="n">
@@ -2073,15 +1983,11 @@
       </c>
       <c r="J18" s="13" t="n"/>
       <c r="K18" s="14" t="inlineStr"/>
-      <c r="L18" s="15" t="n"/>
-      <c r="M18" s="15" t="n"/>
-      <c r="N18" s="15" t="n"/>
-      <c r="O18" s="15" t="n"/>
-      <c r="P18" s="13" t="n"/>
-      <c r="Q18" s="13" t="n"/>
-      <c r="R18" s="13" t="n"/>
-      <c r="S18" s="13" t="n"/>
-      <c r="T18" s="24" t="n"/>
+      <c r="L18" s="13" t="n"/>
+      <c r="M18" s="13" t="n"/>
+      <c r="N18" s="13" t="n"/>
+      <c r="O18" s="13" t="n"/>
+      <c r="P18" s="24" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="8" t="n">
@@ -2129,15 +2035,11 @@
       </c>
       <c r="J19" s="9" t="n"/>
       <c r="K19" s="10" t="inlineStr"/>
-      <c r="L19" s="11" t="n"/>
-      <c r="M19" s="11" t="n"/>
-      <c r="N19" s="11" t="n"/>
-      <c r="O19" s="11" t="n"/>
-      <c r="P19" s="9" t="n"/>
-      <c r="Q19" s="9" t="n"/>
-      <c r="R19" s="9" t="n"/>
-      <c r="S19" s="9" t="n"/>
-      <c r="T19" s="22" t="n"/>
+      <c r="L19" s="9" t="n"/>
+      <c r="M19" s="9" t="n"/>
+      <c r="N19" s="9" t="n"/>
+      <c r="O19" s="9" t="n"/>
+      <c r="P19" s="22" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="12" t="n">
@@ -2185,15 +2087,11 @@
       </c>
       <c r="J20" s="13" t="n"/>
       <c r="K20" s="14" t="inlineStr"/>
-      <c r="L20" s="15" t="n"/>
-      <c r="M20" s="15" t="n"/>
-      <c r="N20" s="15" t="n"/>
-      <c r="O20" s="15" t="n"/>
-      <c r="P20" s="13" t="n"/>
-      <c r="Q20" s="13" t="n"/>
-      <c r="R20" s="13" t="n"/>
-      <c r="S20" s="13" t="n"/>
-      <c r="T20" s="24" t="n"/>
+      <c r="L20" s="13" t="n"/>
+      <c r="M20" s="13" t="n"/>
+      <c r="N20" s="13" t="n"/>
+      <c r="O20" s="13" t="n"/>
+      <c r="P20" s="24" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="8" t="n">
@@ -2241,15 +2139,11 @@
       </c>
       <c r="J21" s="9" t="n"/>
       <c r="K21" s="10" t="inlineStr"/>
-      <c r="L21" s="11" t="n"/>
-      <c r="M21" s="11" t="n"/>
-      <c r="N21" s="11" t="n"/>
-      <c r="O21" s="11" t="n"/>
-      <c r="P21" s="9" t="n"/>
-      <c r="Q21" s="9" t="n"/>
-      <c r="R21" s="9" t="n"/>
-      <c r="S21" s="9" t="n"/>
-      <c r="T21" s="22" t="n"/>
+      <c r="L21" s="9" t="n"/>
+      <c r="M21" s="9" t="n"/>
+      <c r="N21" s="9" t="n"/>
+      <c r="O21" s="9" t="n"/>
+      <c r="P21" s="22" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="12" t="n">
@@ -2297,15 +2191,11 @@
       </c>
       <c r="J22" s="13" t="n"/>
       <c r="K22" s="14" t="inlineStr"/>
-      <c r="L22" s="15" t="n"/>
-      <c r="M22" s="15" t="n"/>
-      <c r="N22" s="15" t="n"/>
-      <c r="O22" s="15" t="n"/>
-      <c r="P22" s="13" t="n"/>
-      <c r="Q22" s="13" t="n"/>
-      <c r="R22" s="13" t="n"/>
-      <c r="S22" s="13" t="n"/>
-      <c r="T22" s="24" t="n"/>
+      <c r="L22" s="13" t="n"/>
+      <c r="M22" s="13" t="n"/>
+      <c r="N22" s="13" t="n"/>
+      <c r="O22" s="13" t="n"/>
+      <c r="P22" s="24" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="8" t="n">
@@ -2353,15 +2243,11 @@
       </c>
       <c r="J23" s="9" t="n"/>
       <c r="K23" s="10" t="inlineStr"/>
-      <c r="L23" s="11" t="n"/>
-      <c r="M23" s="11" t="n"/>
-      <c r="N23" s="11" t="n"/>
-      <c r="O23" s="11" t="n"/>
-      <c r="P23" s="9" t="n"/>
-      <c r="Q23" s="9" t="n"/>
-      <c r="R23" s="9" t="n"/>
-      <c r="S23" s="9" t="n"/>
-      <c r="T23" s="22" t="n"/>
+      <c r="L23" s="9" t="n"/>
+      <c r="M23" s="9" t="n"/>
+      <c r="N23" s="9" t="n"/>
+      <c r="O23" s="9" t="n"/>
+      <c r="P23" s="22" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="12" t="n">
@@ -2409,15 +2295,11 @@
       </c>
       <c r="J24" s="13" t="n"/>
       <c r="K24" s="14" t="inlineStr"/>
-      <c r="L24" s="15" t="n"/>
-      <c r="M24" s="15" t="n"/>
-      <c r="N24" s="15" t="n"/>
-      <c r="O24" s="15" t="n"/>
-      <c r="P24" s="13" t="n"/>
-      <c r="Q24" s="13" t="n"/>
-      <c r="R24" s="13" t="n"/>
-      <c r="S24" s="13" t="n"/>
-      <c r="T24" s="24" t="n"/>
+      <c r="L24" s="13" t="n"/>
+      <c r="M24" s="13" t="n"/>
+      <c r="N24" s="13" t="n"/>
+      <c r="O24" s="13" t="n"/>
+      <c r="P24" s="24" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="8" t="n">
@@ -2465,15 +2347,11 @@
       </c>
       <c r="J25" s="9" t="n"/>
       <c r="K25" s="10" t="inlineStr"/>
-      <c r="L25" s="11" t="n"/>
-      <c r="M25" s="11" t="n"/>
-      <c r="N25" s="11" t="n"/>
-      <c r="O25" s="11" t="n"/>
-      <c r="P25" s="9" t="n"/>
-      <c r="Q25" s="9" t="n"/>
-      <c r="R25" s="9" t="n"/>
-      <c r="S25" s="9" t="n"/>
-      <c r="T25" s="22" t="n"/>
+      <c r="L25" s="9" t="n"/>
+      <c r="M25" s="9" t="n"/>
+      <c r="N25" s="9" t="n"/>
+      <c r="O25" s="9" t="n"/>
+      <c r="P25" s="22" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="12" t="n">
@@ -2521,15 +2399,11 @@
       </c>
       <c r="J26" s="13" t="n"/>
       <c r="K26" s="14" t="inlineStr"/>
-      <c r="L26" s="15" t="n"/>
-      <c r="M26" s="15" t="n"/>
-      <c r="N26" s="15" t="n"/>
-      <c r="O26" s="15" t="n"/>
-      <c r="P26" s="13" t="n"/>
-      <c r="Q26" s="13" t="n"/>
-      <c r="R26" s="13" t="n"/>
-      <c r="S26" s="13" t="n"/>
-      <c r="T26" s="24" t="n"/>
+      <c r="L26" s="13" t="n"/>
+      <c r="M26" s="13" t="n"/>
+      <c r="N26" s="13" t="n"/>
+      <c r="O26" s="13" t="n"/>
+      <c r="P26" s="24" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="8" t="n">
@@ -2577,15 +2451,11 @@
       </c>
       <c r="J27" s="9" t="n"/>
       <c r="K27" s="10" t="inlineStr"/>
-      <c r="L27" s="11" t="n"/>
-      <c r="M27" s="11" t="n"/>
-      <c r="N27" s="11" t="n"/>
-      <c r="O27" s="11" t="n"/>
-      <c r="P27" s="9" t="n"/>
-      <c r="Q27" s="9" t="n"/>
-      <c r="R27" s="9" t="n"/>
-      <c r="S27" s="9" t="n"/>
-      <c r="T27" s="22" t="n"/>
+      <c r="L27" s="9" t="n"/>
+      <c r="M27" s="9" t="n"/>
+      <c r="N27" s="9" t="n"/>
+      <c r="O27" s="9" t="n"/>
+      <c r="P27" s="22" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="12" t="n">
@@ -2633,15 +2503,11 @@
       </c>
       <c r="J28" s="13" t="n"/>
       <c r="K28" s="14" t="inlineStr"/>
-      <c r="L28" s="15" t="n"/>
-      <c r="M28" s="15" t="n"/>
-      <c r="N28" s="15" t="n"/>
-      <c r="O28" s="15" t="n"/>
-      <c r="P28" s="13" t="n"/>
-      <c r="Q28" s="13" t="n"/>
-      <c r="R28" s="13" t="n"/>
-      <c r="S28" s="13" t="n"/>
-      <c r="T28" s="24" t="n"/>
+      <c r="L28" s="13" t="n"/>
+      <c r="M28" s="13" t="n"/>
+      <c r="N28" s="13" t="n"/>
+      <c r="O28" s="13" t="n"/>
+      <c r="P28" s="24" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="8" t="n">
@@ -2689,15 +2555,11 @@
       </c>
       <c r="J29" s="9" t="n"/>
       <c r="K29" s="10" t="inlineStr"/>
-      <c r="L29" s="11" t="n"/>
-      <c r="M29" s="11" t="n"/>
-      <c r="N29" s="11" t="n"/>
-      <c r="O29" s="11" t="n"/>
-      <c r="P29" s="9" t="n"/>
-      <c r="Q29" s="9" t="n"/>
-      <c r="R29" s="9" t="n"/>
-      <c r="S29" s="9" t="n"/>
-      <c r="T29" s="22" t="n"/>
+      <c r="L29" s="9" t="n"/>
+      <c r="M29" s="9" t="n"/>
+      <c r="N29" s="9" t="n"/>
+      <c r="O29" s="9" t="n"/>
+      <c r="P29" s="22" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="12" t="n">
@@ -2745,15 +2607,11 @@
       </c>
       <c r="J30" s="13" t="n"/>
       <c r="K30" s="14" t="inlineStr"/>
-      <c r="L30" s="15" t="n"/>
-      <c r="M30" s="15" t="n"/>
-      <c r="N30" s="15" t="n"/>
-      <c r="O30" s="15" t="n"/>
-      <c r="P30" s="13" t="n"/>
-      <c r="Q30" s="13" t="n"/>
-      <c r="R30" s="13" t="n"/>
-      <c r="S30" s="13" t="n"/>
-      <c r="T30" s="24" t="n"/>
+      <c r="L30" s="13" t="n"/>
+      <c r="M30" s="13" t="n"/>
+      <c r="N30" s="13" t="n"/>
+      <c r="O30" s="13" t="n"/>
+      <c r="P30" s="24" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="8" t="n">
@@ -2801,15 +2659,11 @@
       </c>
       <c r="J31" s="9" t="n"/>
       <c r="K31" s="10" t="inlineStr"/>
-      <c r="L31" s="11" t="n"/>
-      <c r="M31" s="11" t="n"/>
-      <c r="N31" s="11" t="n"/>
-      <c r="O31" s="11" t="n"/>
-      <c r="P31" s="9" t="n"/>
-      <c r="Q31" s="9" t="n"/>
-      <c r="R31" s="9" t="n"/>
-      <c r="S31" s="9" t="n"/>
-      <c r="T31" s="22" t="n"/>
+      <c r="L31" s="9" t="n"/>
+      <c r="M31" s="9" t="n"/>
+      <c r="N31" s="9" t="n"/>
+      <c r="O31" s="9" t="n"/>
+      <c r="P31" s="22" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="12" t="n">
@@ -2857,15 +2711,11 @@
       </c>
       <c r="J32" s="13" t="n"/>
       <c r="K32" s="14" t="inlineStr"/>
-      <c r="L32" s="15" t="n"/>
-      <c r="M32" s="15" t="n"/>
-      <c r="N32" s="15" t="n"/>
-      <c r="O32" s="15" t="n"/>
-      <c r="P32" s="13" t="n"/>
-      <c r="Q32" s="13" t="n"/>
-      <c r="R32" s="13" t="n"/>
-      <c r="S32" s="13" t="n"/>
-      <c r="T32" s="24" t="n"/>
+      <c r="L32" s="13" t="n"/>
+      <c r="M32" s="13" t="n"/>
+      <c r="N32" s="13" t="n"/>
+      <c r="O32" s="13" t="n"/>
+      <c r="P32" s="24" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="8" t="n">
@@ -2913,15 +2763,11 @@
       </c>
       <c r="J33" s="9" t="n"/>
       <c r="K33" s="10" t="inlineStr"/>
-      <c r="L33" s="11" t="n"/>
-      <c r="M33" s="11" t="n"/>
-      <c r="N33" s="11" t="n"/>
-      <c r="O33" s="11" t="n"/>
-      <c r="P33" s="9" t="n"/>
-      <c r="Q33" s="9" t="n"/>
-      <c r="R33" s="9" t="n"/>
-      <c r="S33" s="9" t="n"/>
-      <c r="T33" s="22" t="n"/>
+      <c r="L33" s="9" t="n"/>
+      <c r="M33" s="9" t="n"/>
+      <c r="N33" s="9" t="n"/>
+      <c r="O33" s="9" t="n"/>
+      <c r="P33" s="22" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="12" t="n">
@@ -2969,15 +2815,11 @@
       </c>
       <c r="J34" s="13" t="n"/>
       <c r="K34" s="14" t="inlineStr"/>
-      <c r="L34" s="15" t="n"/>
-      <c r="M34" s="15" t="n"/>
-      <c r="N34" s="15" t="n"/>
-      <c r="O34" s="15" t="n"/>
-      <c r="P34" s="13" t="n"/>
-      <c r="Q34" s="13" t="n"/>
-      <c r="R34" s="13" t="n"/>
-      <c r="S34" s="13" t="n"/>
-      <c r="T34" s="24" t="n"/>
+      <c r="L34" s="13" t="n"/>
+      <c r="M34" s="13" t="n"/>
+      <c r="N34" s="13" t="n"/>
+      <c r="O34" s="13" t="n"/>
+      <c r="P34" s="24" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="8" t="n">
@@ -3025,15 +2867,11 @@
       </c>
       <c r="J35" s="9" t="n"/>
       <c r="K35" s="10" t="inlineStr"/>
-      <c r="L35" s="11" t="n"/>
-      <c r="M35" s="11" t="n"/>
-      <c r="N35" s="11" t="n"/>
-      <c r="O35" s="11" t="n"/>
-      <c r="P35" s="9" t="n"/>
-      <c r="Q35" s="9" t="n"/>
-      <c r="R35" s="9" t="n"/>
-      <c r="S35" s="9" t="n"/>
-      <c r="T35" s="22" t="n"/>
+      <c r="L35" s="9" t="n"/>
+      <c r="M35" s="9" t="n"/>
+      <c r="N35" s="9" t="n"/>
+      <c r="O35" s="9" t="n"/>
+      <c r="P35" s="22" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="12" t="n">
@@ -3081,15 +2919,11 @@
       </c>
       <c r="J36" s="13" t="n"/>
       <c r="K36" s="14" t="inlineStr"/>
-      <c r="L36" s="15" t="n"/>
-      <c r="M36" s="15" t="n"/>
-      <c r="N36" s="15" t="n"/>
-      <c r="O36" s="15" t="n"/>
-      <c r="P36" s="13" t="n"/>
-      <c r="Q36" s="13" t="n"/>
-      <c r="R36" s="13" t="n"/>
-      <c r="S36" s="13" t="n"/>
-      <c r="T36" s="24" t="n"/>
+      <c r="L36" s="13" t="n"/>
+      <c r="M36" s="13" t="n"/>
+      <c r="N36" s="13" t="n"/>
+      <c r="O36" s="13" t="n"/>
+      <c r="P36" s="24" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="8" t="n">
@@ -3137,15 +2971,11 @@
       </c>
       <c r="J37" s="9" t="n"/>
       <c r="K37" s="10" t="inlineStr"/>
-      <c r="L37" s="11" t="n"/>
-      <c r="M37" s="11" t="n"/>
-      <c r="N37" s="11" t="n"/>
-      <c r="O37" s="11" t="n"/>
-      <c r="P37" s="9" t="n"/>
-      <c r="Q37" s="9" t="n"/>
-      <c r="R37" s="9" t="n"/>
-      <c r="S37" s="9" t="n"/>
-      <c r="T37" s="22" t="n"/>
+      <c r="L37" s="9" t="n"/>
+      <c r="M37" s="9" t="n"/>
+      <c r="N37" s="9" t="n"/>
+      <c r="O37" s="9" t="n"/>
+      <c r="P37" s="22" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="12" t="n">
@@ -3193,15 +3023,11 @@
       </c>
       <c r="J38" s="13" t="n"/>
       <c r="K38" s="14" t="inlineStr"/>
-      <c r="L38" s="15" t="n"/>
-      <c r="M38" s="15" t="n"/>
-      <c r="N38" s="15" t="n"/>
-      <c r="O38" s="15" t="n"/>
-      <c r="P38" s="13" t="n"/>
-      <c r="Q38" s="13" t="n"/>
-      <c r="R38" s="13" t="n"/>
-      <c r="S38" s="13" t="n"/>
-      <c r="T38" s="24" t="n"/>
+      <c r="L38" s="13" t="n"/>
+      <c r="M38" s="13" t="n"/>
+      <c r="N38" s="13" t="n"/>
+      <c r="O38" s="13" t="n"/>
+      <c r="P38" s="24" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="8" t="n">
@@ -3249,15 +3075,11 @@
       </c>
       <c r="J39" s="9" t="n"/>
       <c r="K39" s="10" t="inlineStr"/>
-      <c r="L39" s="11" t="n"/>
-      <c r="M39" s="11" t="n"/>
-      <c r="N39" s="11" t="n"/>
-      <c r="O39" s="11" t="n"/>
-      <c r="P39" s="9" t="n"/>
-      <c r="Q39" s="9" t="n"/>
-      <c r="R39" s="9" t="n"/>
-      <c r="S39" s="9" t="n"/>
-      <c r="T39" s="22" t="n"/>
+      <c r="L39" s="9" t="n"/>
+      <c r="M39" s="9" t="n"/>
+      <c r="N39" s="9" t="n"/>
+      <c r="O39" s="9" t="n"/>
+      <c r="P39" s="22" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="12" t="n">
@@ -3305,15 +3127,11 @@
       </c>
       <c r="J40" s="13" t="n"/>
       <c r="K40" s="14" t="inlineStr"/>
-      <c r="L40" s="15" t="n"/>
-      <c r="M40" s="15" t="n"/>
-      <c r="N40" s="15" t="n"/>
-      <c r="O40" s="15" t="n"/>
-      <c r="P40" s="13" t="n"/>
-      <c r="Q40" s="13" t="n"/>
-      <c r="R40" s="13" t="n"/>
-      <c r="S40" s="13" t="n"/>
-      <c r="T40" s="24" t="n"/>
+      <c r="L40" s="13" t="n"/>
+      <c r="M40" s="13" t="n"/>
+      <c r="N40" s="13" t="n"/>
+      <c r="O40" s="13" t="n"/>
+      <c r="P40" s="24" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="8" t="n">
@@ -3361,15 +3179,11 @@
       </c>
       <c r="J41" s="9" t="n"/>
       <c r="K41" s="10" t="inlineStr"/>
-      <c r="L41" s="11" t="n"/>
-      <c r="M41" s="11" t="n"/>
-      <c r="N41" s="11" t="n"/>
-      <c r="O41" s="11" t="n"/>
-      <c r="P41" s="9" t="n"/>
-      <c r="Q41" s="9" t="n"/>
-      <c r="R41" s="9" t="n"/>
-      <c r="S41" s="9" t="n"/>
-      <c r="T41" s="22" t="n"/>
+      <c r="L41" s="9" t="n"/>
+      <c r="M41" s="9" t="n"/>
+      <c r="N41" s="9" t="n"/>
+      <c r="O41" s="9" t="n"/>
+      <c r="P41" s="22" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="12" t="n">
@@ -3417,15 +3231,11 @@
       </c>
       <c r="J42" s="13" t="n"/>
       <c r="K42" s="14" t="inlineStr"/>
-      <c r="L42" s="15" t="n"/>
-      <c r="M42" s="15" t="n"/>
-      <c r="N42" s="15" t="n"/>
-      <c r="O42" s="15" t="n"/>
-      <c r="P42" s="13" t="n"/>
-      <c r="Q42" s="13" t="n"/>
-      <c r="R42" s="13" t="n"/>
-      <c r="S42" s="13" t="n"/>
-      <c r="T42" s="24" t="n"/>
+      <c r="L42" s="13" t="n"/>
+      <c r="M42" s="13" t="n"/>
+      <c r="N42" s="13" t="n"/>
+      <c r="O42" s="13" t="n"/>
+      <c r="P42" s="24" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="8" t="n">
@@ -3473,15 +3283,11 @@
       </c>
       <c r="J43" s="9" t="n"/>
       <c r="K43" s="10" t="inlineStr"/>
-      <c r="L43" s="11" t="n"/>
-      <c r="M43" s="11" t="n"/>
-      <c r="N43" s="11" t="n"/>
-      <c r="O43" s="11" t="n"/>
-      <c r="P43" s="9" t="n"/>
-      <c r="Q43" s="9" t="n"/>
-      <c r="R43" s="9" t="n"/>
-      <c r="S43" s="9" t="n"/>
-      <c r="T43" s="22" t="n"/>
+      <c r="L43" s="9" t="n"/>
+      <c r="M43" s="9" t="n"/>
+      <c r="N43" s="9" t="n"/>
+      <c r="O43" s="9" t="n"/>
+      <c r="P43" s="22" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="12" t="n">
@@ -3529,15 +3335,11 @@
       </c>
       <c r="J44" s="13" t="n"/>
       <c r="K44" s="14" t="inlineStr"/>
-      <c r="L44" s="15" t="n"/>
-      <c r="M44" s="15" t="n"/>
-      <c r="N44" s="15" t="n"/>
-      <c r="O44" s="15" t="n"/>
-      <c r="P44" s="13" t="n"/>
-      <c r="Q44" s="13" t="n"/>
-      <c r="R44" s="13" t="n"/>
-      <c r="S44" s="13" t="n"/>
-      <c r="T44" s="24" t="n"/>
+      <c r="L44" s="13" t="n"/>
+      <c r="M44" s="13" t="n"/>
+      <c r="N44" s="13" t="n"/>
+      <c r="O44" s="13" t="n"/>
+      <c r="P44" s="24" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="8" t="n">
@@ -3585,15 +3387,11 @@
       </c>
       <c r="J45" s="9" t="n"/>
       <c r="K45" s="10" t="inlineStr"/>
-      <c r="L45" s="11" t="n"/>
-      <c r="M45" s="11" t="n"/>
-      <c r="N45" s="11" t="n"/>
-      <c r="O45" s="11" t="n"/>
-      <c r="P45" s="9" t="n"/>
-      <c r="Q45" s="9" t="n"/>
-      <c r="R45" s="9" t="n"/>
-      <c r="S45" s="9" t="n"/>
-      <c r="T45" s="22" t="n"/>
+      <c r="L45" s="9" t="n"/>
+      <c r="M45" s="9" t="n"/>
+      <c r="N45" s="9" t="n"/>
+      <c r="O45" s="9" t="n"/>
+      <c r="P45" s="22" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="12" t="n">
@@ -3641,15 +3439,11 @@
       </c>
       <c r="J46" s="13" t="n"/>
       <c r="K46" s="14" t="inlineStr"/>
-      <c r="L46" s="15" t="n"/>
-      <c r="M46" s="15" t="n"/>
-      <c r="N46" s="15" t="n"/>
-      <c r="O46" s="15" t="n"/>
-      <c r="P46" s="13" t="n"/>
-      <c r="Q46" s="13" t="n"/>
-      <c r="R46" s="13" t="n"/>
-      <c r="S46" s="13" t="n"/>
-      <c r="T46" s="24" t="n"/>
+      <c r="L46" s="13" t="n"/>
+      <c r="M46" s="13" t="n"/>
+      <c r="N46" s="13" t="n"/>
+      <c r="O46" s="13" t="n"/>
+      <c r="P46" s="24" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="8" t="n">
@@ -3697,15 +3491,11 @@
       </c>
       <c r="J47" s="9" t="n"/>
       <c r="K47" s="10" t="inlineStr"/>
-      <c r="L47" s="11" t="n"/>
-      <c r="M47" s="11" t="n"/>
-      <c r="N47" s="11" t="n"/>
-      <c r="O47" s="11" t="n"/>
-      <c r="P47" s="9" t="n"/>
-      <c r="Q47" s="9" t="n"/>
-      <c r="R47" s="9" t="n"/>
-      <c r="S47" s="9" t="n"/>
-      <c r="T47" s="22" t="n"/>
+      <c r="L47" s="9" t="n"/>
+      <c r="M47" s="9" t="n"/>
+      <c r="N47" s="9" t="n"/>
+      <c r="O47" s="9" t="n"/>
+      <c r="P47" s="22" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="12" t="n">
@@ -3753,15 +3543,11 @@
       </c>
       <c r="J48" s="13" t="n"/>
       <c r="K48" s="14" t="inlineStr"/>
-      <c r="L48" s="15" t="n"/>
-      <c r="M48" s="15" t="n"/>
-      <c r="N48" s="15" t="n"/>
-      <c r="O48" s="15" t="n"/>
-      <c r="P48" s="13" t="n"/>
-      <c r="Q48" s="13" t="n"/>
-      <c r="R48" s="13" t="n"/>
-      <c r="S48" s="13" t="n"/>
-      <c r="T48" s="24" t="n"/>
+      <c r="L48" s="13" t="n"/>
+      <c r="M48" s="13" t="n"/>
+      <c r="N48" s="13" t="n"/>
+      <c r="O48" s="13" t="n"/>
+      <c r="P48" s="24" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="8" t="n">
@@ -3809,15 +3595,11 @@
       </c>
       <c r="J49" s="9" t="n"/>
       <c r="K49" s="10" t="inlineStr"/>
-      <c r="L49" s="11" t="n"/>
-      <c r="M49" s="11" t="n"/>
-      <c r="N49" s="11" t="n"/>
-      <c r="O49" s="11" t="n"/>
-      <c r="P49" s="9" t="n"/>
-      <c r="Q49" s="9" t="n"/>
-      <c r="R49" s="9" t="n"/>
-      <c r="S49" s="9" t="n"/>
-      <c r="T49" s="22" t="n"/>
+      <c r="L49" s="9" t="n"/>
+      <c r="M49" s="9" t="n"/>
+      <c r="N49" s="9" t="n"/>
+      <c r="O49" s="9" t="n"/>
+      <c r="P49" s="22" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="12" t="n">
@@ -3865,15 +3647,11 @@
       </c>
       <c r="J50" s="13" t="n"/>
       <c r="K50" s="14" t="inlineStr"/>
-      <c r="L50" s="15" t="n"/>
-      <c r="M50" s="15" t="n"/>
-      <c r="N50" s="15" t="n"/>
-      <c r="O50" s="15" t="n"/>
-      <c r="P50" s="13" t="n"/>
-      <c r="Q50" s="13" t="n"/>
-      <c r="R50" s="13" t="n"/>
-      <c r="S50" s="13" t="n"/>
-      <c r="T50" s="24" t="n"/>
+      <c r="L50" s="13" t="n"/>
+      <c r="M50" s="13" t="n"/>
+      <c r="N50" s="13" t="n"/>
+      <c r="O50" s="13" t="n"/>
+      <c r="P50" s="24" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="8" t="n">
@@ -3921,15 +3699,11 @@
       </c>
       <c r="J51" s="9" t="n"/>
       <c r="K51" s="10" t="inlineStr"/>
-      <c r="L51" s="11" t="n"/>
-      <c r="M51" s="11" t="n"/>
-      <c r="N51" s="11" t="n"/>
-      <c r="O51" s="11" t="n"/>
-      <c r="P51" s="9" t="n"/>
-      <c r="Q51" s="9" t="n"/>
-      <c r="R51" s="9" t="n"/>
-      <c r="S51" s="9" t="n"/>
-      <c r="T51" s="22" t="n"/>
+      <c r="L51" s="9" t="n"/>
+      <c r="M51" s="9" t="n"/>
+      <c r="N51" s="9" t="n"/>
+      <c r="O51" s="9" t="n"/>
+      <c r="P51" s="22" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="12" t="n">
@@ -3977,15 +3751,11 @@
       </c>
       <c r="J52" s="13" t="n"/>
       <c r="K52" s="14" t="inlineStr"/>
-      <c r="L52" s="15" t="n"/>
-      <c r="M52" s="15" t="n"/>
-      <c r="N52" s="15" t="n"/>
-      <c r="O52" s="15" t="n"/>
-      <c r="P52" s="13" t="n"/>
-      <c r="Q52" s="13" t="n"/>
-      <c r="R52" s="13" t="n"/>
-      <c r="S52" s="13" t="n"/>
-      <c r="T52" s="24" t="n"/>
+      <c r="L52" s="13" t="n"/>
+      <c r="M52" s="13" t="n"/>
+      <c r="N52" s="13" t="n"/>
+      <c r="O52" s="13" t="n"/>
+      <c r="P52" s="24" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="8" t="n">
@@ -4033,15 +3803,11 @@
       </c>
       <c r="J53" s="9" t="n"/>
       <c r="K53" s="10" t="inlineStr"/>
-      <c r="L53" s="11" t="n"/>
-      <c r="M53" s="11" t="n"/>
-      <c r="N53" s="11" t="n"/>
-      <c r="O53" s="11" t="n"/>
-      <c r="P53" s="9" t="n"/>
-      <c r="Q53" s="9" t="n"/>
-      <c r="R53" s="9" t="n"/>
-      <c r="S53" s="9" t="n"/>
-      <c r="T53" s="22" t="n"/>
+      <c r="L53" s="9" t="n"/>
+      <c r="M53" s="9" t="n"/>
+      <c r="N53" s="9" t="n"/>
+      <c r="O53" s="9" t="n"/>
+      <c r="P53" s="22" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="12" t="n">
@@ -4089,15 +3855,11 @@
       </c>
       <c r="J54" s="13" t="n"/>
       <c r="K54" s="14" t="inlineStr"/>
-      <c r="L54" s="15" t="n"/>
-      <c r="M54" s="15" t="n"/>
-      <c r="N54" s="15" t="n"/>
-      <c r="O54" s="15" t="n"/>
-      <c r="P54" s="13" t="n"/>
-      <c r="Q54" s="13" t="n"/>
-      <c r="R54" s="13" t="n"/>
-      <c r="S54" s="13" t="n"/>
-      <c r="T54" s="24" t="n"/>
+      <c r="L54" s="13" t="n"/>
+      <c r="M54" s="13" t="n"/>
+      <c r="N54" s="13" t="n"/>
+      <c r="O54" s="13" t="n"/>
+      <c r="P54" s="24" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="8" t="n">
@@ -4145,15 +3907,11 @@
       </c>
       <c r="J55" s="9" t="n"/>
       <c r="K55" s="10" t="inlineStr"/>
-      <c r="L55" s="11" t="n"/>
-      <c r="M55" s="11" t="n"/>
-      <c r="N55" s="11" t="n"/>
-      <c r="O55" s="11" t="n"/>
-      <c r="P55" s="9" t="n"/>
-      <c r="Q55" s="9" t="n"/>
-      <c r="R55" s="9" t="n"/>
-      <c r="S55" s="9" t="n"/>
-      <c r="T55" s="22" t="n"/>
+      <c r="L55" s="9" t="n"/>
+      <c r="M55" s="9" t="n"/>
+      <c r="N55" s="9" t="n"/>
+      <c r="O55" s="9" t="n"/>
+      <c r="P55" s="22" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="12" t="n">
@@ -4201,15 +3959,11 @@
       </c>
       <c r="J56" s="13" t="n"/>
       <c r="K56" s="14" t="inlineStr"/>
-      <c r="L56" s="15" t="n"/>
-      <c r="M56" s="15" t="n"/>
-      <c r="N56" s="15" t="n"/>
-      <c r="O56" s="15" t="n"/>
-      <c r="P56" s="13" t="n"/>
-      <c r="Q56" s="13" t="n"/>
-      <c r="R56" s="13" t="n"/>
-      <c r="S56" s="13" t="n"/>
-      <c r="T56" s="24" t="n"/>
+      <c r="L56" s="13" t="n"/>
+      <c r="M56" s="13" t="n"/>
+      <c r="N56" s="13" t="n"/>
+      <c r="O56" s="13" t="n"/>
+      <c r="P56" s="24" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="8" t="n">
@@ -4257,15 +4011,11 @@
       </c>
       <c r="J57" s="9" t="n"/>
       <c r="K57" s="10" t="inlineStr"/>
-      <c r="L57" s="11" t="n"/>
-      <c r="M57" s="11" t="n"/>
-      <c r="N57" s="11" t="n"/>
-      <c r="O57" s="11" t="n"/>
-      <c r="P57" s="9" t="n"/>
-      <c r="Q57" s="9" t="n"/>
-      <c r="R57" s="9" t="n"/>
-      <c r="S57" s="9" t="n"/>
-      <c r="T57" s="22" t="n"/>
+      <c r="L57" s="9" t="n"/>
+      <c r="M57" s="9" t="n"/>
+      <c r="N57" s="9" t="n"/>
+      <c r="O57" s="9" t="n"/>
+      <c r="P57" s="22" t="n"/>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="12" t="n">
@@ -4313,15 +4063,11 @@
       </c>
       <c r="J58" s="13" t="n"/>
       <c r="K58" s="14" t="inlineStr"/>
-      <c r="L58" s="15" t="n"/>
-      <c r="M58" s="15" t="n"/>
-      <c r="N58" s="15" t="n"/>
-      <c r="O58" s="15" t="n"/>
-      <c r="P58" s="13" t="n"/>
-      <c r="Q58" s="13" t="n"/>
-      <c r="R58" s="13" t="n"/>
-      <c r="S58" s="13" t="n"/>
-      <c r="T58" s="24" t="n"/>
+      <c r="L58" s="13" t="n"/>
+      <c r="M58" s="13" t="n"/>
+      <c r="N58" s="13" t="n"/>
+      <c r="O58" s="13" t="n"/>
+      <c r="P58" s="24" t="n"/>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="8" t="n">
@@ -4369,15 +4115,11 @@
       </c>
       <c r="J59" s="9" t="n"/>
       <c r="K59" s="10" t="inlineStr"/>
-      <c r="L59" s="11" t="n"/>
-      <c r="M59" s="11" t="n"/>
-      <c r="N59" s="11" t="n"/>
-      <c r="O59" s="11" t="n"/>
-      <c r="P59" s="9" t="n"/>
-      <c r="Q59" s="9" t="n"/>
-      <c r="R59" s="9" t="n"/>
-      <c r="S59" s="9" t="n"/>
-      <c r="T59" s="22" t="n"/>
+      <c r="L59" s="9" t="n"/>
+      <c r="M59" s="9" t="n"/>
+      <c r="N59" s="9" t="n"/>
+      <c r="O59" s="9" t="n"/>
+      <c r="P59" s="22" t="n"/>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="12" t="n">
@@ -4425,15 +4167,11 @@
       </c>
       <c r="J60" s="13" t="n"/>
       <c r="K60" s="14" t="inlineStr"/>
-      <c r="L60" s="15" t="n"/>
-      <c r="M60" s="15" t="n"/>
-      <c r="N60" s="15" t="n"/>
-      <c r="O60" s="15" t="n"/>
-      <c r="P60" s="13" t="n"/>
-      <c r="Q60" s="13" t="n"/>
-      <c r="R60" s="13" t="n"/>
-      <c r="S60" s="13" t="n"/>
-      <c r="T60" s="24" t="n"/>
+      <c r="L60" s="13" t="n"/>
+      <c r="M60" s="13" t="n"/>
+      <c r="N60" s="13" t="n"/>
+      <c r="O60" s="13" t="n"/>
+      <c r="P60" s="24" t="n"/>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="8" t="n">
@@ -4481,15 +4219,11 @@
       </c>
       <c r="J61" s="9" t="n"/>
       <c r="K61" s="10" t="inlineStr"/>
-      <c r="L61" s="11" t="n"/>
-      <c r="M61" s="11" t="n"/>
-      <c r="N61" s="11" t="n"/>
-      <c r="O61" s="11" t="n"/>
-      <c r="P61" s="9" t="n"/>
-      <c r="Q61" s="9" t="n"/>
-      <c r="R61" s="9" t="n"/>
-      <c r="S61" s="9" t="n"/>
-      <c r="T61" s="22" t="n"/>
+      <c r="L61" s="9" t="n"/>
+      <c r="M61" s="9" t="n"/>
+      <c r="N61" s="9" t="n"/>
+      <c r="O61" s="9" t="n"/>
+      <c r="P61" s="22" t="n"/>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="12" t="n">
@@ -4537,15 +4271,11 @@
       </c>
       <c r="J62" s="13" t="n"/>
       <c r="K62" s="14" t="inlineStr"/>
-      <c r="L62" s="15" t="n"/>
-      <c r="M62" s="15" t="n"/>
-      <c r="N62" s="15" t="n"/>
-      <c r="O62" s="15" t="n"/>
-      <c r="P62" s="13" t="n"/>
-      <c r="Q62" s="13" t="n"/>
-      <c r="R62" s="13" t="n"/>
-      <c r="S62" s="13" t="n"/>
-      <c r="T62" s="24" t="n"/>
+      <c r="L62" s="13" t="n"/>
+      <c r="M62" s="13" t="n"/>
+      <c r="N62" s="13" t="n"/>
+      <c r="O62" s="13" t="n"/>
+      <c r="P62" s="24" t="n"/>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="8" t="n">
@@ -4593,15 +4323,11 @@
       </c>
       <c r="J63" s="9" t="n"/>
       <c r="K63" s="10" t="inlineStr"/>
-      <c r="L63" s="11" t="n"/>
-      <c r="M63" s="11" t="n"/>
-      <c r="N63" s="11" t="n"/>
-      <c r="O63" s="11" t="n"/>
-      <c r="P63" s="9" t="n"/>
-      <c r="Q63" s="9" t="n"/>
-      <c r="R63" s="9" t="n"/>
-      <c r="S63" s="9" t="n"/>
-      <c r="T63" s="22" t="n"/>
+      <c r="L63" s="9" t="n"/>
+      <c r="M63" s="9" t="n"/>
+      <c r="N63" s="9" t="n"/>
+      <c r="O63" s="9" t="n"/>
+      <c r="P63" s="22" t="n"/>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="12" t="n">
@@ -4649,15 +4375,11 @@
       </c>
       <c r="J64" s="13" t="n"/>
       <c r="K64" s="14" t="inlineStr"/>
-      <c r="L64" s="15" t="n"/>
-      <c r="M64" s="15" t="n"/>
-      <c r="N64" s="15" t="n"/>
-      <c r="O64" s="15" t="n"/>
-      <c r="P64" s="13" t="n"/>
-      <c r="Q64" s="13" t="n"/>
-      <c r="R64" s="13" t="n"/>
-      <c r="S64" s="13" t="n"/>
-      <c r="T64" s="24" t="n"/>
+      <c r="L64" s="13" t="n"/>
+      <c r="M64" s="13" t="n"/>
+      <c r="N64" s="13" t="n"/>
+      <c r="O64" s="13" t="n"/>
+      <c r="P64" s="24" t="n"/>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="8" t="n">
@@ -4705,15 +4427,11 @@
       </c>
       <c r="J65" s="9" t="n"/>
       <c r="K65" s="10" t="inlineStr"/>
-      <c r="L65" s="11" t="n"/>
-      <c r="M65" s="11" t="n"/>
-      <c r="N65" s="11" t="n"/>
-      <c r="O65" s="11" t="n"/>
-      <c r="P65" s="9" t="n"/>
-      <c r="Q65" s="9" t="n"/>
-      <c r="R65" s="9" t="n"/>
-      <c r="S65" s="9" t="n"/>
-      <c r="T65" s="22" t="n"/>
+      <c r="L65" s="9" t="n"/>
+      <c r="M65" s="9" t="n"/>
+      <c r="N65" s="9" t="n"/>
+      <c r="O65" s="9" t="n"/>
+      <c r="P65" s="22" t="n"/>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="12" t="n">
@@ -4761,15 +4479,11 @@
       </c>
       <c r="J66" s="13" t="n"/>
       <c r="K66" s="14" t="inlineStr"/>
-      <c r="L66" s="15" t="n"/>
-      <c r="M66" s="15" t="n"/>
-      <c r="N66" s="15" t="n"/>
-      <c r="O66" s="15" t="n"/>
-      <c r="P66" s="13" t="n"/>
-      <c r="Q66" s="13" t="n"/>
-      <c r="R66" s="13" t="n"/>
-      <c r="S66" s="13" t="n"/>
-      <c r="T66" s="24" t="n"/>
+      <c r="L66" s="13" t="n"/>
+      <c r="M66" s="13" t="n"/>
+      <c r="N66" s="13" t="n"/>
+      <c r="O66" s="13" t="n"/>
+      <c r="P66" s="24" t="n"/>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="8" t="n">
@@ -4817,15 +4531,11 @@
       </c>
       <c r="J67" s="9" t="n"/>
       <c r="K67" s="10" t="inlineStr"/>
-      <c r="L67" s="11" t="n"/>
-      <c r="M67" s="11" t="n"/>
-      <c r="N67" s="11" t="n"/>
-      <c r="O67" s="11" t="n"/>
-      <c r="P67" s="9" t="n"/>
-      <c r="Q67" s="9" t="n"/>
-      <c r="R67" s="9" t="n"/>
-      <c r="S67" s="9" t="n"/>
-      <c r="T67" s="22" t="n"/>
+      <c r="L67" s="9" t="n"/>
+      <c r="M67" s="9" t="n"/>
+      <c r="N67" s="9" t="n"/>
+      <c r="O67" s="9" t="n"/>
+      <c r="P67" s="22" t="n"/>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="12" t="n">
@@ -4873,15 +4583,11 @@
       </c>
       <c r="J68" s="13" t="n"/>
       <c r="K68" s="14" t="inlineStr"/>
-      <c r="L68" s="15" t="n"/>
-      <c r="M68" s="15" t="n"/>
-      <c r="N68" s="15" t="n"/>
-      <c r="O68" s="15" t="n"/>
-      <c r="P68" s="13" t="n"/>
-      <c r="Q68" s="13" t="n"/>
-      <c r="R68" s="13" t="n"/>
-      <c r="S68" s="13" t="n"/>
-      <c r="T68" s="24" t="n"/>
+      <c r="L68" s="13" t="n"/>
+      <c r="M68" s="13" t="n"/>
+      <c r="N68" s="13" t="n"/>
+      <c r="O68" s="13" t="n"/>
+      <c r="P68" s="24" t="n"/>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="8" t="n">
@@ -4929,15 +4635,11 @@
       </c>
       <c r="J69" s="9" t="n"/>
       <c r="K69" s="10" t="inlineStr"/>
-      <c r="L69" s="11" t="n"/>
-      <c r="M69" s="11" t="n"/>
-      <c r="N69" s="11" t="n"/>
-      <c r="O69" s="11" t="n"/>
-      <c r="P69" s="9" t="n"/>
-      <c r="Q69" s="9" t="n"/>
-      <c r="R69" s="9" t="n"/>
-      <c r="S69" s="9" t="n"/>
-      <c r="T69" s="22" t="n"/>
+      <c r="L69" s="9" t="n"/>
+      <c r="M69" s="9" t="n"/>
+      <c r="N69" s="9" t="n"/>
+      <c r="O69" s="9" t="n"/>
+      <c r="P69" s="22" t="n"/>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="12" t="n">
@@ -4985,15 +4687,11 @@
       </c>
       <c r="J70" s="13" t="n"/>
       <c r="K70" s="14" t="inlineStr"/>
-      <c r="L70" s="15" t="n"/>
-      <c r="M70" s="15" t="n"/>
-      <c r="N70" s="15" t="n"/>
-      <c r="O70" s="15" t="n"/>
-      <c r="P70" s="13" t="n"/>
-      <c r="Q70" s="13" t="n"/>
-      <c r="R70" s="13" t="n"/>
-      <c r="S70" s="13" t="n"/>
-      <c r="T70" s="24" t="n"/>
+      <c r="L70" s="13" t="n"/>
+      <c r="M70" s="13" t="n"/>
+      <c r="N70" s="13" t="n"/>
+      <c r="O70" s="13" t="n"/>
+      <c r="P70" s="24" t="n"/>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="8" t="n">
@@ -5041,15 +4739,11 @@
       </c>
       <c r="J71" s="9" t="n"/>
       <c r="K71" s="10" t="inlineStr"/>
-      <c r="L71" s="11" t="n"/>
-      <c r="M71" s="11" t="n"/>
-      <c r="N71" s="11" t="n"/>
-      <c r="O71" s="11" t="n"/>
-      <c r="P71" s="9" t="n"/>
-      <c r="Q71" s="9" t="n"/>
-      <c r="R71" s="9" t="n"/>
-      <c r="S71" s="9" t="n"/>
-      <c r="T71" s="22" t="n"/>
+      <c r="L71" s="9" t="n"/>
+      <c r="M71" s="9" t="n"/>
+      <c r="N71" s="9" t="n"/>
+      <c r="O71" s="9" t="n"/>
+      <c r="P71" s="22" t="n"/>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="12" t="n">
@@ -5097,15 +4791,11 @@
       </c>
       <c r="J72" s="13" t="n"/>
       <c r="K72" s="14" t="inlineStr"/>
-      <c r="L72" s="15" t="n"/>
-      <c r="M72" s="15" t="n"/>
-      <c r="N72" s="15" t="n"/>
-      <c r="O72" s="15" t="n"/>
-      <c r="P72" s="13" t="n"/>
-      <c r="Q72" s="13" t="n"/>
-      <c r="R72" s="13" t="n"/>
-      <c r="S72" s="13" t="n"/>
-      <c r="T72" s="24" t="n"/>
+      <c r="L72" s="13" t="n"/>
+      <c r="M72" s="13" t="n"/>
+      <c r="N72" s="13" t="n"/>
+      <c r="O72" s="13" t="n"/>
+      <c r="P72" s="24" t="n"/>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="8" t="n">
@@ -5153,15 +4843,11 @@
       </c>
       <c r="J73" s="9" t="n"/>
       <c r="K73" s="10" t="inlineStr"/>
-      <c r="L73" s="11" t="n"/>
-      <c r="M73" s="11" t="n"/>
-      <c r="N73" s="11" t="n"/>
-      <c r="O73" s="11" t="n"/>
-      <c r="P73" s="9" t="n"/>
-      <c r="Q73" s="9" t="n"/>
-      <c r="R73" s="9" t="n"/>
-      <c r="S73" s="9" t="n"/>
-      <c r="T73" s="22" t="n"/>
+      <c r="L73" s="9" t="n"/>
+      <c r="M73" s="9" t="n"/>
+      <c r="N73" s="9" t="n"/>
+      <c r="O73" s="9" t="n"/>
+      <c r="P73" s="22" t="n"/>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="12" t="n">
@@ -5209,15 +4895,11 @@
       </c>
       <c r="J74" s="13" t="n"/>
       <c r="K74" s="14" t="inlineStr"/>
-      <c r="L74" s="15" t="n"/>
-      <c r="M74" s="15" t="n"/>
-      <c r="N74" s="15" t="n"/>
-      <c r="O74" s="15" t="n"/>
-      <c r="P74" s="13" t="n"/>
-      <c r="Q74" s="13" t="n"/>
-      <c r="R74" s="13" t="n"/>
-      <c r="S74" s="13" t="n"/>
-      <c r="T74" s="24" t="n"/>
+      <c r="L74" s="13" t="n"/>
+      <c r="M74" s="13" t="n"/>
+      <c r="N74" s="13" t="n"/>
+      <c r="O74" s="13" t="n"/>
+      <c r="P74" s="24" t="n"/>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="8" t="n">
@@ -5265,15 +4947,11 @@
       </c>
       <c r="J75" s="9" t="n"/>
       <c r="K75" s="10" t="inlineStr"/>
-      <c r="L75" s="11" t="n"/>
-      <c r="M75" s="11" t="n"/>
-      <c r="N75" s="11" t="n"/>
-      <c r="O75" s="11" t="n"/>
-      <c r="P75" s="9" t="n"/>
-      <c r="Q75" s="9" t="n"/>
-      <c r="R75" s="9" t="n"/>
-      <c r="S75" s="9" t="n"/>
-      <c r="T75" s="22" t="n"/>
+      <c r="L75" s="9" t="n"/>
+      <c r="M75" s="9" t="n"/>
+      <c r="N75" s="9" t="n"/>
+      <c r="O75" s="9" t="n"/>
+      <c r="P75" s="22" t="n"/>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="12" t="n">
@@ -5321,15 +4999,11 @@
       </c>
       <c r="J76" s="13" t="n"/>
       <c r="K76" s="14" t="inlineStr"/>
-      <c r="L76" s="15" t="n"/>
-      <c r="M76" s="15" t="n"/>
-      <c r="N76" s="15" t="n"/>
-      <c r="O76" s="15" t="n"/>
-      <c r="P76" s="13" t="n"/>
-      <c r="Q76" s="13" t="n"/>
-      <c r="R76" s="13" t="n"/>
-      <c r="S76" s="13" t="n"/>
-      <c r="T76" s="24" t="n"/>
+      <c r="L76" s="13" t="n"/>
+      <c r="M76" s="13" t="n"/>
+      <c r="N76" s="13" t="n"/>
+      <c r="O76" s="13" t="n"/>
+      <c r="P76" s="24" t="n"/>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="8" t="n">
@@ -5377,15 +5051,11 @@
       </c>
       <c r="J77" s="9" t="n"/>
       <c r="K77" s="10" t="inlineStr"/>
-      <c r="L77" s="11" t="n"/>
-      <c r="M77" s="11" t="n"/>
-      <c r="N77" s="11" t="n"/>
-      <c r="O77" s="11" t="n"/>
-      <c r="P77" s="9" t="n"/>
-      <c r="Q77" s="9" t="n"/>
-      <c r="R77" s="9" t="n"/>
-      <c r="S77" s="9" t="n"/>
-      <c r="T77" s="22" t="n"/>
+      <c r="L77" s="9" t="n"/>
+      <c r="M77" s="9" t="n"/>
+      <c r="N77" s="9" t="n"/>
+      <c r="O77" s="9" t="n"/>
+      <c r="P77" s="22" t="n"/>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="12" t="n">
@@ -5433,15 +5103,11 @@
       </c>
       <c r="J78" s="13" t="n"/>
       <c r="K78" s="14" t="inlineStr"/>
-      <c r="L78" s="15" t="n"/>
-      <c r="M78" s="15" t="n"/>
-      <c r="N78" s="15" t="n"/>
-      <c r="O78" s="15" t="n"/>
-      <c r="P78" s="13" t="n"/>
-      <c r="Q78" s="13" t="n"/>
-      <c r="R78" s="13" t="n"/>
-      <c r="S78" s="13" t="n"/>
-      <c r="T78" s="24" t="n"/>
+      <c r="L78" s="13" t="n"/>
+      <c r="M78" s="13" t="n"/>
+      <c r="N78" s="13" t="n"/>
+      <c r="O78" s="13" t="n"/>
+      <c r="P78" s="24" t="n"/>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="8" t="n">
@@ -5489,15 +5155,11 @@
       </c>
       <c r="J79" s="9" t="n"/>
       <c r="K79" s="10" t="inlineStr"/>
-      <c r="L79" s="11" t="n"/>
-      <c r="M79" s="11" t="n"/>
-      <c r="N79" s="11" t="n"/>
-      <c r="O79" s="11" t="n"/>
-      <c r="P79" s="9" t="n"/>
-      <c r="Q79" s="9" t="n"/>
-      <c r="R79" s="9" t="n"/>
-      <c r="S79" s="9" t="n"/>
-      <c r="T79" s="22" t="n"/>
+      <c r="L79" s="9" t="n"/>
+      <c r="M79" s="9" t="n"/>
+      <c r="N79" s="9" t="n"/>
+      <c r="O79" s="9" t="n"/>
+      <c r="P79" s="22" t="n"/>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="12" t="n">
@@ -5545,15 +5207,11 @@
       </c>
       <c r="J80" s="13" t="n"/>
       <c r="K80" s="14" t="inlineStr"/>
-      <c r="L80" s="15" t="n"/>
-      <c r="M80" s="15" t="n"/>
-      <c r="N80" s="15" t="n"/>
-      <c r="O80" s="15" t="n"/>
-      <c r="P80" s="13" t="n"/>
-      <c r="Q80" s="13" t="n"/>
-      <c r="R80" s="13" t="n"/>
-      <c r="S80" s="13" t="n"/>
-      <c r="T80" s="24" t="n"/>
+      <c r="L80" s="13" t="n"/>
+      <c r="M80" s="13" t="n"/>
+      <c r="N80" s="13" t="n"/>
+      <c r="O80" s="13" t="n"/>
+      <c r="P80" s="24" t="n"/>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="8" t="n">
@@ -5601,15 +5259,11 @@
       </c>
       <c r="J81" s="9" t="n"/>
       <c r="K81" s="10" t="inlineStr"/>
-      <c r="L81" s="11" t="n"/>
-      <c r="M81" s="11" t="n"/>
-      <c r="N81" s="11" t="n"/>
-      <c r="O81" s="11" t="n"/>
-      <c r="P81" s="9" t="n"/>
-      <c r="Q81" s="9" t="n"/>
-      <c r="R81" s="9" t="n"/>
-      <c r="S81" s="9" t="n"/>
-      <c r="T81" s="22" t="n"/>
+      <c r="L81" s="9" t="n"/>
+      <c r="M81" s="9" t="n"/>
+      <c r="N81" s="9" t="n"/>
+      <c r="O81" s="9" t="n"/>
+      <c r="P81" s="22" t="n"/>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="12" t="n">
@@ -5657,15 +5311,11 @@
       </c>
       <c r="J82" s="13" t="n"/>
       <c r="K82" s="14" t="inlineStr"/>
-      <c r="L82" s="15" t="n"/>
-      <c r="M82" s="15" t="n"/>
-      <c r="N82" s="15" t="n"/>
-      <c r="O82" s="15" t="n"/>
-      <c r="P82" s="13" t="n"/>
-      <c r="Q82" s="13" t="n"/>
-      <c r="R82" s="13" t="n"/>
-      <c r="S82" s="13" t="n"/>
-      <c r="T82" s="24" t="n"/>
+      <c r="L82" s="13" t="n"/>
+      <c r="M82" s="13" t="n"/>
+      <c r="N82" s="13" t="n"/>
+      <c r="O82" s="13" t="n"/>
+      <c r="P82" s="24" t="n"/>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="8" t="n">
@@ -5713,15 +5363,11 @@
       </c>
       <c r="J83" s="9" t="n"/>
       <c r="K83" s="10" t="inlineStr"/>
-      <c r="L83" s="11" t="n"/>
-      <c r="M83" s="11" t="n"/>
-      <c r="N83" s="11" t="n"/>
-      <c r="O83" s="11" t="n"/>
-      <c r="P83" s="9" t="n"/>
-      <c r="Q83" s="9" t="n"/>
-      <c r="R83" s="9" t="n"/>
-      <c r="S83" s="9" t="n"/>
-      <c r="T83" s="22" t="n"/>
+      <c r="L83" s="9" t="n"/>
+      <c r="M83" s="9" t="n"/>
+      <c r="N83" s="9" t="n"/>
+      <c r="O83" s="9" t="n"/>
+      <c r="P83" s="22" t="n"/>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="12" t="n">
@@ -5769,15 +5415,11 @@
       </c>
       <c r="J84" s="13" t="n"/>
       <c r="K84" s="14" t="inlineStr"/>
-      <c r="L84" s="15" t="n"/>
-      <c r="M84" s="15" t="n"/>
-      <c r="N84" s="15" t="n"/>
-      <c r="O84" s="15" t="n"/>
-      <c r="P84" s="13" t="n"/>
-      <c r="Q84" s="13" t="n"/>
-      <c r="R84" s="13" t="n"/>
-      <c r="S84" s="13" t="n"/>
-      <c r="T84" s="24" t="n"/>
+      <c r="L84" s="13" t="n"/>
+      <c r="M84" s="13" t="n"/>
+      <c r="N84" s="13" t="n"/>
+      <c r="O84" s="13" t="n"/>
+      <c r="P84" s="24" t="n"/>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="8" t="n">
@@ -5825,15 +5467,11 @@
       </c>
       <c r="J85" s="9" t="n"/>
       <c r="K85" s="10" t="inlineStr"/>
-      <c r="L85" s="11" t="n"/>
-      <c r="M85" s="11" t="n"/>
-      <c r="N85" s="11" t="n"/>
-      <c r="O85" s="11" t="n"/>
-      <c r="P85" s="9" t="n"/>
-      <c r="Q85" s="9" t="n"/>
-      <c r="R85" s="9" t="n"/>
-      <c r="S85" s="9" t="n"/>
-      <c r="T85" s="22" t="n"/>
+      <c r="L85" s="9" t="n"/>
+      <c r="M85" s="9" t="n"/>
+      <c r="N85" s="9" t="n"/>
+      <c r="O85" s="9" t="n"/>
+      <c r="P85" s="22" t="n"/>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="12" t="n">
@@ -5881,15 +5519,11 @@
       </c>
       <c r="J86" s="13" t="n"/>
       <c r="K86" s="14" t="inlineStr"/>
-      <c r="L86" s="15" t="n"/>
-      <c r="M86" s="15" t="n"/>
-      <c r="N86" s="15" t="n"/>
-      <c r="O86" s="15" t="n"/>
-      <c r="P86" s="13" t="n"/>
-      <c r="Q86" s="13" t="n"/>
-      <c r="R86" s="13" t="n"/>
-      <c r="S86" s="13" t="n"/>
-      <c r="T86" s="24" t="n"/>
+      <c r="L86" s="13" t="n"/>
+      <c r="M86" s="13" t="n"/>
+      <c r="N86" s="13" t="n"/>
+      <c r="O86" s="13" t="n"/>
+      <c r="P86" s="24" t="n"/>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="8" t="n">
@@ -5937,15 +5571,11 @@
       </c>
       <c r="J87" s="9" t="n"/>
       <c r="K87" s="10" t="inlineStr"/>
-      <c r="L87" s="11" t="n"/>
-      <c r="M87" s="11" t="n"/>
-      <c r="N87" s="11" t="n"/>
-      <c r="O87" s="11" t="n"/>
-      <c r="P87" s="9" t="n"/>
-      <c r="Q87" s="9" t="n"/>
-      <c r="R87" s="9" t="n"/>
-      <c r="S87" s="9" t="n"/>
-      <c r="T87" s="22" t="n"/>
+      <c r="L87" s="9" t="n"/>
+      <c r="M87" s="9" t="n"/>
+      <c r="N87" s="9" t="n"/>
+      <c r="O87" s="9" t="n"/>
+      <c r="P87" s="22" t="n"/>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="12" t="n">
@@ -5993,15 +5623,11 @@
       </c>
       <c r="J88" s="13" t="n"/>
       <c r="K88" s="14" t="inlineStr"/>
-      <c r="L88" s="15" t="n"/>
-      <c r="M88" s="15" t="n"/>
-      <c r="N88" s="15" t="n"/>
-      <c r="O88" s="15" t="n"/>
-      <c r="P88" s="13" t="n"/>
-      <c r="Q88" s="13" t="n"/>
-      <c r="R88" s="13" t="n"/>
-      <c r="S88" s="13" t="n"/>
-      <c r="T88" s="24" t="n"/>
+      <c r="L88" s="13" t="n"/>
+      <c r="M88" s="13" t="n"/>
+      <c r="N88" s="13" t="n"/>
+      <c r="O88" s="13" t="n"/>
+      <c r="P88" s="24" t="n"/>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="8" t="n">
@@ -6049,15 +5675,11 @@
       </c>
       <c r="J89" s="9" t="n"/>
       <c r="K89" s="10" t="inlineStr"/>
-      <c r="L89" s="11" t="n"/>
-      <c r="M89" s="11" t="n"/>
-      <c r="N89" s="11" t="n"/>
-      <c r="O89" s="11" t="n"/>
-      <c r="P89" s="9" t="n"/>
-      <c r="Q89" s="9" t="n"/>
-      <c r="R89" s="9" t="n"/>
-      <c r="S89" s="9" t="n"/>
-      <c r="T89" s="22" t="n"/>
+      <c r="L89" s="9" t="n"/>
+      <c r="M89" s="9" t="n"/>
+      <c r="N89" s="9" t="n"/>
+      <c r="O89" s="9" t="n"/>
+      <c r="P89" s="22" t="n"/>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="12" t="n">
@@ -6105,15 +5727,11 @@
       </c>
       <c r="J90" s="13" t="n"/>
       <c r="K90" s="14" t="inlineStr"/>
-      <c r="L90" s="15" t="n"/>
-      <c r="M90" s="15" t="n"/>
-      <c r="N90" s="15" t="n"/>
-      <c r="O90" s="15" t="n"/>
-      <c r="P90" s="13" t="n"/>
-      <c r="Q90" s="13" t="n"/>
-      <c r="R90" s="13" t="n"/>
-      <c r="S90" s="13" t="n"/>
-      <c r="T90" s="24" t="n"/>
+      <c r="L90" s="13" t="n"/>
+      <c r="M90" s="13" t="n"/>
+      <c r="N90" s="13" t="n"/>
+      <c r="O90" s="13" t="n"/>
+      <c r="P90" s="24" t="n"/>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="8" t="n">
@@ -6161,15 +5779,11 @@
       </c>
       <c r="J91" s="9" t="n"/>
       <c r="K91" s="10" t="inlineStr"/>
-      <c r="L91" s="11" t="n"/>
-      <c r="M91" s="11" t="n"/>
-      <c r="N91" s="11" t="n"/>
-      <c r="O91" s="11" t="n"/>
-      <c r="P91" s="9" t="n"/>
-      <c r="Q91" s="9" t="n"/>
-      <c r="R91" s="9" t="n"/>
-      <c r="S91" s="9" t="n"/>
-      <c r="T91" s="22" t="n"/>
+      <c r="L91" s="9" t="n"/>
+      <c r="M91" s="9" t="n"/>
+      <c r="N91" s="9" t="n"/>
+      <c r="O91" s="9" t="n"/>
+      <c r="P91" s="22" t="n"/>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="12" t="n">
@@ -6217,15 +5831,11 @@
       </c>
       <c r="J92" s="13" t="n"/>
       <c r="K92" s="14" t="inlineStr"/>
-      <c r="L92" s="15" t="n"/>
-      <c r="M92" s="15" t="n"/>
-      <c r="N92" s="15" t="n"/>
-      <c r="O92" s="15" t="n"/>
-      <c r="P92" s="13" t="n"/>
-      <c r="Q92" s="13" t="n"/>
-      <c r="R92" s="13" t="n"/>
-      <c r="S92" s="13" t="n"/>
-      <c r="T92" s="24" t="n"/>
+      <c r="L92" s="13" t="n"/>
+      <c r="M92" s="13" t="n"/>
+      <c r="N92" s="13" t="n"/>
+      <c r="O92" s="13" t="n"/>
+      <c r="P92" s="24" t="n"/>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="8" t="n">
@@ -6273,15 +5883,11 @@
       </c>
       <c r="J93" s="9" t="n"/>
       <c r="K93" s="10" t="inlineStr"/>
-      <c r="L93" s="11" t="n"/>
-      <c r="M93" s="11" t="n"/>
-      <c r="N93" s="11" t="n"/>
-      <c r="O93" s="11" t="n"/>
-      <c r="P93" s="9" t="n"/>
-      <c r="Q93" s="9" t="n"/>
-      <c r="R93" s="9" t="n"/>
-      <c r="S93" s="9" t="n"/>
-      <c r="T93" s="22" t="n"/>
+      <c r="L93" s="9" t="n"/>
+      <c r="M93" s="9" t="n"/>
+      <c r="N93" s="9" t="n"/>
+      <c r="O93" s="9" t="n"/>
+      <c r="P93" s="22" t="n"/>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="12" t="n">
@@ -6329,15 +5935,11 @@
       </c>
       <c r="J94" s="13" t="n"/>
       <c r="K94" s="14" t="inlineStr"/>
-      <c r="L94" s="15" t="n"/>
-      <c r="M94" s="15" t="n"/>
-      <c r="N94" s="15" t="n"/>
-      <c r="O94" s="15" t="n"/>
-      <c r="P94" s="13" t="n"/>
-      <c r="Q94" s="13" t="n"/>
-      <c r="R94" s="13" t="n"/>
-      <c r="S94" s="13" t="n"/>
-      <c r="T94" s="24" t="n"/>
+      <c r="L94" s="13" t="n"/>
+      <c r="M94" s="13" t="n"/>
+      <c r="N94" s="13" t="n"/>
+      <c r="O94" s="13" t="n"/>
+      <c r="P94" s="24" t="n"/>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="8" t="n">
@@ -6385,15 +5987,11 @@
       </c>
       <c r="J95" s="9" t="n"/>
       <c r="K95" s="10" t="inlineStr"/>
-      <c r="L95" s="11" t="n"/>
-      <c r="M95" s="11" t="n"/>
-      <c r="N95" s="11" t="n"/>
-      <c r="O95" s="11" t="n"/>
-      <c r="P95" s="9" t="n"/>
-      <c r="Q95" s="9" t="n"/>
-      <c r="R95" s="9" t="n"/>
-      <c r="S95" s="9" t="n"/>
-      <c r="T95" s="22" t="n"/>
+      <c r="L95" s="9" t="n"/>
+      <c r="M95" s="9" t="n"/>
+      <c r="N95" s="9" t="n"/>
+      <c r="O95" s="9" t="n"/>
+      <c r="P95" s="22" t="n"/>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="12" t="n">
@@ -6441,15 +6039,11 @@
       </c>
       <c r="J96" s="13" t="n"/>
       <c r="K96" s="14" t="inlineStr"/>
-      <c r="L96" s="15" t="n"/>
-      <c r="M96" s="15" t="n"/>
-      <c r="N96" s="15" t="n"/>
-      <c r="O96" s="15" t="n"/>
-      <c r="P96" s="13" t="n"/>
-      <c r="Q96" s="13" t="n"/>
-      <c r="R96" s="13" t="n"/>
-      <c r="S96" s="13" t="n"/>
-      <c r="T96" s="24" t="n"/>
+      <c r="L96" s="13" t="n"/>
+      <c r="M96" s="13" t="n"/>
+      <c r="N96" s="13" t="n"/>
+      <c r="O96" s="13" t="n"/>
+      <c r="P96" s="24" t="n"/>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="8" t="n">
@@ -6497,15 +6091,11 @@
       </c>
       <c r="J97" s="9" t="n"/>
       <c r="K97" s="10" t="inlineStr"/>
-      <c r="L97" s="11" t="n"/>
-      <c r="M97" s="11" t="n"/>
-      <c r="N97" s="11" t="n"/>
-      <c r="O97" s="11" t="n"/>
-      <c r="P97" s="9" t="n"/>
-      <c r="Q97" s="9" t="n"/>
-      <c r="R97" s="9" t="n"/>
-      <c r="S97" s="9" t="n"/>
-      <c r="T97" s="22" t="n"/>
+      <c r="L97" s="9" t="n"/>
+      <c r="M97" s="9" t="n"/>
+      <c r="N97" s="9" t="n"/>
+      <c r="O97" s="9" t="n"/>
+      <c r="P97" s="22" t="n"/>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="12" t="n">
@@ -6553,15 +6143,11 @@
       </c>
       <c r="J98" s="13" t="n"/>
       <c r="K98" s="14" t="inlineStr"/>
-      <c r="L98" s="15" t="n"/>
-      <c r="M98" s="15" t="n"/>
-      <c r="N98" s="15" t="n"/>
-      <c r="O98" s="15" t="n"/>
-      <c r="P98" s="13" t="n"/>
-      <c r="Q98" s="13" t="n"/>
-      <c r="R98" s="13" t="n"/>
-      <c r="S98" s="13" t="n"/>
-      <c r="T98" s="24" t="n"/>
+      <c r="L98" s="13" t="n"/>
+      <c r="M98" s="13" t="n"/>
+      <c r="N98" s="13" t="n"/>
+      <c r="O98" s="13" t="n"/>
+      <c r="P98" s="24" t="n"/>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="8" t="n">
@@ -6609,15 +6195,11 @@
       </c>
       <c r="J99" s="9" t="n"/>
       <c r="K99" s="10" t="inlineStr"/>
-      <c r="L99" s="11" t="n"/>
-      <c r="M99" s="11" t="n"/>
-      <c r="N99" s="11" t="n"/>
-      <c r="O99" s="11" t="n"/>
-      <c r="P99" s="9" t="n"/>
-      <c r="Q99" s="9" t="n"/>
-      <c r="R99" s="9" t="n"/>
-      <c r="S99" s="9" t="n"/>
-      <c r="T99" s="22" t="n"/>
+      <c r="L99" s="9" t="n"/>
+      <c r="M99" s="9" t="n"/>
+      <c r="N99" s="9" t="n"/>
+      <c r="O99" s="9" t="n"/>
+      <c r="P99" s="22" t="n"/>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="12" t="n">
@@ -6665,15 +6247,11 @@
       </c>
       <c r="J100" s="13" t="n"/>
       <c r="K100" s="14" t="inlineStr"/>
-      <c r="L100" s="15" t="n"/>
-      <c r="M100" s="15" t="n"/>
-      <c r="N100" s="15" t="n"/>
-      <c r="O100" s="15" t="n"/>
-      <c r="P100" s="13" t="n"/>
-      <c r="Q100" s="13" t="n"/>
-      <c r="R100" s="13" t="n"/>
-      <c r="S100" s="13" t="n"/>
-      <c r="T100" s="24" t="n"/>
+      <c r="L100" s="13" t="n"/>
+      <c r="M100" s="13" t="n"/>
+      <c r="N100" s="13" t="n"/>
+      <c r="O100" s="13" t="n"/>
+      <c r="P100" s="24" t="n"/>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="8" t="n">
@@ -6721,15 +6299,11 @@
       </c>
       <c r="J101" s="9" t="n"/>
       <c r="K101" s="10" t="inlineStr"/>
-      <c r="L101" s="11" t="n"/>
-      <c r="M101" s="11" t="n"/>
-      <c r="N101" s="11" t="n"/>
-      <c r="O101" s="11" t="n"/>
-      <c r="P101" s="9" t="n"/>
-      <c r="Q101" s="9" t="n"/>
-      <c r="R101" s="9" t="n"/>
-      <c r="S101" s="9" t="n"/>
-      <c r="T101" s="22" t="n"/>
+      <c r="L101" s="9" t="n"/>
+      <c r="M101" s="9" t="n"/>
+      <c r="N101" s="9" t="n"/>
+      <c r="O101" s="9" t="n"/>
+      <c r="P101" s="22" t="n"/>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="12" t="n">
@@ -6777,15 +6351,11 @@
       </c>
       <c r="J102" s="13" t="n"/>
       <c r="K102" s="14" t="inlineStr"/>
-      <c r="L102" s="15" t="n"/>
-      <c r="M102" s="15" t="n"/>
-      <c r="N102" s="15" t="n"/>
-      <c r="O102" s="15" t="n"/>
-      <c r="P102" s="13" t="n"/>
-      <c r="Q102" s="13" t="n"/>
-      <c r="R102" s="13" t="n"/>
-      <c r="S102" s="13" t="n"/>
-      <c r="T102" s="24" t="n"/>
+      <c r="L102" s="13" t="n"/>
+      <c r="M102" s="13" t="n"/>
+      <c r="N102" s="13" t="n"/>
+      <c r="O102" s="13" t="n"/>
+      <c r="P102" s="24" t="n"/>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="8" t="n">
@@ -6833,15 +6403,11 @@
       </c>
       <c r="J103" s="9" t="n"/>
       <c r="K103" s="10" t="inlineStr"/>
-      <c r="L103" s="11" t="n"/>
-      <c r="M103" s="11" t="n"/>
-      <c r="N103" s="11" t="n"/>
-      <c r="O103" s="11" t="n"/>
-      <c r="P103" s="9" t="n"/>
-      <c r="Q103" s="9" t="n"/>
-      <c r="R103" s="9" t="n"/>
-      <c r="S103" s="9" t="n"/>
-      <c r="T103" s="22" t="n"/>
+      <c r="L103" s="9" t="n"/>
+      <c r="M103" s="9" t="n"/>
+      <c r="N103" s="9" t="n"/>
+      <c r="O103" s="9" t="n"/>
+      <c r="P103" s="22" t="n"/>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="12" t="n">
@@ -6889,15 +6455,11 @@
       </c>
       <c r="J104" s="13" t="n"/>
       <c r="K104" s="14" t="inlineStr"/>
-      <c r="L104" s="15" t="n"/>
-      <c r="M104" s="15" t="n"/>
-      <c r="N104" s="15" t="n"/>
-      <c r="O104" s="15" t="n"/>
-      <c r="P104" s="13" t="n"/>
-      <c r="Q104" s="13" t="n"/>
-      <c r="R104" s="13" t="n"/>
-      <c r="S104" s="13" t="n"/>
-      <c r="T104" s="24" t="n"/>
+      <c r="L104" s="13" t="n"/>
+      <c r="M104" s="13" t="n"/>
+      <c r="N104" s="13" t="n"/>
+      <c r="O104" s="13" t="n"/>
+      <c r="P104" s="24" t="n"/>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="8" t="n">
@@ -6945,15 +6507,11 @@
       </c>
       <c r="J105" s="9" t="n"/>
       <c r="K105" s="10" t="inlineStr"/>
-      <c r="L105" s="11" t="n"/>
-      <c r="M105" s="11" t="n"/>
-      <c r="N105" s="11" t="n"/>
-      <c r="O105" s="11" t="n"/>
-      <c r="P105" s="9" t="n"/>
-      <c r="Q105" s="9" t="n"/>
-      <c r="R105" s="9" t="n"/>
-      <c r="S105" s="9" t="n"/>
-      <c r="T105" s="22" t="n"/>
+      <c r="L105" s="9" t="n"/>
+      <c r="M105" s="9" t="n"/>
+      <c r="N105" s="9" t="n"/>
+      <c r="O105" s="9" t="n"/>
+      <c r="P105" s="22" t="n"/>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="12" t="n">
@@ -7001,15 +6559,11 @@
       </c>
       <c r="J106" s="13" t="n"/>
       <c r="K106" s="14" t="inlineStr"/>
-      <c r="L106" s="15" t="n"/>
-      <c r="M106" s="15" t="n"/>
-      <c r="N106" s="15" t="n"/>
-      <c r="O106" s="15" t="n"/>
-      <c r="P106" s="13" t="n"/>
-      <c r="Q106" s="13" t="n"/>
-      <c r="R106" s="13" t="n"/>
-      <c r="S106" s="13" t="n"/>
-      <c r="T106" s="24" t="n"/>
+      <c r="L106" s="13" t="n"/>
+      <c r="M106" s="13" t="n"/>
+      <c r="N106" s="13" t="n"/>
+      <c r="O106" s="13" t="n"/>
+      <c r="P106" s="24" t="n"/>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="8" t="n">
@@ -7057,15 +6611,11 @@
       </c>
       <c r="J107" s="9" t="n"/>
       <c r="K107" s="10" t="inlineStr"/>
-      <c r="L107" s="11" t="n"/>
-      <c r="M107" s="11" t="n"/>
-      <c r="N107" s="11" t="n"/>
-      <c r="O107" s="11" t="n"/>
-      <c r="P107" s="9" t="n"/>
-      <c r="Q107" s="9" t="n"/>
-      <c r="R107" s="9" t="n"/>
-      <c r="S107" s="9" t="n"/>
-      <c r="T107" s="22" t="n"/>
+      <c r="L107" s="9" t="n"/>
+      <c r="M107" s="9" t="n"/>
+      <c r="N107" s="9" t="n"/>
+      <c r="O107" s="9" t="n"/>
+      <c r="P107" s="22" t="n"/>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="12" t="n">
@@ -7113,15 +6663,11 @@
       </c>
       <c r="J108" s="13" t="n"/>
       <c r="K108" s="14" t="inlineStr"/>
-      <c r="L108" s="15" t="n"/>
-      <c r="M108" s="15" t="n"/>
-      <c r="N108" s="15" t="n"/>
-      <c r="O108" s="15" t="n"/>
-      <c r="P108" s="13" t="n"/>
-      <c r="Q108" s="13" t="n"/>
-      <c r="R108" s="13" t="n"/>
-      <c r="S108" s="13" t="n"/>
-      <c r="T108" s="24" t="n"/>
+      <c r="L108" s="13" t="n"/>
+      <c r="M108" s="13" t="n"/>
+      <c r="N108" s="13" t="n"/>
+      <c r="O108" s="13" t="n"/>
+      <c r="P108" s="24" t="n"/>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="8" t="n">
@@ -7169,11 +6715,7 @@
       <c r="M109" s="9" t="n"/>
       <c r="N109" s="9" t="n"/>
       <c r="O109" s="9" t="n"/>
-      <c r="P109" s="9" t="n"/>
-      <c r="Q109" s="9" t="n"/>
-      <c r="R109" s="9" t="n"/>
-      <c r="S109" s="9" t="n"/>
-      <c r="T109" s="22" t="n"/>
+      <c r="P109" s="22" t="n"/>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="12" t="n">
@@ -7213,11 +6755,7 @@
       <c r="M110" s="13" t="n"/>
       <c r="N110" s="13" t="n"/>
       <c r="O110" s="13" t="n"/>
-      <c r="P110" s="13" t="n"/>
-      <c r="Q110" s="13" t="n"/>
-      <c r="R110" s="13" t="n"/>
-      <c r="S110" s="13" t="n"/>
-      <c r="T110" s="24" t="n"/>
+      <c r="P110" s="24" t="n"/>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="8" t="n"/>
@@ -7235,11 +6773,7 @@
       <c r="M111" s="9" t="n"/>
       <c r="N111" s="9" t="n"/>
       <c r="O111" s="9" t="n"/>
-      <c r="P111" s="9" t="n"/>
-      <c r="Q111" s="9" t="n"/>
-      <c r="R111" s="9" t="n"/>
-      <c r="S111" s="9" t="n"/>
-      <c r="T111" s="22" t="n"/>
+      <c r="P111" s="22" t="n"/>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="12" t="n"/>
@@ -7257,11 +6791,7 @@
       <c r="M112" s="13" t="n"/>
       <c r="N112" s="13" t="n"/>
       <c r="O112" s="13" t="n"/>
-      <c r="P112" s="13" t="n"/>
-      <c r="Q112" s="13" t="n"/>
-      <c r="R112" s="13" t="n"/>
-      <c r="S112" s="13" t="n"/>
-      <c r="T112" s="24" t="n"/>
+      <c r="P112" s="24" t="n"/>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="8" t="n"/>
@@ -7279,11 +6809,7 @@
       <c r="M113" s="9" t="n"/>
       <c r="N113" s="9" t="n"/>
       <c r="O113" s="9" t="n"/>
-      <c r="P113" s="9" t="n"/>
-      <c r="Q113" s="9" t="n"/>
-      <c r="R113" s="9" t="n"/>
-      <c r="S113" s="9" t="n"/>
-      <c r="T113" s="22" t="n"/>
+      <c r="P113" s="22" t="n"/>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="12" t="n"/>
@@ -7301,11 +6827,7 @@
       <c r="M114" s="13" t="n"/>
       <c r="N114" s="13" t="n"/>
       <c r="O114" s="13" t="n"/>
-      <c r="P114" s="13" t="n"/>
-      <c r="Q114" s="13" t="n"/>
-      <c r="R114" s="13" t="n"/>
-      <c r="S114" s="13" t="n"/>
-      <c r="T114" s="24" t="n"/>
+      <c r="P114" s="24" t="n"/>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="8" t="n"/>
@@ -7323,11 +6845,7 @@
       <c r="M115" s="9" t="n"/>
       <c r="N115" s="9" t="n"/>
       <c r="O115" s="9" t="n"/>
-      <c r="P115" s="9" t="n"/>
-      <c r="Q115" s="9" t="n"/>
-      <c r="R115" s="9" t="n"/>
-      <c r="S115" s="9" t="n"/>
-      <c r="T115" s="22" t="n"/>
+      <c r="P115" s="22" t="n"/>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="12" t="n"/>
@@ -7345,11 +6863,7 @@
       <c r="M116" s="13" t="n"/>
       <c r="N116" s="13" t="n"/>
       <c r="O116" s="13" t="n"/>
-      <c r="P116" s="13" t="n"/>
-      <c r="Q116" s="13" t="n"/>
-      <c r="R116" s="13" t="n"/>
-      <c r="S116" s="13" t="n"/>
-      <c r="T116" s="24" t="n"/>
+      <c r="P116" s="24" t="n"/>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="8" t="n"/>
@@ -7367,11 +6881,7 @@
       <c r="M117" s="9" t="n"/>
       <c r="N117" s="9" t="n"/>
       <c r="O117" s="9" t="n"/>
-      <c r="P117" s="9" t="n"/>
-      <c r="Q117" s="9" t="n"/>
-      <c r="R117" s="9" t="n"/>
-      <c r="S117" s="9" t="n"/>
-      <c r="T117" s="22" t="n"/>
+      <c r="P117" s="22" t="n"/>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="12" t="n"/>
@@ -7389,11 +6899,7 @@
       <c r="M118" s="13" t="n"/>
       <c r="N118" s="13" t="n"/>
       <c r="O118" s="13" t="n"/>
-      <c r="P118" s="13" t="n"/>
-      <c r="Q118" s="13" t="n"/>
-      <c r="R118" s="13" t="n"/>
-      <c r="S118" s="13" t="n"/>
-      <c r="T118" s="24" t="n"/>
+      <c r="P118" s="24" t="n"/>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="8" t="n"/>
@@ -7411,11 +6917,7 @@
       <c r="M119" s="9" t="n"/>
       <c r="N119" s="9" t="n"/>
       <c r="O119" s="9" t="n"/>
-      <c r="P119" s="9" t="n"/>
-      <c r="Q119" s="9" t="n"/>
-      <c r="R119" s="9" t="n"/>
-      <c r="S119" s="9" t="n"/>
-      <c r="T119" s="22" t="n"/>
+      <c r="P119" s="22" t="n"/>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="12" t="n"/>
@@ -7433,11 +6935,7 @@
       <c r="M120" s="13" t="n"/>
       <c r="N120" s="13" t="n"/>
       <c r="O120" s="13" t="n"/>
-      <c r="P120" s="13" t="n"/>
-      <c r="Q120" s="13" t="n"/>
-      <c r="R120" s="13" t="n"/>
-      <c r="S120" s="13" t="n"/>
-      <c r="T120" s="24" t="n"/>
+      <c r="P120" s="24" t="n"/>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="8" t="n"/>
@@ -7455,11 +6953,7 @@
       <c r="M121" s="9" t="n"/>
       <c r="N121" s="9" t="n"/>
       <c r="O121" s="9" t="n"/>
-      <c r="P121" s="9" t="n"/>
-      <c r="Q121" s="9" t="n"/>
-      <c r="R121" s="9" t="n"/>
-      <c r="S121" s="9" t="n"/>
-      <c r="T121" s="22" t="n"/>
+      <c r="P121" s="22" t="n"/>
     </row>
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="12" t="n"/>
@@ -7477,11 +6971,7 @@
       <c r="M122" s="13" t="n"/>
       <c r="N122" s="13" t="n"/>
       <c r="O122" s="13" t="n"/>
-      <c r="P122" s="13" t="n"/>
-      <c r="Q122" s="13" t="n"/>
-      <c r="R122" s="13" t="n"/>
-      <c r="S122" s="13" t="n"/>
-      <c r="T122" s="24" t="n"/>
+      <c r="P122" s="24" t="n"/>
     </row>
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="8" t="n"/>
@@ -7499,11 +6989,7 @@
       <c r="M123" s="9" t="n"/>
       <c r="N123" s="9" t="n"/>
       <c r="O123" s="9" t="n"/>
-      <c r="P123" s="9" t="n"/>
-      <c r="Q123" s="9" t="n"/>
-      <c r="R123" s="9" t="n"/>
-      <c r="S123" s="9" t="n"/>
-      <c r="T123" s="22" t="n"/>
+      <c r="P123" s="22" t="n"/>
     </row>
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="12" t="n"/>
@@ -7521,11 +7007,7 @@
       <c r="M124" s="13" t="n"/>
       <c r="N124" s="13" t="n"/>
       <c r="O124" s="13" t="n"/>
-      <c r="P124" s="13" t="n"/>
-      <c r="Q124" s="13" t="n"/>
-      <c r="R124" s="13" t="n"/>
-      <c r="S124" s="13" t="n"/>
-      <c r="T124" s="24" t="n"/>
+      <c r="P124" s="24" t="n"/>
     </row>
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="8" t="n"/>
@@ -7543,11 +7025,7 @@
       <c r="M125" s="9" t="n"/>
       <c r="N125" s="9" t="n"/>
       <c r="O125" s="9" t="n"/>
-      <c r="P125" s="9" t="n"/>
-      <c r="Q125" s="9" t="n"/>
-      <c r="R125" s="9" t="n"/>
-      <c r="S125" s="9" t="n"/>
-      <c r="T125" s="22" t="n"/>
+      <c r="P125" s="22" t="n"/>
     </row>
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="12" t="n"/>
@@ -7565,11 +7043,7 @@
       <c r="M126" s="13" t="n"/>
       <c r="N126" s="13" t="n"/>
       <c r="O126" s="13" t="n"/>
-      <c r="P126" s="13" t="n"/>
-      <c r="Q126" s="13" t="n"/>
-      <c r="R126" s="13" t="n"/>
-      <c r="S126" s="13" t="n"/>
-      <c r="T126" s="24" t="n"/>
+      <c r="P126" s="24" t="n"/>
     </row>
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="8" t="n"/>
@@ -7587,11 +7061,7 @@
       <c r="M127" s="9" t="n"/>
       <c r="N127" s="9" t="n"/>
       <c r="O127" s="9" t="n"/>
-      <c r="P127" s="9" t="n"/>
-      <c r="Q127" s="9" t="n"/>
-      <c r="R127" s="9" t="n"/>
-      <c r="S127" s="9" t="n"/>
-      <c r="T127" s="22" t="n"/>
+      <c r="P127" s="22" t="n"/>
     </row>
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="12" t="n"/>
@@ -7609,11 +7079,7 @@
       <c r="M128" s="13" t="n"/>
       <c r="N128" s="13" t="n"/>
       <c r="O128" s="13" t="n"/>
-      <c r="P128" s="13" t="n"/>
-      <c r="Q128" s="13" t="n"/>
-      <c r="R128" s="13" t="n"/>
-      <c r="S128" s="13" t="n"/>
-      <c r="T128" s="24" t="n"/>
+      <c r="P128" s="24" t="n"/>
     </row>
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="8" t="n"/>
@@ -7631,11 +7097,7 @@
       <c r="M129" s="9" t="n"/>
       <c r="N129" s="9" t="n"/>
       <c r="O129" s="9" t="n"/>
-      <c r="P129" s="9" t="n"/>
-      <c r="Q129" s="9" t="n"/>
-      <c r="R129" s="9" t="n"/>
-      <c r="S129" s="9" t="n"/>
-      <c r="T129" s="22" t="n"/>
+      <c r="P129" s="22" t="n"/>
     </row>
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="12" t="n"/>
@@ -7653,11 +7115,7 @@
       <c r="M130" s="13" t="n"/>
       <c r="N130" s="13" t="n"/>
       <c r="O130" s="13" t="n"/>
-      <c r="P130" s="13" t="n"/>
-      <c r="Q130" s="13" t="n"/>
-      <c r="R130" s="13" t="n"/>
-      <c r="S130" s="13" t="n"/>
-      <c r="T130" s="24" t="n"/>
+      <c r="P130" s="24" t="n"/>
     </row>
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="8" t="n"/>
@@ -7675,11 +7133,7 @@
       <c r="M131" s="9" t="n"/>
       <c r="N131" s="9" t="n"/>
       <c r="O131" s="9" t="n"/>
-      <c r="P131" s="9" t="n"/>
-      <c r="Q131" s="9" t="n"/>
-      <c r="R131" s="9" t="n"/>
-      <c r="S131" s="9" t="n"/>
-      <c r="T131" s="22" t="n"/>
+      <c r="P131" s="22" t="n"/>
     </row>
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="12" t="n"/>
@@ -7697,11 +7151,7 @@
       <c r="M132" s="13" t="n"/>
       <c r="N132" s="13" t="n"/>
       <c r="O132" s="13" t="n"/>
-      <c r="P132" s="13" t="n"/>
-      <c r="Q132" s="13" t="n"/>
-      <c r="R132" s="13" t="n"/>
-      <c r="S132" s="13" t="n"/>
-      <c r="T132" s="24" t="n"/>
+      <c r="P132" s="24" t="n"/>
     </row>
     <row r="133" ht="22" customHeight="1">
       <c r="A133" s="8" t="n"/>
@@ -7719,11 +7169,7 @@
       <c r="M133" s="9" t="n"/>
       <c r="N133" s="9" t="n"/>
       <c r="O133" s="9" t="n"/>
-      <c r="P133" s="9" t="n"/>
-      <c r="Q133" s="9" t="n"/>
-      <c r="R133" s="9" t="n"/>
-      <c r="S133" s="9" t="n"/>
-      <c r="T133" s="22" t="n"/>
+      <c r="P133" s="22" t="n"/>
     </row>
     <row r="134" ht="22" customHeight="1">
       <c r="A134" s="12" t="n"/>
@@ -7741,11 +7187,7 @@
       <c r="M134" s="13" t="n"/>
       <c r="N134" s="13" t="n"/>
       <c r="O134" s="13" t="n"/>
-      <c r="P134" s="13" t="n"/>
-      <c r="Q134" s="13" t="n"/>
-      <c r="R134" s="13" t="n"/>
-      <c r="S134" s="13" t="n"/>
-      <c r="T134" s="24" t="n"/>
+      <c r="P134" s="24" t="n"/>
     </row>
     <row r="135" ht="22" customHeight="1">
       <c r="A135" s="8" t="n"/>
@@ -7763,11 +7205,7 @@
       <c r="M135" s="9" t="n"/>
       <c r="N135" s="9" t="n"/>
       <c r="O135" s="9" t="n"/>
-      <c r="P135" s="9" t="n"/>
-      <c r="Q135" s="9" t="n"/>
-      <c r="R135" s="9" t="n"/>
-      <c r="S135" s="9" t="n"/>
-      <c r="T135" s="22" t="n"/>
+      <c r="P135" s="22" t="n"/>
     </row>
     <row r="136" ht="22" customHeight="1">
       <c r="A136" s="12" t="n"/>
@@ -7785,11 +7223,7 @@
       <c r="M136" s="13" t="n"/>
       <c r="N136" s="13" t="n"/>
       <c r="O136" s="13" t="n"/>
-      <c r="P136" s="13" t="n"/>
-      <c r="Q136" s="13" t="n"/>
-      <c r="R136" s="13" t="n"/>
-      <c r="S136" s="13" t="n"/>
-      <c r="T136" s="24" t="n"/>
+      <c r="P136" s="24" t="n"/>
     </row>
     <row r="137" ht="22" customHeight="1">
       <c r="A137" s="8" t="n"/>
@@ -7807,11 +7241,7 @@
       <c r="M137" s="9" t="n"/>
       <c r="N137" s="9" t="n"/>
       <c r="O137" s="9" t="n"/>
-      <c r="P137" s="9" t="n"/>
-      <c r="Q137" s="9" t="n"/>
-      <c r="R137" s="9" t="n"/>
-      <c r="S137" s="9" t="n"/>
-      <c r="T137" s="22" t="n"/>
+      <c r="P137" s="22" t="n"/>
     </row>
     <row r="138" ht="22" customHeight="1">
       <c r="A138" s="12" t="n"/>
@@ -7829,11 +7259,7 @@
       <c r="M138" s="13" t="n"/>
       <c r="N138" s="13" t="n"/>
       <c r="O138" s="13" t="n"/>
-      <c r="P138" s="13" t="n"/>
-      <c r="Q138" s="13" t="n"/>
-      <c r="R138" s="13" t="n"/>
-      <c r="S138" s="13" t="n"/>
-      <c r="T138" s="24" t="n"/>
+      <c r="P138" s="24" t="n"/>
     </row>
     <row r="139" ht="22" customHeight="1">
       <c r="A139" s="8" t="n"/>
@@ -7851,11 +7277,7 @@
       <c r="M139" s="9" t="n"/>
       <c r="N139" s="9" t="n"/>
       <c r="O139" s="9" t="n"/>
-      <c r="P139" s="9" t="n"/>
-      <c r="Q139" s="9" t="n"/>
-      <c r="R139" s="9" t="n"/>
-      <c r="S139" s="9" t="n"/>
-      <c r="T139" s="22" t="n"/>
+      <c r="P139" s="22" t="n"/>
     </row>
     <row r="140" ht="22" customHeight="1">
       <c r="A140" s="12" t="n"/>
@@ -7873,17 +7295,13 @@
       <c r="M140" s="13" t="n"/>
       <c r="N140" s="13" t="n"/>
       <c r="O140" s="13" t="n"/>
-      <c r="P140" s="13" t="n"/>
-      <c r="Q140" s="13" t="n"/>
-      <c r="R140" s="13" t="n"/>
-      <c r="S140" s="13" t="n"/>
-      <c r="T140" s="24" t="n"/>
+      <c r="P140" s="24" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:O2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="P5:P109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_설계팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_설계팀_입력_2026.xlsx
@@ -214,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -424,6 +424,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -660,11 +669,15 @@
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률(%)
-• 자동 계산 — 참여 부서 소계의 평균
-  예: 3개 부서 진척률 80/50/30 → 53%
-• sync 시 갱신, 수동 수정 불가
-• 100% = 전 부서 완료 상태</t>
+        <t>▣ 부서 진척률 (%) — 본인 부서 작업
+• 자동 계산 (수정 불가, sync 시 갱신)
+• 시작일·완료일 입력 기반:
+    0%  = 미착수    (시작일·완료일 모두 빈 칸)
+   50%  = 진행중    (시작일만 입력)
+  100%  = 완료      (완료일까지 입력)
+• ★ 이 값은 '이 부서'만의 진척률입니다.
+• 프로젝트 전체 진척률은 PMS 1_프로젝트등록
+  '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
@@ -1047,7 +1060,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="79" t="inlineStr">
+      <c r="A1" s="82" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 설계팀 │ 2026</t>
         </is>
@@ -1069,7 +1082,7 @@
       <c r="P1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="80" t="inlineStr">
+      <c r="A2" s="83" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 설계팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1088,9 +1101,9 @@
       <c r="M2" s="16" t="n"/>
       <c r="N2" s="16" t="n"/>
       <c r="O2" s="17" t="n"/>
-      <c r="P2" s="81" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 02:00</t>
+      <c r="P2" s="84" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 11:44</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1242,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>전체진척률(%)</t>
+          <t>부서진척률(%)</t>
         </is>
       </c>
       <c r="L4" s="61" t="inlineStr">
@@ -1306,7 +1319,9 @@
         </is>
       </c>
       <c r="J5" s="9" t="n"/>
-      <c r="K5" s="10" t="inlineStr"/>
+      <c r="K5" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
       <c r="N5" s="9" t="n"/>
@@ -1358,7 +1373,9 @@
         </is>
       </c>
       <c r="J6" s="13" t="n"/>
-      <c r="K6" s="14" t="inlineStr"/>
+      <c r="K6" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L6" s="13" t="n"/>
       <c r="M6" s="13" t="n"/>
       <c r="N6" s="13" t="n"/>
@@ -1410,7 +1427,9 @@
         </is>
       </c>
       <c r="J7" s="9" t="n"/>
-      <c r="K7" s="10" t="inlineStr"/>
+      <c r="K7" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
       <c r="N7" s="9" t="n"/>
@@ -1462,7 +1481,9 @@
         </is>
       </c>
       <c r="J8" s="13" t="n"/>
-      <c r="K8" s="14" t="inlineStr"/>
+      <c r="K8" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L8" s="13" t="n"/>
       <c r="M8" s="13" t="n"/>
       <c r="N8" s="13" t="n"/>
@@ -1514,7 +1535,9 @@
         </is>
       </c>
       <c r="J9" s="9" t="n"/>
-      <c r="K9" s="10" t="inlineStr"/>
+      <c r="K9" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
       <c r="N9" s="9" t="n"/>
@@ -1566,7 +1589,9 @@
         </is>
       </c>
       <c r="J10" s="13" t="n"/>
-      <c r="K10" s="14" t="inlineStr"/>
+      <c r="K10" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L10" s="13" t="n"/>
       <c r="M10" s="13" t="n"/>
       <c r="N10" s="13" t="n"/>
@@ -1618,7 +1643,9 @@
         </is>
       </c>
       <c r="J11" s="9" t="n"/>
-      <c r="K11" s="10" t="inlineStr"/>
+      <c r="K11" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
       <c r="N11" s="9" t="n"/>
@@ -1670,7 +1697,9 @@
         </is>
       </c>
       <c r="J12" s="13" t="n"/>
-      <c r="K12" s="14" t="inlineStr"/>
+      <c r="K12" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L12" s="13" t="n"/>
       <c r="M12" s="13" t="n"/>
       <c r="N12" s="13" t="n"/>
@@ -1722,7 +1751,9 @@
         </is>
       </c>
       <c r="J13" s="9" t="n"/>
-      <c r="K13" s="10" t="inlineStr"/>
+      <c r="K13" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
       <c r="N13" s="9" t="n"/>
@@ -1774,7 +1805,9 @@
         </is>
       </c>
       <c r="J14" s="13" t="n"/>
-      <c r="K14" s="14" t="inlineStr"/>
+      <c r="K14" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L14" s="13" t="n"/>
       <c r="M14" s="13" t="n"/>
       <c r="N14" s="13" t="n"/>
@@ -1826,7 +1859,9 @@
         </is>
       </c>
       <c r="J15" s="9" t="n"/>
-      <c r="K15" s="10" t="inlineStr"/>
+      <c r="K15" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="9" t="n"/>
       <c r="N15" s="9" t="n"/>
@@ -1878,7 +1913,9 @@
         </is>
       </c>
       <c r="J16" s="13" t="n"/>
-      <c r="K16" s="14" t="inlineStr"/>
+      <c r="K16" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L16" s="13" t="n"/>
       <c r="M16" s="13" t="n"/>
       <c r="N16" s="13" t="n"/>
@@ -1930,7 +1967,9 @@
         </is>
       </c>
       <c r="J17" s="9" t="n"/>
-      <c r="K17" s="10" t="inlineStr"/>
+      <c r="K17" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="9" t="n"/>
       <c r="N17" s="9" t="n"/>
@@ -1982,7 +2021,9 @@
         </is>
       </c>
       <c r="J18" s="13" t="n"/>
-      <c r="K18" s="14" t="inlineStr"/>
+      <c r="K18" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L18" s="13" t="n"/>
       <c r="M18" s="13" t="n"/>
       <c r="N18" s="13" t="n"/>
@@ -2034,7 +2075,9 @@
         </is>
       </c>
       <c r="J19" s="9" t="n"/>
-      <c r="K19" s="10" t="inlineStr"/>
+      <c r="K19" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="9" t="n"/>
       <c r="N19" s="9" t="n"/>
@@ -2086,7 +2129,9 @@
         </is>
       </c>
       <c r="J20" s="13" t="n"/>
-      <c r="K20" s="14" t="inlineStr"/>
+      <c r="K20" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L20" s="13" t="n"/>
       <c r="M20" s="13" t="n"/>
       <c r="N20" s="13" t="n"/>
@@ -2138,7 +2183,9 @@
         </is>
       </c>
       <c r="J21" s="9" t="n"/>
-      <c r="K21" s="10" t="inlineStr"/>
+      <c r="K21" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="9" t="n"/>
       <c r="N21" s="9" t="n"/>
@@ -2190,7 +2237,9 @@
         </is>
       </c>
       <c r="J22" s="13" t="n"/>
-      <c r="K22" s="14" t="inlineStr"/>
+      <c r="K22" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L22" s="13" t="n"/>
       <c r="M22" s="13" t="n"/>
       <c r="N22" s="13" t="n"/>
@@ -2242,7 +2291,9 @@
         </is>
       </c>
       <c r="J23" s="9" t="n"/>
-      <c r="K23" s="10" t="inlineStr"/>
+      <c r="K23" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="9" t="n"/>
       <c r="N23" s="9" t="n"/>
@@ -2294,7 +2345,9 @@
         </is>
       </c>
       <c r="J24" s="13" t="n"/>
-      <c r="K24" s="14" t="inlineStr"/>
+      <c r="K24" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L24" s="13" t="n"/>
       <c r="M24" s="13" t="n"/>
       <c r="N24" s="13" t="n"/>
@@ -2346,7 +2399,9 @@
         </is>
       </c>
       <c r="J25" s="9" t="n"/>
-      <c r="K25" s="10" t="inlineStr"/>
+      <c r="K25" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L25" s="9" t="n"/>
       <c r="M25" s="9" t="n"/>
       <c r="N25" s="9" t="n"/>
@@ -2398,7 +2453,9 @@
         </is>
       </c>
       <c r="J26" s="13" t="n"/>
-      <c r="K26" s="14" t="inlineStr"/>
+      <c r="K26" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L26" s="13" t="n"/>
       <c r="M26" s="13" t="n"/>
       <c r="N26" s="13" t="n"/>
@@ -2450,7 +2507,9 @@
         </is>
       </c>
       <c r="J27" s="9" t="n"/>
-      <c r="K27" s="10" t="inlineStr"/>
+      <c r="K27" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L27" s="9" t="n"/>
       <c r="M27" s="9" t="n"/>
       <c r="N27" s="9" t="n"/>
@@ -2502,7 +2561,9 @@
         </is>
       </c>
       <c r="J28" s="13" t="n"/>
-      <c r="K28" s="14" t="inlineStr"/>
+      <c r="K28" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L28" s="13" t="n"/>
       <c r="M28" s="13" t="n"/>
       <c r="N28" s="13" t="n"/>
@@ -2554,7 +2615,9 @@
         </is>
       </c>
       <c r="J29" s="9" t="n"/>
-      <c r="K29" s="10" t="inlineStr"/>
+      <c r="K29" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L29" s="9" t="n"/>
       <c r="M29" s="9" t="n"/>
       <c r="N29" s="9" t="n"/>
@@ -2606,7 +2669,9 @@
         </is>
       </c>
       <c r="J30" s="13" t="n"/>
-      <c r="K30" s="14" t="inlineStr"/>
+      <c r="K30" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L30" s="13" t="n"/>
       <c r="M30" s="13" t="n"/>
       <c r="N30" s="13" t="n"/>
@@ -2658,7 +2723,9 @@
         </is>
       </c>
       <c r="J31" s="9" t="n"/>
-      <c r="K31" s="10" t="inlineStr"/>
+      <c r="K31" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L31" s="9" t="n"/>
       <c r="M31" s="9" t="n"/>
       <c r="N31" s="9" t="n"/>
@@ -2710,7 +2777,9 @@
         </is>
       </c>
       <c r="J32" s="13" t="n"/>
-      <c r="K32" s="14" t="inlineStr"/>
+      <c r="K32" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L32" s="13" t="n"/>
       <c r="M32" s="13" t="n"/>
       <c r="N32" s="13" t="n"/>
@@ -2762,7 +2831,9 @@
         </is>
       </c>
       <c r="J33" s="9" t="n"/>
-      <c r="K33" s="10" t="inlineStr"/>
+      <c r="K33" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L33" s="9" t="n"/>
       <c r="M33" s="9" t="n"/>
       <c r="N33" s="9" t="n"/>
@@ -2814,7 +2885,9 @@
         </is>
       </c>
       <c r="J34" s="13" t="n"/>
-      <c r="K34" s="14" t="inlineStr"/>
+      <c r="K34" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L34" s="13" t="n"/>
       <c r="M34" s="13" t="n"/>
       <c r="N34" s="13" t="n"/>
@@ -2866,7 +2939,9 @@
         </is>
       </c>
       <c r="J35" s="9" t="n"/>
-      <c r="K35" s="10" t="inlineStr"/>
+      <c r="K35" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L35" s="9" t="n"/>
       <c r="M35" s="9" t="n"/>
       <c r="N35" s="9" t="n"/>
@@ -2918,7 +2993,9 @@
         </is>
       </c>
       <c r="J36" s="13" t="n"/>
-      <c r="K36" s="14" t="inlineStr"/>
+      <c r="K36" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L36" s="13" t="n"/>
       <c r="M36" s="13" t="n"/>
       <c r="N36" s="13" t="n"/>
@@ -2970,7 +3047,9 @@
         </is>
       </c>
       <c r="J37" s="9" t="n"/>
-      <c r="K37" s="10" t="inlineStr"/>
+      <c r="K37" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L37" s="9" t="n"/>
       <c r="M37" s="9" t="n"/>
       <c r="N37" s="9" t="n"/>
@@ -3022,7 +3101,9 @@
         </is>
       </c>
       <c r="J38" s="13" t="n"/>
-      <c r="K38" s="14" t="inlineStr"/>
+      <c r="K38" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L38" s="13" t="n"/>
       <c r="M38" s="13" t="n"/>
       <c r="N38" s="13" t="n"/>
@@ -3074,7 +3155,9 @@
         </is>
       </c>
       <c r="J39" s="9" t="n"/>
-      <c r="K39" s="10" t="inlineStr"/>
+      <c r="K39" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L39" s="9" t="n"/>
       <c r="M39" s="9" t="n"/>
       <c r="N39" s="9" t="n"/>
@@ -3126,7 +3209,9 @@
         </is>
       </c>
       <c r="J40" s="13" t="n"/>
-      <c r="K40" s="14" t="inlineStr"/>
+      <c r="K40" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L40" s="13" t="n"/>
       <c r="M40" s="13" t="n"/>
       <c r="N40" s="13" t="n"/>
@@ -3178,7 +3263,9 @@
         </is>
       </c>
       <c r="J41" s="9" t="n"/>
-      <c r="K41" s="10" t="inlineStr"/>
+      <c r="K41" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L41" s="9" t="n"/>
       <c r="M41" s="9" t="n"/>
       <c r="N41" s="9" t="n"/>
@@ -3230,7 +3317,9 @@
         </is>
       </c>
       <c r="J42" s="13" t="n"/>
-      <c r="K42" s="14" t="inlineStr"/>
+      <c r="K42" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L42" s="13" t="n"/>
       <c r="M42" s="13" t="n"/>
       <c r="N42" s="13" t="n"/>
@@ -3282,7 +3371,9 @@
         </is>
       </c>
       <c r="J43" s="9" t="n"/>
-      <c r="K43" s="10" t="inlineStr"/>
+      <c r="K43" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L43" s="9" t="n"/>
       <c r="M43" s="9" t="n"/>
       <c r="N43" s="9" t="n"/>
@@ -3334,7 +3425,9 @@
         </is>
       </c>
       <c r="J44" s="13" t="n"/>
-      <c r="K44" s="14" t="inlineStr"/>
+      <c r="K44" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L44" s="13" t="n"/>
       <c r="M44" s="13" t="n"/>
       <c r="N44" s="13" t="n"/>
@@ -3386,7 +3479,9 @@
         </is>
       </c>
       <c r="J45" s="9" t="n"/>
-      <c r="K45" s="10" t="inlineStr"/>
+      <c r="K45" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L45" s="9" t="n"/>
       <c r="M45" s="9" t="n"/>
       <c r="N45" s="9" t="n"/>
@@ -3438,7 +3533,9 @@
         </is>
       </c>
       <c r="J46" s="13" t="n"/>
-      <c r="K46" s="14" t="inlineStr"/>
+      <c r="K46" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L46" s="13" t="n"/>
       <c r="M46" s="13" t="n"/>
       <c r="N46" s="13" t="n"/>
@@ -3490,7 +3587,9 @@
         </is>
       </c>
       <c r="J47" s="9" t="n"/>
-      <c r="K47" s="10" t="inlineStr"/>
+      <c r="K47" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L47" s="9" t="n"/>
       <c r="M47" s="9" t="n"/>
       <c r="N47" s="9" t="n"/>
@@ -3542,7 +3641,9 @@
         </is>
       </c>
       <c r="J48" s="13" t="n"/>
-      <c r="K48" s="14" t="inlineStr"/>
+      <c r="K48" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L48" s="13" t="n"/>
       <c r="M48" s="13" t="n"/>
       <c r="N48" s="13" t="n"/>
@@ -3594,7 +3695,9 @@
         </is>
       </c>
       <c r="J49" s="9" t="n"/>
-      <c r="K49" s="10" t="inlineStr"/>
+      <c r="K49" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L49" s="9" t="n"/>
       <c r="M49" s="9" t="n"/>
       <c r="N49" s="9" t="n"/>
@@ -3646,7 +3749,9 @@
         </is>
       </c>
       <c r="J50" s="13" t="n"/>
-      <c r="K50" s="14" t="inlineStr"/>
+      <c r="K50" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L50" s="13" t="n"/>
       <c r="M50" s="13" t="n"/>
       <c r="N50" s="13" t="n"/>
@@ -3698,7 +3803,9 @@
         </is>
       </c>
       <c r="J51" s="9" t="n"/>
-      <c r="K51" s="10" t="inlineStr"/>
+      <c r="K51" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L51" s="9" t="n"/>
       <c r="M51" s="9" t="n"/>
       <c r="N51" s="9" t="n"/>
@@ -3750,7 +3857,9 @@
         </is>
       </c>
       <c r="J52" s="13" t="n"/>
-      <c r="K52" s="14" t="inlineStr"/>
+      <c r="K52" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L52" s="13" t="n"/>
       <c r="M52" s="13" t="n"/>
       <c r="N52" s="13" t="n"/>
@@ -3802,7 +3911,9 @@
         </is>
       </c>
       <c r="J53" s="9" t="n"/>
-      <c r="K53" s="10" t="inlineStr"/>
+      <c r="K53" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L53" s="9" t="n"/>
       <c r="M53" s="9" t="n"/>
       <c r="N53" s="9" t="n"/>
@@ -3854,7 +3965,9 @@
         </is>
       </c>
       <c r="J54" s="13" t="n"/>
-      <c r="K54" s="14" t="inlineStr"/>
+      <c r="K54" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L54" s="13" t="n"/>
       <c r="M54" s="13" t="n"/>
       <c r="N54" s="13" t="n"/>
@@ -3906,7 +4019,9 @@
         </is>
       </c>
       <c r="J55" s="9" t="n"/>
-      <c r="K55" s="10" t="inlineStr"/>
+      <c r="K55" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L55" s="9" t="n"/>
       <c r="M55" s="9" t="n"/>
       <c r="N55" s="9" t="n"/>
@@ -3958,7 +4073,9 @@
         </is>
       </c>
       <c r="J56" s="13" t="n"/>
-      <c r="K56" s="14" t="inlineStr"/>
+      <c r="K56" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L56" s="13" t="n"/>
       <c r="M56" s="13" t="n"/>
       <c r="N56" s="13" t="n"/>
@@ -4010,7 +4127,9 @@
         </is>
       </c>
       <c r="J57" s="9" t="n"/>
-      <c r="K57" s="10" t="inlineStr"/>
+      <c r="K57" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L57" s="9" t="n"/>
       <c r="M57" s="9" t="n"/>
       <c r="N57" s="9" t="n"/>
@@ -4062,7 +4181,9 @@
         </is>
       </c>
       <c r="J58" s="13" t="n"/>
-      <c r="K58" s="14" t="inlineStr"/>
+      <c r="K58" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L58" s="13" t="n"/>
       <c r="M58" s="13" t="n"/>
       <c r="N58" s="13" t="n"/>
@@ -4114,7 +4235,9 @@
         </is>
       </c>
       <c r="J59" s="9" t="n"/>
-      <c r="K59" s="10" t="inlineStr"/>
+      <c r="K59" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L59" s="9" t="n"/>
       <c r="M59" s="9" t="n"/>
       <c r="N59" s="9" t="n"/>
@@ -4166,7 +4289,9 @@
         </is>
       </c>
       <c r="J60" s="13" t="n"/>
-      <c r="K60" s="14" t="inlineStr"/>
+      <c r="K60" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L60" s="13" t="n"/>
       <c r="M60" s="13" t="n"/>
       <c r="N60" s="13" t="n"/>
@@ -4218,7 +4343,9 @@
         </is>
       </c>
       <c r="J61" s="9" t="n"/>
-      <c r="K61" s="10" t="inlineStr"/>
+      <c r="K61" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L61" s="9" t="n"/>
       <c r="M61" s="9" t="n"/>
       <c r="N61" s="9" t="n"/>
@@ -4270,7 +4397,9 @@
         </is>
       </c>
       <c r="J62" s="13" t="n"/>
-      <c r="K62" s="14" t="inlineStr"/>
+      <c r="K62" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L62" s="13" t="n"/>
       <c r="M62" s="13" t="n"/>
       <c r="N62" s="13" t="n"/>
@@ -4322,7 +4451,9 @@
         </is>
       </c>
       <c r="J63" s="9" t="n"/>
-      <c r="K63" s="10" t="inlineStr"/>
+      <c r="K63" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L63" s="9" t="n"/>
       <c r="M63" s="9" t="n"/>
       <c r="N63" s="9" t="n"/>
@@ -4374,7 +4505,9 @@
         </is>
       </c>
       <c r="J64" s="13" t="n"/>
-      <c r="K64" s="14" t="inlineStr"/>
+      <c r="K64" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L64" s="13" t="n"/>
       <c r="M64" s="13" t="n"/>
       <c r="N64" s="13" t="n"/>
@@ -4426,7 +4559,9 @@
         </is>
       </c>
       <c r="J65" s="9" t="n"/>
-      <c r="K65" s="10" t="inlineStr"/>
+      <c r="K65" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L65" s="9" t="n"/>
       <c r="M65" s="9" t="n"/>
       <c r="N65" s="9" t="n"/>
@@ -4478,7 +4613,9 @@
         </is>
       </c>
       <c r="J66" s="13" t="n"/>
-      <c r="K66" s="14" t="inlineStr"/>
+      <c r="K66" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L66" s="13" t="n"/>
       <c r="M66" s="13" t="n"/>
       <c r="N66" s="13" t="n"/>
@@ -4530,7 +4667,9 @@
         </is>
       </c>
       <c r="J67" s="9" t="n"/>
-      <c r="K67" s="10" t="inlineStr"/>
+      <c r="K67" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L67" s="9" t="n"/>
       <c r="M67" s="9" t="n"/>
       <c r="N67" s="9" t="n"/>
@@ -4582,7 +4721,9 @@
         </is>
       </c>
       <c r="J68" s="13" t="n"/>
-      <c r="K68" s="14" t="inlineStr"/>
+      <c r="K68" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L68" s="13" t="n"/>
       <c r="M68" s="13" t="n"/>
       <c r="N68" s="13" t="n"/>
@@ -4634,7 +4775,9 @@
         </is>
       </c>
       <c r="J69" s="9" t="n"/>
-      <c r="K69" s="10" t="inlineStr"/>
+      <c r="K69" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L69" s="9" t="n"/>
       <c r="M69" s="9" t="n"/>
       <c r="N69" s="9" t="n"/>
@@ -4686,7 +4829,9 @@
         </is>
       </c>
       <c r="J70" s="13" t="n"/>
-      <c r="K70" s="14" t="inlineStr"/>
+      <c r="K70" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L70" s="13" t="n"/>
       <c r="M70" s="13" t="n"/>
       <c r="N70" s="13" t="n"/>
@@ -4738,7 +4883,9 @@
         </is>
       </c>
       <c r="J71" s="9" t="n"/>
-      <c r="K71" s="10" t="inlineStr"/>
+      <c r="K71" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L71" s="9" t="n"/>
       <c r="M71" s="9" t="n"/>
       <c r="N71" s="9" t="n"/>
@@ -4790,7 +4937,9 @@
         </is>
       </c>
       <c r="J72" s="13" t="n"/>
-      <c r="K72" s="14" t="inlineStr"/>
+      <c r="K72" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L72" s="13" t="n"/>
       <c r="M72" s="13" t="n"/>
       <c r="N72" s="13" t="n"/>
@@ -4842,7 +4991,9 @@
         </is>
       </c>
       <c r="J73" s="9" t="n"/>
-      <c r="K73" s="10" t="inlineStr"/>
+      <c r="K73" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L73" s="9" t="n"/>
       <c r="M73" s="9" t="n"/>
       <c r="N73" s="9" t="n"/>
@@ -4894,7 +5045,9 @@
         </is>
       </c>
       <c r="J74" s="13" t="n"/>
-      <c r="K74" s="14" t="inlineStr"/>
+      <c r="K74" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L74" s="13" t="n"/>
       <c r="M74" s="13" t="n"/>
       <c r="N74" s="13" t="n"/>
@@ -4946,7 +5099,9 @@
         </is>
       </c>
       <c r="J75" s="9" t="n"/>
-      <c r="K75" s="10" t="inlineStr"/>
+      <c r="K75" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L75" s="9" t="n"/>
       <c r="M75" s="9" t="n"/>
       <c r="N75" s="9" t="n"/>
@@ -4998,7 +5153,9 @@
         </is>
       </c>
       <c r="J76" s="13" t="n"/>
-      <c r="K76" s="14" t="inlineStr"/>
+      <c r="K76" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L76" s="13" t="n"/>
       <c r="M76" s="13" t="n"/>
       <c r="N76" s="13" t="n"/>
@@ -5050,7 +5207,9 @@
         </is>
       </c>
       <c r="J77" s="9" t="n"/>
-      <c r="K77" s="10" t="inlineStr"/>
+      <c r="K77" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L77" s="9" t="n"/>
       <c r="M77" s="9" t="n"/>
       <c r="N77" s="9" t="n"/>
@@ -5102,7 +5261,9 @@
         </is>
       </c>
       <c r="J78" s="13" t="n"/>
-      <c r="K78" s="14" t="inlineStr"/>
+      <c r="K78" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L78" s="13" t="n"/>
       <c r="M78" s="13" t="n"/>
       <c r="N78" s="13" t="n"/>
@@ -5154,7 +5315,9 @@
         </is>
       </c>
       <c r="J79" s="9" t="n"/>
-      <c r="K79" s="10" t="inlineStr"/>
+      <c r="K79" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L79" s="9" t="n"/>
       <c r="M79" s="9" t="n"/>
       <c r="N79" s="9" t="n"/>
@@ -5206,7 +5369,9 @@
         </is>
       </c>
       <c r="J80" s="13" t="n"/>
-      <c r="K80" s="14" t="inlineStr"/>
+      <c r="K80" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L80" s="13" t="n"/>
       <c r="M80" s="13" t="n"/>
       <c r="N80" s="13" t="n"/>
@@ -5258,7 +5423,9 @@
         </is>
       </c>
       <c r="J81" s="9" t="n"/>
-      <c r="K81" s="10" t="inlineStr"/>
+      <c r="K81" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L81" s="9" t="n"/>
       <c r="M81" s="9" t="n"/>
       <c r="N81" s="9" t="n"/>
@@ -5310,7 +5477,9 @@
         </is>
       </c>
       <c r="J82" s="13" t="n"/>
-      <c r="K82" s="14" t="inlineStr"/>
+      <c r="K82" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L82" s="13" t="n"/>
       <c r="M82" s="13" t="n"/>
       <c r="N82" s="13" t="n"/>
@@ -5362,7 +5531,9 @@
         </is>
       </c>
       <c r="J83" s="9" t="n"/>
-      <c r="K83" s="10" t="inlineStr"/>
+      <c r="K83" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L83" s="9" t="n"/>
       <c r="M83" s="9" t="n"/>
       <c r="N83" s="9" t="n"/>
@@ -5414,7 +5585,9 @@
         </is>
       </c>
       <c r="J84" s="13" t="n"/>
-      <c r="K84" s="14" t="inlineStr"/>
+      <c r="K84" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L84" s="13" t="n"/>
       <c r="M84" s="13" t="n"/>
       <c r="N84" s="13" t="n"/>
@@ -5466,7 +5639,9 @@
         </is>
       </c>
       <c r="J85" s="9" t="n"/>
-      <c r="K85" s="10" t="inlineStr"/>
+      <c r="K85" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L85" s="9" t="n"/>
       <c r="M85" s="9" t="n"/>
       <c r="N85" s="9" t="n"/>
@@ -5518,7 +5693,9 @@
         </is>
       </c>
       <c r="J86" s="13" t="n"/>
-      <c r="K86" s="14" t="inlineStr"/>
+      <c r="K86" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L86" s="13" t="n"/>
       <c r="M86" s="13" t="n"/>
       <c r="N86" s="13" t="n"/>
@@ -5570,7 +5747,9 @@
         </is>
       </c>
       <c r="J87" s="9" t="n"/>
-      <c r="K87" s="10" t="inlineStr"/>
+      <c r="K87" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L87" s="9" t="n"/>
       <c r="M87" s="9" t="n"/>
       <c r="N87" s="9" t="n"/>
@@ -5622,7 +5801,9 @@
         </is>
       </c>
       <c r="J88" s="13" t="n"/>
-      <c r="K88" s="14" t="inlineStr"/>
+      <c r="K88" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L88" s="13" t="n"/>
       <c r="M88" s="13" t="n"/>
       <c r="N88" s="13" t="n"/>
@@ -5674,7 +5855,9 @@
         </is>
       </c>
       <c r="J89" s="9" t="n"/>
-      <c r="K89" s="10" t="inlineStr"/>
+      <c r="K89" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L89" s="9" t="n"/>
       <c r="M89" s="9" t="n"/>
       <c r="N89" s="9" t="n"/>
@@ -5726,7 +5909,9 @@
         </is>
       </c>
       <c r="J90" s="13" t="n"/>
-      <c r="K90" s="14" t="inlineStr"/>
+      <c r="K90" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L90" s="13" t="n"/>
       <c r="M90" s="13" t="n"/>
       <c r="N90" s="13" t="n"/>
@@ -5778,7 +5963,9 @@
         </is>
       </c>
       <c r="J91" s="9" t="n"/>
-      <c r="K91" s="10" t="inlineStr"/>
+      <c r="K91" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L91" s="9" t="n"/>
       <c r="M91" s="9" t="n"/>
       <c r="N91" s="9" t="n"/>
@@ -5830,7 +6017,9 @@
         </is>
       </c>
       <c r="J92" s="13" t="n"/>
-      <c r="K92" s="14" t="inlineStr"/>
+      <c r="K92" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L92" s="13" t="n"/>
       <c r="M92" s="13" t="n"/>
       <c r="N92" s="13" t="n"/>
@@ -5882,7 +6071,9 @@
         </is>
       </c>
       <c r="J93" s="9" t="n"/>
-      <c r="K93" s="10" t="inlineStr"/>
+      <c r="K93" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L93" s="9" t="n"/>
       <c r="M93" s="9" t="n"/>
       <c r="N93" s="9" t="n"/>
@@ -5934,7 +6125,9 @@
         </is>
       </c>
       <c r="J94" s="13" t="n"/>
-      <c r="K94" s="14" t="inlineStr"/>
+      <c r="K94" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L94" s="13" t="n"/>
       <c r="M94" s="13" t="n"/>
       <c r="N94" s="13" t="n"/>
@@ -5986,7 +6179,9 @@
         </is>
       </c>
       <c r="J95" s="9" t="n"/>
-      <c r="K95" s="10" t="inlineStr"/>
+      <c r="K95" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L95" s="9" t="n"/>
       <c r="M95" s="9" t="n"/>
       <c r="N95" s="9" t="n"/>
@@ -6038,7 +6233,9 @@
         </is>
       </c>
       <c r="J96" s="13" t="n"/>
-      <c r="K96" s="14" t="inlineStr"/>
+      <c r="K96" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L96" s="13" t="n"/>
       <c r="M96" s="13" t="n"/>
       <c r="N96" s="13" t="n"/>
@@ -6090,7 +6287,9 @@
         </is>
       </c>
       <c r="J97" s="9" t="n"/>
-      <c r="K97" s="10" t="inlineStr"/>
+      <c r="K97" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L97" s="9" t="n"/>
       <c r="M97" s="9" t="n"/>
       <c r="N97" s="9" t="n"/>
@@ -6142,7 +6341,9 @@
         </is>
       </c>
       <c r="J98" s="13" t="n"/>
-      <c r="K98" s="14" t="inlineStr"/>
+      <c r="K98" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L98" s="13" t="n"/>
       <c r="M98" s="13" t="n"/>
       <c r="N98" s="13" t="n"/>
@@ -6194,7 +6395,9 @@
         </is>
       </c>
       <c r="J99" s="9" t="n"/>
-      <c r="K99" s="10" t="inlineStr"/>
+      <c r="K99" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L99" s="9" t="n"/>
       <c r="M99" s="9" t="n"/>
       <c r="N99" s="9" t="n"/>
@@ -6246,7 +6449,9 @@
         </is>
       </c>
       <c r="J100" s="13" t="n"/>
-      <c r="K100" s="14" t="inlineStr"/>
+      <c r="K100" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L100" s="13" t="n"/>
       <c r="M100" s="13" t="n"/>
       <c r="N100" s="13" t="n"/>
@@ -6298,7 +6503,9 @@
         </is>
       </c>
       <c r="J101" s="9" t="n"/>
-      <c r="K101" s="10" t="inlineStr"/>
+      <c r="K101" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L101" s="9" t="n"/>
       <c r="M101" s="9" t="n"/>
       <c r="N101" s="9" t="n"/>
@@ -6350,7 +6557,9 @@
         </is>
       </c>
       <c r="J102" s="13" t="n"/>
-      <c r="K102" s="14" t="inlineStr"/>
+      <c r="K102" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L102" s="13" t="n"/>
       <c r="M102" s="13" t="n"/>
       <c r="N102" s="13" t="n"/>
@@ -6402,7 +6611,9 @@
         </is>
       </c>
       <c r="J103" s="9" t="n"/>
-      <c r="K103" s="10" t="inlineStr"/>
+      <c r="K103" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L103" s="9" t="n"/>
       <c r="M103" s="9" t="n"/>
       <c r="N103" s="9" t="n"/>
@@ -6454,7 +6665,9 @@
         </is>
       </c>
       <c r="J104" s="13" t="n"/>
-      <c r="K104" s="14" t="inlineStr"/>
+      <c r="K104" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L104" s="13" t="n"/>
       <c r="M104" s="13" t="n"/>
       <c r="N104" s="13" t="n"/>
@@ -6506,7 +6719,9 @@
         </is>
       </c>
       <c r="J105" s="9" t="n"/>
-      <c r="K105" s="10" t="inlineStr"/>
+      <c r="K105" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L105" s="9" t="n"/>
       <c r="M105" s="9" t="n"/>
       <c r="N105" s="9" t="n"/>
@@ -6558,7 +6773,9 @@
         </is>
       </c>
       <c r="J106" s="13" t="n"/>
-      <c r="K106" s="14" t="inlineStr"/>
+      <c r="K106" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L106" s="13" t="n"/>
       <c r="M106" s="13" t="n"/>
       <c r="N106" s="13" t="n"/>
@@ -6610,7 +6827,9 @@
         </is>
       </c>
       <c r="J107" s="9" t="n"/>
-      <c r="K107" s="10" t="inlineStr"/>
+      <c r="K107" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L107" s="9" t="n"/>
       <c r="M107" s="9" t="n"/>
       <c r="N107" s="9" t="n"/>
@@ -6662,7 +6881,9 @@
         </is>
       </c>
       <c r="J108" s="13" t="n"/>
-      <c r="K108" s="14" t="inlineStr"/>
+      <c r="K108" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L108" s="13" t="n"/>
       <c r="M108" s="13" t="n"/>
       <c r="N108" s="13" t="n"/>
@@ -6710,7 +6931,9 @@
       </c>
       <c r="I109" s="8" t="inlineStr"/>
       <c r="J109" s="9" t="n"/>
-      <c r="K109" s="8" t="inlineStr"/>
+      <c r="K109" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L109" s="9" t="n"/>
       <c r="M109" s="9" t="n"/>
       <c r="N109" s="9" t="n"/>
@@ -6750,7 +6973,9 @@
       <c r="H110" s="12" t="inlineStr"/>
       <c r="I110" s="12" t="inlineStr"/>
       <c r="J110" s="13" t="n"/>
-      <c r="K110" s="12" t="inlineStr"/>
+      <c r="K110" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L110" s="13" t="n"/>
       <c r="M110" s="13" t="n"/>
       <c r="N110" s="13" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_설계팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_설계팀_입력_2026.xlsx
@@ -214,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -424,6 +424,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -554,15 +572,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -576,46 +609,86 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -626,11 +699,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -645,31 +726,55 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -678,11 +783,19 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 시작일
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 시작일
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-05-10
 • 허용: 26-5-10, 260510, 2026.5.10 (자동 정규화)
@@ -691,11 +804,19 @@
 • 비워두면: 미착수 상태
 • v3.1 검사기 운영: 진척률 % 대신 시작·완료일로 추적
   (2주 단위 빠른 작업 사이클이라 % 입력이 비효율)</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 완료일
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 완료일
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-05-24
 • 허용: 26-5-24, 260524, 2026.5.24 (자동 정규화)
@@ -705,39 +826,64 @@
 • 입력 시: PMS 2_진행현황에 자동 표시 +
   전체 진척률 = (완료 부서 수) / (참여 부서 수) 자동 계산
 • '제외' 부서는 분모에서 제외됨</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 가공의뢰 입고일
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 가공의뢰 입고일
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-07-10
 • 가공팀 의뢰분 또는 외주 가공품의
   ★실제 입고된 날짜★ 기입 (내부·외주 무관)
 • 비워두면: 대시보드 외주현황에 '진행중' 표시
 • 입고일 입력 시: '입고완료'로 자동 분류</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 작업 상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메모 (부서 자유 입력)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -1060,7 +1206,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="82" t="inlineStr">
+      <c r="A1" s="88" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 설계팀 │ 2026</t>
         </is>
@@ -1082,7 +1228,7 @@
       <c r="P1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="83" t="inlineStr">
+      <c r="A2" s="89" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 설계팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1101,9 +1247,9 @@
       <c r="M2" s="16" t="n"/>
       <c r="N2" s="16" t="n"/>
       <c r="O2" s="17" t="n"/>
-      <c r="P2" s="84" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 11:44</t>
+      <c r="P2" s="90" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:33</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_설계팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_설계팀_입력_2026.xlsx
@@ -130,7 +130,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -210,11 +210,40 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -488,6 +517,17 @@
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1206,7 +1246,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="88" t="inlineStr">
+      <c r="A1" s="91" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 설계팀 │ 2026</t>
         </is>
@@ -1228,7 +1268,7 @@
       <c r="P1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
+      <c r="A2" s="92" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 설계팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1244,14 +1284,14 @@
       <c r="J2" s="16" t="n"/>
       <c r="K2" s="16" t="n"/>
       <c r="L2" s="16" t="n"/>
-      <c r="M2" s="16" t="n"/>
-      <c r="N2" s="16" t="n"/>
-      <c r="O2" s="17" t="n"/>
-      <c r="P2" s="90" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:33</t>
-        </is>
-      </c>
+      <c r="M2" s="17" t="n"/>
+      <c r="N2" s="93" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:58</t>
+        </is>
+      </c>
+      <c r="O2" s="94" t="n"/>
+      <c r="P2" s="95" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -7670,9 +7710,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="N2:P2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="P5:P109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_설계팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_설계팀_입력_2026.xlsx
@@ -243,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -528,6 +528,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -841,7 +850,10 @@
 • 허용: 26-5-10, 260510, 2026.5.10 (자동 정규화)
 • 부서가 ★실제로 작업을 시작한 날짜★ 기입
 • PO 후 작업 착수일 (지시 받은 날 아님)
-• 비워두면: 미착수 상태
+📋 입력값 의미:
+  ▸ 빈 칸 → 미착수 또는 '해당없음'
+           (부서 자체가 해당없음이면 PMS에서 '제외' 선택 권장)
+  ▸ 날짜 → 시작 (부서 진척률 50% 인식)
 • v3.1 검사기 운영: 진척률 % 대신 시작·완료일로 추적
   (2주 단위 빠른 작업 사이클이라 % 입력이 비효율)</t>
         </r>
@@ -862,7 +874,10 @@
 • 허용: 26-5-24, 260524, 2026.5.24 (자동 정규화)
 • 부서 작업이 ★실제로 완료된 날짜★ 기입
 • 예정일 아닌 ★실제 완료일★ 만 입력
-• 비워두면: PMS 진행현황에서 '미완료'로 집계
+📋 입력값 의미:
+  ▸ 빈 칸 → 미완료 또는 '해당없음'
+           (부서 자체가 해당없음이면 PMS에서 '제외' 선택 권장)
+  ▸ 날짜 → 완료 (부서 진척률 100%)
 • 입력 시: PMS 2_진행현황에 자동 표시 +
   전체 진척률 = (완료 부서 수) / (참여 부서 수) 자동 계산
 • '제외' 부서는 분모에서 제외됨</t>
@@ -1234,9 +1249,9 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" style="43" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" style="43" min="12" max="12"/>
-    <col width="12" customWidth="1" style="43" min="13" max="13"/>
-    <col width="12" customWidth="1" style="43" min="14" max="14"/>
+    <col width="5" customWidth="1" style="43" min="12" max="12"/>
+    <col width="5" customWidth="1" style="43" min="13" max="13"/>
+    <col width="5" customWidth="1" style="43" min="14" max="14"/>
     <col width="10" customWidth="1" style="43" min="15" max="15"/>
     <col width="28" customWidth="1" style="43" min="16" max="16"/>
     <col width="12" customWidth="1" style="43" min="17" max="17"/>
@@ -1246,7 +1261,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="91" t="inlineStr">
+      <c r="A1" s="96" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 설계팀 │ 2026</t>
         </is>
@@ -1268,7 +1283,7 @@
       <c r="P1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="92" t="inlineStr">
+      <c r="A2" s="97" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 설계팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1285,13 +1300,13 @@
       <c r="K2" s="16" t="n"/>
       <c r="L2" s="16" t="n"/>
       <c r="M2" s="17" t="n"/>
-      <c r="N2" s="93" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:58</t>
-        </is>
-      </c>
-      <c r="O2" s="94" t="n"/>
-      <c r="P2" s="95" t="n"/>
+      <c r="N2" s="98" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:26</t>
+        </is>
+      </c>
+      <c r="O2" s="16" t="n"/>
+      <c r="P2" s="17" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_설계팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_설계팀_입력_2026.xlsx
@@ -243,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -528,6 +528,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -893,13 +902,18 @@
             <family val="3"/>
             <charset val="129"/>
           </rPr>
-          <t>▣ 가공의뢰 입고일
-★ 날짜 입력 (% 아님 ⚠️)
-• 형식: YYYY-MM-DD  예: 2026-07-10
-• 가공팀 의뢰분 또는 외주 가공품의
-  ★실제 입고된 날짜★ 기입 (내부·외주 무관)
-• 비워두면: 대시보드 외주현황에 '진행중' 표시
-• 입고일 입력 시: '입고완료'로 자동 분류</t>
+          <t>▣ 의뢰입고일 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -1249,9 +1263,9 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" style="43" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" style="43" min="12" max="12"/>
-    <col width="5" customWidth="1" style="43" min="13" max="13"/>
-    <col width="5" customWidth="1" style="43" min="14" max="14"/>
+    <col width="7" customWidth="1" style="43" min="12" max="12"/>
+    <col width="7" customWidth="1" style="43" min="13" max="13"/>
+    <col width="7" customWidth="1" style="43" min="14" max="14"/>
     <col width="10" customWidth="1" style="43" min="15" max="15"/>
     <col width="28" customWidth="1" style="43" min="16" max="16"/>
     <col width="12" customWidth="1" style="43" min="17" max="17"/>
@@ -1261,7 +1275,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="96" t="inlineStr">
+      <c r="A1" s="99" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 설계팀 │ 2026</t>
         </is>
@@ -1283,7 +1297,7 @@
       <c r="P1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="97" t="inlineStr">
+      <c r="A2" s="100" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 설계팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1300,9 +1314,9 @@
       <c r="K2" s="16" t="n"/>
       <c r="L2" s="16" t="n"/>
       <c r="M2" s="17" t="n"/>
-      <c r="N2" s="98" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:26</t>
+      <c r="N2" s="101" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:38</t>
         </is>
       </c>
       <c r="O2" s="16" t="n"/>
@@ -1460,7 +1474,7 @@
       </c>
       <c r="N4" s="61" t="inlineStr">
         <is>
-          <t>가공의뢰
+          <t>의뢰
 입고일</t>
         </is>
       </c>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_설계팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_설계팀_입력_2026.xlsx
@@ -243,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -528,6 +528,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -902,22 +911,40 @@
             <family val="3"/>
             <charset val="129"/>
           </rPr>
-          <t>▣ 의뢰입고일 (세부항목 진척률)
-★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
-  또는 0~100 정수도 허용 (예: 50, 100)
-📋 입력값 의미:
-  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
-           — 부서 진척률 평균에서 ★분모 제외★
-  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
-  ▸ 0.5   → 50% 진행 중
-  ▸ 1.0   → 100% 완료
-💡 부서장·담당자가 매주 진척률 갱신
-💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+          <t>▣ 의뢰 입고예정일 (가공의뢰 후 예정)
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-15
+• 가공의뢰 발주 시 외부업체와 약속한
+  ★입고 완료 예정일★ 기입
+📋 운영:
+  ▸ 의뢰 시 예정일 입력
+  ▸ 실제 입고일과 비교 → 지연 여부 추적
+  ▸ 비워두면: 미발주 또는 일정 미정</t>
         </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 의뢰 입고일 (가공의뢰 결과)
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD
+• 가공의뢰한 부품·가공품이
+  ★실제 입고된 날짜★ 기입
+📋 의뢰예정일과 비교:
+  ▸ 입고일 ≤ 예정일 → 정시
+  ▸ 입고일 &gt; 예정일 → 지연
+  ▸ 입고일 = 빈 칸  → 미입고 (진행중)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -936,7 +963,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P4" authorId="0" shapeId="0">
+    <comment ref="Q4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1249,7 +1276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P140"/>
+  <dimension ref="A1:Q140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1266,16 +1293,16 @@
     <col width="7" customWidth="1" style="43" min="12" max="12"/>
     <col width="7" customWidth="1" style="43" min="13" max="13"/>
     <col width="7" customWidth="1" style="43" min="14" max="14"/>
-    <col width="10" customWidth="1" style="43" min="15" max="15"/>
-    <col width="28" customWidth="1" style="43" min="16" max="16"/>
-    <col width="12" customWidth="1" style="43" min="17" max="17"/>
+    <col width="7" customWidth="1" style="43" min="15" max="15"/>
+    <col width="10" customWidth="1" style="43" min="16" max="16"/>
+    <col width="28" customWidth="1" style="43" min="17" max="17"/>
     <col width="12" customWidth="1" style="43" min="18" max="18"/>
     <col width="10" customWidth="1" style="43" min="19" max="19"/>
     <col width="28" customWidth="1" style="43" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="99" t="inlineStr">
+      <c r="A1" s="102" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 설계팀 │ 2026</t>
         </is>
@@ -1294,10 +1321,11 @@
       <c r="M1" s="16" t="n"/>
       <c r="N1" s="16" t="n"/>
       <c r="O1" s="16" t="n"/>
-      <c r="P1" s="17" t="n"/>
+      <c r="P1" s="16" t="n"/>
+      <c r="Q1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="100" t="inlineStr">
+      <c r="A2" s="103" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 설계팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1313,14 +1341,13 @@
       <c r="J2" s="16" t="n"/>
       <c r="K2" s="16" t="n"/>
       <c r="L2" s="16" t="n"/>
-      <c r="M2" s="17" t="n"/>
-      <c r="N2" s="101" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:38</t>
-        </is>
-      </c>
-      <c r="O2" s="16" t="n"/>
-      <c r="P2" s="17" t="n"/>
+      <c r="M2" s="16" t="n"/>
+      <c r="N2" s="17" t="n"/>
+      <c r="O2" s="104" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:46</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -1393,12 +1420,17 @@
           <t>PO후입력</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>✏선택▼</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>✏메모</t>
         </is>
@@ -1475,15 +1507,21 @@
       <c r="N4" s="61" t="inlineStr">
         <is>
           <t>의뢰
+예정일</t>
+        </is>
+      </c>
+      <c r="O4" s="61" t="inlineStr">
+        <is>
+          <t>의뢰
 입고일</t>
         </is>
       </c>
-      <c r="O4" s="7" t="inlineStr">
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="P4" s="7" t="inlineStr">
+      <c r="Q4" s="7" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -1541,7 +1579,8 @@
       <c r="M5" s="9" t="n"/>
       <c r="N5" s="9" t="n"/>
       <c r="O5" s="9" t="n"/>
-      <c r="P5" s="22" t="n"/>
+      <c r="P5" s="9" t="n"/>
+      <c r="Q5" s="22" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="12" t="n">
@@ -1595,7 +1634,8 @@
       <c r="M6" s="13" t="n"/>
       <c r="N6" s="13" t="n"/>
       <c r="O6" s="13" t="n"/>
-      <c r="P6" s="24" t="n"/>
+      <c r="P6" s="13" t="n"/>
+      <c r="Q6" s="24" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="n">
@@ -1649,7 +1689,8 @@
       <c r="M7" s="9" t="n"/>
       <c r="N7" s="9" t="n"/>
       <c r="O7" s="9" t="n"/>
-      <c r="P7" s="22" t="n"/>
+      <c r="P7" s="9" t="n"/>
+      <c r="Q7" s="22" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="12" t="n">
@@ -1703,7 +1744,8 @@
       <c r="M8" s="13" t="n"/>
       <c r="N8" s="13" t="n"/>
       <c r="O8" s="13" t="n"/>
-      <c r="P8" s="24" t="n"/>
+      <c r="P8" s="13" t="n"/>
+      <c r="Q8" s="24" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="8" t="n">
@@ -1757,7 +1799,8 @@
       <c r="M9" s="9" t="n"/>
       <c r="N9" s="9" t="n"/>
       <c r="O9" s="9" t="n"/>
-      <c r="P9" s="22" t="n"/>
+      <c r="P9" s="9" t="n"/>
+      <c r="Q9" s="22" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="12" t="n">
@@ -1811,7 +1854,8 @@
       <c r="M10" s="13" t="n"/>
       <c r="N10" s="13" t="n"/>
       <c r="O10" s="13" t="n"/>
-      <c r="P10" s="24" t="n"/>
+      <c r="P10" s="13" t="n"/>
+      <c r="Q10" s="24" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="8" t="n">
@@ -1865,7 +1909,8 @@
       <c r="M11" s="9" t="n"/>
       <c r="N11" s="9" t="n"/>
       <c r="O11" s="9" t="n"/>
-      <c r="P11" s="22" t="n"/>
+      <c r="P11" s="9" t="n"/>
+      <c r="Q11" s="22" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="12" t="n">
@@ -1919,7 +1964,8 @@
       <c r="M12" s="13" t="n"/>
       <c r="N12" s="13" t="n"/>
       <c r="O12" s="13" t="n"/>
-      <c r="P12" s="24" t="n"/>
+      <c r="P12" s="13" t="n"/>
+      <c r="Q12" s="24" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="8" t="n">
@@ -1973,7 +2019,8 @@
       <c r="M13" s="9" t="n"/>
       <c r="N13" s="9" t="n"/>
       <c r="O13" s="9" t="n"/>
-      <c r="P13" s="22" t="n"/>
+      <c r="P13" s="9" t="n"/>
+      <c r="Q13" s="22" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="12" t="n">
@@ -2027,7 +2074,8 @@
       <c r="M14" s="13" t="n"/>
       <c r="N14" s="13" t="n"/>
       <c r="O14" s="13" t="n"/>
-      <c r="P14" s="24" t="n"/>
+      <c r="P14" s="13" t="n"/>
+      <c r="Q14" s="24" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="8" t="n">
@@ -2081,7 +2129,8 @@
       <c r="M15" s="9" t="n"/>
       <c r="N15" s="9" t="n"/>
       <c r="O15" s="9" t="n"/>
-      <c r="P15" s="22" t="n"/>
+      <c r="P15" s="9" t="n"/>
+      <c r="Q15" s="22" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="12" t="n">
@@ -2135,7 +2184,8 @@
       <c r="M16" s="13" t="n"/>
       <c r="N16" s="13" t="n"/>
       <c r="O16" s="13" t="n"/>
-      <c r="P16" s="24" t="n"/>
+      <c r="P16" s="13" t="n"/>
+      <c r="Q16" s="24" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="8" t="n">
@@ -2189,7 +2239,8 @@
       <c r="M17" s="9" t="n"/>
       <c r="N17" s="9" t="n"/>
       <c r="O17" s="9" t="n"/>
-      <c r="P17" s="22" t="n"/>
+      <c r="P17" s="9" t="n"/>
+      <c r="Q17" s="22" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="12" t="n">
@@ -2243,7 +2294,8 @@
       <c r="M18" s="13" t="n"/>
       <c r="N18" s="13" t="n"/>
       <c r="O18" s="13" t="n"/>
-      <c r="P18" s="24" t="n"/>
+      <c r="P18" s="13" t="n"/>
+      <c r="Q18" s="24" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="8" t="n">
@@ -2297,7 +2349,8 @@
       <c r="M19" s="9" t="n"/>
       <c r="N19" s="9" t="n"/>
       <c r="O19" s="9" t="n"/>
-      <c r="P19" s="22" t="n"/>
+      <c r="P19" s="9" t="n"/>
+      <c r="Q19" s="22" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="12" t="n">
@@ -2351,7 +2404,8 @@
       <c r="M20" s="13" t="n"/>
       <c r="N20" s="13" t="n"/>
       <c r="O20" s="13" t="n"/>
-      <c r="P20" s="24" t="n"/>
+      <c r="P20" s="13" t="n"/>
+      <c r="Q20" s="24" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="8" t="n">
@@ -2405,7 +2459,8 @@
       <c r="M21" s="9" t="n"/>
       <c r="N21" s="9" t="n"/>
       <c r="O21" s="9" t="n"/>
-      <c r="P21" s="22" t="n"/>
+      <c r="P21" s="9" t="n"/>
+      <c r="Q21" s="22" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="12" t="n">
@@ -2459,7 +2514,8 @@
       <c r="M22" s="13" t="n"/>
       <c r="N22" s="13" t="n"/>
       <c r="O22" s="13" t="n"/>
-      <c r="P22" s="24" t="n"/>
+      <c r="P22" s="13" t="n"/>
+      <c r="Q22" s="24" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="8" t="n">
@@ -2513,7 +2569,8 @@
       <c r="M23" s="9" t="n"/>
       <c r="N23" s="9" t="n"/>
       <c r="O23" s="9" t="n"/>
-      <c r="P23" s="22" t="n"/>
+      <c r="P23" s="9" t="n"/>
+      <c r="Q23" s="22" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="12" t="n">
@@ -2567,7 +2624,8 @@
       <c r="M24" s="13" t="n"/>
       <c r="N24" s="13" t="n"/>
       <c r="O24" s="13" t="n"/>
-      <c r="P24" s="24" t="n"/>
+      <c r="P24" s="13" t="n"/>
+      <c r="Q24" s="24" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="8" t="n">
@@ -2621,7 +2679,8 @@
       <c r="M25" s="9" t="n"/>
       <c r="N25" s="9" t="n"/>
       <c r="O25" s="9" t="n"/>
-      <c r="P25" s="22" t="n"/>
+      <c r="P25" s="9" t="n"/>
+      <c r="Q25" s="22" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="12" t="n">
@@ -2675,7 +2734,8 @@
       <c r="M26" s="13" t="n"/>
       <c r="N26" s="13" t="n"/>
       <c r="O26" s="13" t="n"/>
-      <c r="P26" s="24" t="n"/>
+      <c r="P26" s="13" t="n"/>
+      <c r="Q26" s="24" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="8" t="n">
@@ -2729,7 +2789,8 @@
       <c r="M27" s="9" t="n"/>
       <c r="N27" s="9" t="n"/>
       <c r="O27" s="9" t="n"/>
-      <c r="P27" s="22" t="n"/>
+      <c r="P27" s="9" t="n"/>
+      <c r="Q27" s="22" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="12" t="n">
@@ -2783,7 +2844,8 @@
       <c r="M28" s="13" t="n"/>
       <c r="N28" s="13" t="n"/>
       <c r="O28" s="13" t="n"/>
-      <c r="P28" s="24" t="n"/>
+      <c r="P28" s="13" t="n"/>
+      <c r="Q28" s="24" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="8" t="n">
@@ -2837,7 +2899,8 @@
       <c r="M29" s="9" t="n"/>
       <c r="N29" s="9" t="n"/>
       <c r="O29" s="9" t="n"/>
-      <c r="P29" s="22" t="n"/>
+      <c r="P29" s="9" t="n"/>
+      <c r="Q29" s="22" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="12" t="n">
@@ -2891,7 +2954,8 @@
       <c r="M30" s="13" t="n"/>
       <c r="N30" s="13" t="n"/>
       <c r="O30" s="13" t="n"/>
-      <c r="P30" s="24" t="n"/>
+      <c r="P30" s="13" t="n"/>
+      <c r="Q30" s="24" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="8" t="n">
@@ -2945,7 +3009,8 @@
       <c r="M31" s="9" t="n"/>
       <c r="N31" s="9" t="n"/>
       <c r="O31" s="9" t="n"/>
-      <c r="P31" s="22" t="n"/>
+      <c r="P31" s="9" t="n"/>
+      <c r="Q31" s="22" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="12" t="n">
@@ -2999,7 +3064,8 @@
       <c r="M32" s="13" t="n"/>
       <c r="N32" s="13" t="n"/>
       <c r="O32" s="13" t="n"/>
-      <c r="P32" s="24" t="n"/>
+      <c r="P32" s="13" t="n"/>
+      <c r="Q32" s="24" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="8" t="n">
@@ -3053,7 +3119,8 @@
       <c r="M33" s="9" t="n"/>
       <c r="N33" s="9" t="n"/>
       <c r="O33" s="9" t="n"/>
-      <c r="P33" s="22" t="n"/>
+      <c r="P33" s="9" t="n"/>
+      <c r="Q33" s="22" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="12" t="n">
@@ -3107,7 +3174,8 @@
       <c r="M34" s="13" t="n"/>
       <c r="N34" s="13" t="n"/>
       <c r="O34" s="13" t="n"/>
-      <c r="P34" s="24" t="n"/>
+      <c r="P34" s="13" t="n"/>
+      <c r="Q34" s="24" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="8" t="n">
@@ -3161,7 +3229,8 @@
       <c r="M35" s="9" t="n"/>
       <c r="N35" s="9" t="n"/>
       <c r="O35" s="9" t="n"/>
-      <c r="P35" s="22" t="n"/>
+      <c r="P35" s="9" t="n"/>
+      <c r="Q35" s="22" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="12" t="n">
@@ -3215,7 +3284,8 @@
       <c r="M36" s="13" t="n"/>
       <c r="N36" s="13" t="n"/>
       <c r="O36" s="13" t="n"/>
-      <c r="P36" s="24" t="n"/>
+      <c r="P36" s="13" t="n"/>
+      <c r="Q36" s="24" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="8" t="n">
@@ -3269,7 +3339,8 @@
       <c r="M37" s="9" t="n"/>
       <c r="N37" s="9" t="n"/>
       <c r="O37" s="9" t="n"/>
-      <c r="P37" s="22" t="n"/>
+      <c r="P37" s="9" t="n"/>
+      <c r="Q37" s="22" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="12" t="n">
@@ -3323,7 +3394,8 @@
       <c r="M38" s="13" t="n"/>
       <c r="N38" s="13" t="n"/>
       <c r="O38" s="13" t="n"/>
-      <c r="P38" s="24" t="n"/>
+      <c r="P38" s="13" t="n"/>
+      <c r="Q38" s="24" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="8" t="n">
@@ -3377,7 +3449,8 @@
       <c r="M39" s="9" t="n"/>
       <c r="N39" s="9" t="n"/>
       <c r="O39" s="9" t="n"/>
-      <c r="P39" s="22" t="n"/>
+      <c r="P39" s="9" t="n"/>
+      <c r="Q39" s="22" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="12" t="n">
@@ -3431,7 +3504,8 @@
       <c r="M40" s="13" t="n"/>
       <c r="N40" s="13" t="n"/>
       <c r="O40" s="13" t="n"/>
-      <c r="P40" s="24" t="n"/>
+      <c r="P40" s="13" t="n"/>
+      <c r="Q40" s="24" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="8" t="n">
@@ -3485,7 +3559,8 @@
       <c r="M41" s="9" t="n"/>
       <c r="N41" s="9" t="n"/>
       <c r="O41" s="9" t="n"/>
-      <c r="P41" s="22" t="n"/>
+      <c r="P41" s="9" t="n"/>
+      <c r="Q41" s="22" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="12" t="n">
@@ -3539,7 +3614,8 @@
       <c r="M42" s="13" t="n"/>
       <c r="N42" s="13" t="n"/>
       <c r="O42" s="13" t="n"/>
-      <c r="P42" s="24" t="n"/>
+      <c r="P42" s="13" t="n"/>
+      <c r="Q42" s="24" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="8" t="n">
@@ -3593,7 +3669,8 @@
       <c r="M43" s="9" t="n"/>
       <c r="N43" s="9" t="n"/>
       <c r="O43" s="9" t="n"/>
-      <c r="P43" s="22" t="n"/>
+      <c r="P43" s="9" t="n"/>
+      <c r="Q43" s="22" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="12" t="n">
@@ -3647,7 +3724,8 @@
       <c r="M44" s="13" t="n"/>
       <c r="N44" s="13" t="n"/>
       <c r="O44" s="13" t="n"/>
-      <c r="P44" s="24" t="n"/>
+      <c r="P44" s="13" t="n"/>
+      <c r="Q44" s="24" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="8" t="n">
@@ -3701,7 +3779,8 @@
       <c r="M45" s="9" t="n"/>
       <c r="N45" s="9" t="n"/>
       <c r="O45" s="9" t="n"/>
-      <c r="P45" s="22" t="n"/>
+      <c r="P45" s="9" t="n"/>
+      <c r="Q45" s="22" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="12" t="n">
@@ -3755,7 +3834,8 @@
       <c r="M46" s="13" t="n"/>
       <c r="N46" s="13" t="n"/>
       <c r="O46" s="13" t="n"/>
-      <c r="P46" s="24" t="n"/>
+      <c r="P46" s="13" t="n"/>
+      <c r="Q46" s="24" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="8" t="n">
@@ -3809,7 +3889,8 @@
       <c r="M47" s="9" t="n"/>
       <c r="N47" s="9" t="n"/>
       <c r="O47" s="9" t="n"/>
-      <c r="P47" s="22" t="n"/>
+      <c r="P47" s="9" t="n"/>
+      <c r="Q47" s="22" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="12" t="n">
@@ -3863,7 +3944,8 @@
       <c r="M48" s="13" t="n"/>
       <c r="N48" s="13" t="n"/>
       <c r="O48" s="13" t="n"/>
-      <c r="P48" s="24" t="n"/>
+      <c r="P48" s="13" t="n"/>
+      <c r="Q48" s="24" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="8" t="n">
@@ -3917,7 +3999,8 @@
       <c r="M49" s="9" t="n"/>
       <c r="N49" s="9" t="n"/>
       <c r="O49" s="9" t="n"/>
-      <c r="P49" s="22" t="n"/>
+      <c r="P49" s="9" t="n"/>
+      <c r="Q49" s="22" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="12" t="n">
@@ -3971,7 +4054,8 @@
       <c r="M50" s="13" t="n"/>
       <c r="N50" s="13" t="n"/>
       <c r="O50" s="13" t="n"/>
-      <c r="P50" s="24" t="n"/>
+      <c r="P50" s="13" t="n"/>
+      <c r="Q50" s="24" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="8" t="n">
@@ -4025,7 +4109,8 @@
       <c r="M51" s="9" t="n"/>
       <c r="N51" s="9" t="n"/>
       <c r="O51" s="9" t="n"/>
-      <c r="P51" s="22" t="n"/>
+      <c r="P51" s="9" t="n"/>
+      <c r="Q51" s="22" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="12" t="n">
@@ -4079,7 +4164,8 @@
       <c r="M52" s="13" t="n"/>
       <c r="N52" s="13" t="n"/>
       <c r="O52" s="13" t="n"/>
-      <c r="P52" s="24" t="n"/>
+      <c r="P52" s="13" t="n"/>
+      <c r="Q52" s="24" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="8" t="n">
@@ -4133,7 +4219,8 @@
       <c r="M53" s="9" t="n"/>
       <c r="N53" s="9" t="n"/>
       <c r="O53" s="9" t="n"/>
-      <c r="P53" s="22" t="n"/>
+      <c r="P53" s="9" t="n"/>
+      <c r="Q53" s="22" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="12" t="n">
@@ -4187,7 +4274,8 @@
       <c r="M54" s="13" t="n"/>
       <c r="N54" s="13" t="n"/>
       <c r="O54" s="13" t="n"/>
-      <c r="P54" s="24" t="n"/>
+      <c r="P54" s="13" t="n"/>
+      <c r="Q54" s="24" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="8" t="n">
@@ -4241,7 +4329,8 @@
       <c r="M55" s="9" t="n"/>
       <c r="N55" s="9" t="n"/>
       <c r="O55" s="9" t="n"/>
-      <c r="P55" s="22" t="n"/>
+      <c r="P55" s="9" t="n"/>
+      <c r="Q55" s="22" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="12" t="n">
@@ -4295,7 +4384,8 @@
       <c r="M56" s="13" t="n"/>
       <c r="N56" s="13" t="n"/>
       <c r="O56" s="13" t="n"/>
-      <c r="P56" s="24" t="n"/>
+      <c r="P56" s="13" t="n"/>
+      <c r="Q56" s="24" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="8" t="n">
@@ -4349,7 +4439,8 @@
       <c r="M57" s="9" t="n"/>
       <c r="N57" s="9" t="n"/>
       <c r="O57" s="9" t="n"/>
-      <c r="P57" s="22" t="n"/>
+      <c r="P57" s="9" t="n"/>
+      <c r="Q57" s="22" t="n"/>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="12" t="n">
@@ -4403,7 +4494,8 @@
       <c r="M58" s="13" t="n"/>
       <c r="N58" s="13" t="n"/>
       <c r="O58" s="13" t="n"/>
-      <c r="P58" s="24" t="n"/>
+      <c r="P58" s="13" t="n"/>
+      <c r="Q58" s="24" t="n"/>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="8" t="n">
@@ -4457,7 +4549,8 @@
       <c r="M59" s="9" t="n"/>
       <c r="N59" s="9" t="n"/>
       <c r="O59" s="9" t="n"/>
-      <c r="P59" s="22" t="n"/>
+      <c r="P59" s="9" t="n"/>
+      <c r="Q59" s="22" t="n"/>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="12" t="n">
@@ -4511,7 +4604,8 @@
       <c r="M60" s="13" t="n"/>
       <c r="N60" s="13" t="n"/>
       <c r="O60" s="13" t="n"/>
-      <c r="P60" s="24" t="n"/>
+      <c r="P60" s="13" t="n"/>
+      <c r="Q60" s="24" t="n"/>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="8" t="n">
@@ -4565,7 +4659,8 @@
       <c r="M61" s="9" t="n"/>
       <c r="N61" s="9" t="n"/>
       <c r="O61" s="9" t="n"/>
-      <c r="P61" s="22" t="n"/>
+      <c r="P61" s="9" t="n"/>
+      <c r="Q61" s="22" t="n"/>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="12" t="n">
@@ -4619,7 +4714,8 @@
       <c r="M62" s="13" t="n"/>
       <c r="N62" s="13" t="n"/>
       <c r="O62" s="13" t="n"/>
-      <c r="P62" s="24" t="n"/>
+      <c r="P62" s="13" t="n"/>
+      <c r="Q62" s="24" t="n"/>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="8" t="n">
@@ -4673,7 +4769,8 @@
       <c r="M63" s="9" t="n"/>
       <c r="N63" s="9" t="n"/>
       <c r="O63" s="9" t="n"/>
-      <c r="P63" s="22" t="n"/>
+      <c r="P63" s="9" t="n"/>
+      <c r="Q63" s="22" t="n"/>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="12" t="n">
@@ -4727,7 +4824,8 @@
       <c r="M64" s="13" t="n"/>
       <c r="N64" s="13" t="n"/>
       <c r="O64" s="13" t="n"/>
-      <c r="P64" s="24" t="n"/>
+      <c r="P64" s="13" t="n"/>
+      <c r="Q64" s="24" t="n"/>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="8" t="n">
@@ -4781,7 +4879,8 @@
       <c r="M65" s="9" t="n"/>
       <c r="N65" s="9" t="n"/>
       <c r="O65" s="9" t="n"/>
-      <c r="P65" s="22" t="n"/>
+      <c r="P65" s="9" t="n"/>
+      <c r="Q65" s="22" t="n"/>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="12" t="n">
@@ -4835,7 +4934,8 @@
       <c r="M66" s="13" t="n"/>
       <c r="N66" s="13" t="n"/>
       <c r="O66" s="13" t="n"/>
-      <c r="P66" s="24" t="n"/>
+      <c r="P66" s="13" t="n"/>
+      <c r="Q66" s="24" t="n"/>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="8" t="n">
@@ -4889,7 +4989,8 @@
       <c r="M67" s="9" t="n"/>
       <c r="N67" s="9" t="n"/>
       <c r="O67" s="9" t="n"/>
-      <c r="P67" s="22" t="n"/>
+      <c r="P67" s="9" t="n"/>
+      <c r="Q67" s="22" t="n"/>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="12" t="n">
@@ -4943,7 +5044,8 @@
       <c r="M68" s="13" t="n"/>
       <c r="N68" s="13" t="n"/>
       <c r="O68" s="13" t="n"/>
-      <c r="P68" s="24" t="n"/>
+      <c r="P68" s="13" t="n"/>
+      <c r="Q68" s="24" t="n"/>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="8" t="n">
@@ -4997,7 +5099,8 @@
       <c r="M69" s="9" t="n"/>
       <c r="N69" s="9" t="n"/>
       <c r="O69" s="9" t="n"/>
-      <c r="P69" s="22" t="n"/>
+      <c r="P69" s="9" t="n"/>
+      <c r="Q69" s="22" t="n"/>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="12" t="n">
@@ -5051,7 +5154,8 @@
       <c r="M70" s="13" t="n"/>
       <c r="N70" s="13" t="n"/>
       <c r="O70" s="13" t="n"/>
-      <c r="P70" s="24" t="n"/>
+      <c r="P70" s="13" t="n"/>
+      <c r="Q70" s="24" t="n"/>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="8" t="n">
@@ -5105,7 +5209,8 @@
       <c r="M71" s="9" t="n"/>
       <c r="N71" s="9" t="n"/>
       <c r="O71" s="9" t="n"/>
-      <c r="P71" s="22" t="n"/>
+      <c r="P71" s="9" t="n"/>
+      <c r="Q71" s="22" t="n"/>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="12" t="n">
@@ -5159,7 +5264,8 @@
       <c r="M72" s="13" t="n"/>
       <c r="N72" s="13" t="n"/>
       <c r="O72" s="13" t="n"/>
-      <c r="P72" s="24" t="n"/>
+      <c r="P72" s="13" t="n"/>
+      <c r="Q72" s="24" t="n"/>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="8" t="n">
@@ -5213,7 +5319,8 @@
       <c r="M73" s="9" t="n"/>
       <c r="N73" s="9" t="n"/>
       <c r="O73" s="9" t="n"/>
-      <c r="P73" s="22" t="n"/>
+      <c r="P73" s="9" t="n"/>
+      <c r="Q73" s="22" t="n"/>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="12" t="n">
@@ -5267,7 +5374,8 @@
       <c r="M74" s="13" t="n"/>
       <c r="N74" s="13" t="n"/>
       <c r="O74" s="13" t="n"/>
-      <c r="P74" s="24" t="n"/>
+      <c r="P74" s="13" t="n"/>
+      <c r="Q74" s="24" t="n"/>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="8" t="n">
@@ -5321,7 +5429,8 @@
       <c r="M75" s="9" t="n"/>
       <c r="N75" s="9" t="n"/>
       <c r="O75" s="9" t="n"/>
-      <c r="P75" s="22" t="n"/>
+      <c r="P75" s="9" t="n"/>
+      <c r="Q75" s="22" t="n"/>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="12" t="n">
@@ -5375,7 +5484,8 @@
       <c r="M76" s="13" t="n"/>
       <c r="N76" s="13" t="n"/>
       <c r="O76" s="13" t="n"/>
-      <c r="P76" s="24" t="n"/>
+      <c r="P76" s="13" t="n"/>
+      <c r="Q76" s="24" t="n"/>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="8" t="n">
@@ -5429,7 +5539,8 @@
       <c r="M77" s="9" t="n"/>
       <c r="N77" s="9" t="n"/>
       <c r="O77" s="9" t="n"/>
-      <c r="P77" s="22" t="n"/>
+      <c r="P77" s="9" t="n"/>
+      <c r="Q77" s="22" t="n"/>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="12" t="n">
@@ -5483,7 +5594,8 @@
       <c r="M78" s="13" t="n"/>
       <c r="N78" s="13" t="n"/>
       <c r="O78" s="13" t="n"/>
-      <c r="P78" s="24" t="n"/>
+      <c r="P78" s="13" t="n"/>
+      <c r="Q78" s="24" t="n"/>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="8" t="n">
@@ -5537,7 +5649,8 @@
       <c r="M79" s="9" t="n"/>
       <c r="N79" s="9" t="n"/>
       <c r="O79" s="9" t="n"/>
-      <c r="P79" s="22" t="n"/>
+      <c r="P79" s="9" t="n"/>
+      <c r="Q79" s="22" t="n"/>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="12" t="n">
@@ -5591,7 +5704,8 @@
       <c r="M80" s="13" t="n"/>
       <c r="N80" s="13" t="n"/>
       <c r="O80" s="13" t="n"/>
-      <c r="P80" s="24" t="n"/>
+      <c r="P80" s="13" t="n"/>
+      <c r="Q80" s="24" t="n"/>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="8" t="n">
@@ -5645,7 +5759,8 @@
       <c r="M81" s="9" t="n"/>
       <c r="N81" s="9" t="n"/>
       <c r="O81" s="9" t="n"/>
-      <c r="P81" s="22" t="n"/>
+      <c r="P81" s="9" t="n"/>
+      <c r="Q81" s="22" t="n"/>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="12" t="n">
@@ -5699,7 +5814,8 @@
       <c r="M82" s="13" t="n"/>
       <c r="N82" s="13" t="n"/>
       <c r="O82" s="13" t="n"/>
-      <c r="P82" s="24" t="n"/>
+      <c r="P82" s="13" t="n"/>
+      <c r="Q82" s="24" t="n"/>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="8" t="n">
@@ -5753,7 +5869,8 @@
       <c r="M83" s="9" t="n"/>
       <c r="N83" s="9" t="n"/>
       <c r="O83" s="9" t="n"/>
-      <c r="P83" s="22" t="n"/>
+      <c r="P83" s="9" t="n"/>
+      <c r="Q83" s="22" t="n"/>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="12" t="n">
@@ -5807,7 +5924,8 @@
       <c r="M84" s="13" t="n"/>
       <c r="N84" s="13" t="n"/>
       <c r="O84" s="13" t="n"/>
-      <c r="P84" s="24" t="n"/>
+      <c r="P84" s="13" t="n"/>
+      <c r="Q84" s="24" t="n"/>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="8" t="n">
@@ -5861,7 +5979,8 @@
       <c r="M85" s="9" t="n"/>
       <c r="N85" s="9" t="n"/>
       <c r="O85" s="9" t="n"/>
-      <c r="P85" s="22" t="n"/>
+      <c r="P85" s="9" t="n"/>
+      <c r="Q85" s="22" t="n"/>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="12" t="n">
@@ -5915,7 +6034,8 @@
       <c r="M86" s="13" t="n"/>
       <c r="N86" s="13" t="n"/>
       <c r="O86" s="13" t="n"/>
-      <c r="P86" s="24" t="n"/>
+      <c r="P86" s="13" t="n"/>
+      <c r="Q86" s="24" t="n"/>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="8" t="n">
@@ -5969,7 +6089,8 @@
       <c r="M87" s="9" t="n"/>
       <c r="N87" s="9" t="n"/>
       <c r="O87" s="9" t="n"/>
-      <c r="P87" s="22" t="n"/>
+      <c r="P87" s="9" t="n"/>
+      <c r="Q87" s="22" t="n"/>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="12" t="n">
@@ -6023,7 +6144,8 @@
       <c r="M88" s="13" t="n"/>
       <c r="N88" s="13" t="n"/>
       <c r="O88" s="13" t="n"/>
-      <c r="P88" s="24" t="n"/>
+      <c r="P88" s="13" t="n"/>
+      <c r="Q88" s="24" t="n"/>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="8" t="n">
@@ -6077,7 +6199,8 @@
       <c r="M89" s="9" t="n"/>
       <c r="N89" s="9" t="n"/>
       <c r="O89" s="9" t="n"/>
-      <c r="P89" s="22" t="n"/>
+      <c r="P89" s="9" t="n"/>
+      <c r="Q89" s="22" t="n"/>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="12" t="n">
@@ -6131,7 +6254,8 @@
       <c r="M90" s="13" t="n"/>
       <c r="N90" s="13" t="n"/>
       <c r="O90" s="13" t="n"/>
-      <c r="P90" s="24" t="n"/>
+      <c r="P90" s="13" t="n"/>
+      <c r="Q90" s="24" t="n"/>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="8" t="n">
@@ -6185,7 +6309,8 @@
       <c r="M91" s="9" t="n"/>
       <c r="N91" s="9" t="n"/>
       <c r="O91" s="9" t="n"/>
-      <c r="P91" s="22" t="n"/>
+      <c r="P91" s="9" t="n"/>
+      <c r="Q91" s="22" t="n"/>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="12" t="n">
@@ -6239,7 +6364,8 @@
       <c r="M92" s="13" t="n"/>
       <c r="N92" s="13" t="n"/>
       <c r="O92" s="13" t="n"/>
-      <c r="P92" s="24" t="n"/>
+      <c r="P92" s="13" t="n"/>
+      <c r="Q92" s="24" t="n"/>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="8" t="n">
@@ -6293,7 +6419,8 @@
       <c r="M93" s="9" t="n"/>
       <c r="N93" s="9" t="n"/>
       <c r="O93" s="9" t="n"/>
-      <c r="P93" s="22" t="n"/>
+      <c r="P93" s="9" t="n"/>
+      <c r="Q93" s="22" t="n"/>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="12" t="n">
@@ -6347,7 +6474,8 @@
       <c r="M94" s="13" t="n"/>
       <c r="N94" s="13" t="n"/>
       <c r="O94" s="13" t="n"/>
-      <c r="P94" s="24" t="n"/>
+      <c r="P94" s="13" t="n"/>
+      <c r="Q94" s="24" t="n"/>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="8" t="n">
@@ -6401,7 +6529,8 @@
       <c r="M95" s="9" t="n"/>
       <c r="N95" s="9" t="n"/>
       <c r="O95" s="9" t="n"/>
-      <c r="P95" s="22" t="n"/>
+      <c r="P95" s="9" t="n"/>
+      <c r="Q95" s="22" t="n"/>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="12" t="n">
@@ -6455,7 +6584,8 @@
       <c r="M96" s="13" t="n"/>
       <c r="N96" s="13" t="n"/>
       <c r="O96" s="13" t="n"/>
-      <c r="P96" s="24" t="n"/>
+      <c r="P96" s="13" t="n"/>
+      <c r="Q96" s="24" t="n"/>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="8" t="n">
@@ -6509,7 +6639,8 @@
       <c r="M97" s="9" t="n"/>
       <c r="N97" s="9" t="n"/>
       <c r="O97" s="9" t="n"/>
-      <c r="P97" s="22" t="n"/>
+      <c r="P97" s="9" t="n"/>
+      <c r="Q97" s="22" t="n"/>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="12" t="n">
@@ -6563,7 +6694,8 @@
       <c r="M98" s="13" t="n"/>
       <c r="N98" s="13" t="n"/>
       <c r="O98" s="13" t="n"/>
-      <c r="P98" s="24" t="n"/>
+      <c r="P98" s="13" t="n"/>
+      <c r="Q98" s="24" t="n"/>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="8" t="n">
@@ -6617,7 +6749,8 @@
       <c r="M99" s="9" t="n"/>
       <c r="N99" s="9" t="n"/>
       <c r="O99" s="9" t="n"/>
-      <c r="P99" s="22" t="n"/>
+      <c r="P99" s="9" t="n"/>
+      <c r="Q99" s="22" t="n"/>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="12" t="n">
@@ -6671,7 +6804,8 @@
       <c r="M100" s="13" t="n"/>
       <c r="N100" s="13" t="n"/>
       <c r="O100" s="13" t="n"/>
-      <c r="P100" s="24" t="n"/>
+      <c r="P100" s="13" t="n"/>
+      <c r="Q100" s="24" t="n"/>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="8" t="n">
@@ -6725,7 +6859,8 @@
       <c r="M101" s="9" t="n"/>
       <c r="N101" s="9" t="n"/>
       <c r="O101" s="9" t="n"/>
-      <c r="P101" s="22" t="n"/>
+      <c r="P101" s="9" t="n"/>
+      <c r="Q101" s="22" t="n"/>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="12" t="n">
@@ -6779,7 +6914,8 @@
       <c r="M102" s="13" t="n"/>
       <c r="N102" s="13" t="n"/>
       <c r="O102" s="13" t="n"/>
-      <c r="P102" s="24" t="n"/>
+      <c r="P102" s="13" t="n"/>
+      <c r="Q102" s="24" t="n"/>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="8" t="n">
@@ -6833,7 +6969,8 @@
       <c r="M103" s="9" t="n"/>
       <c r="N103" s="9" t="n"/>
       <c r="O103" s="9" t="n"/>
-      <c r="P103" s="22" t="n"/>
+      <c r="P103" s="9" t="n"/>
+      <c r="Q103" s="22" t="n"/>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="12" t="n">
@@ -6887,7 +7024,8 @@
       <c r="M104" s="13" t="n"/>
       <c r="N104" s="13" t="n"/>
       <c r="O104" s="13" t="n"/>
-      <c r="P104" s="24" t="n"/>
+      <c r="P104" s="13" t="n"/>
+      <c r="Q104" s="24" t="n"/>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="8" t="n">
@@ -6941,7 +7079,8 @@
       <c r="M105" s="9" t="n"/>
       <c r="N105" s="9" t="n"/>
       <c r="O105" s="9" t="n"/>
-      <c r="P105" s="22" t="n"/>
+      <c r="P105" s="9" t="n"/>
+      <c r="Q105" s="22" t="n"/>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="12" t="n">
@@ -6995,7 +7134,8 @@
       <c r="M106" s="13" t="n"/>
       <c r="N106" s="13" t="n"/>
       <c r="O106" s="13" t="n"/>
-      <c r="P106" s="24" t="n"/>
+      <c r="P106" s="13" t="n"/>
+      <c r="Q106" s="24" t="n"/>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="8" t="n">
@@ -7049,7 +7189,8 @@
       <c r="M107" s="9" t="n"/>
       <c r="N107" s="9" t="n"/>
       <c r="O107" s="9" t="n"/>
-      <c r="P107" s="22" t="n"/>
+      <c r="P107" s="9" t="n"/>
+      <c r="Q107" s="22" t="n"/>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="12" t="n">
@@ -7103,7 +7244,8 @@
       <c r="M108" s="13" t="n"/>
       <c r="N108" s="13" t="n"/>
       <c r="O108" s="13" t="n"/>
-      <c r="P108" s="24" t="n"/>
+      <c r="P108" s="13" t="n"/>
+      <c r="Q108" s="24" t="n"/>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="8" t="n">
@@ -7153,7 +7295,8 @@
       <c r="M109" s="9" t="n"/>
       <c r="N109" s="9" t="n"/>
       <c r="O109" s="9" t="n"/>
-      <c r="P109" s="22" t="n"/>
+      <c r="P109" s="9" t="n"/>
+      <c r="Q109" s="22" t="n"/>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="12" t="n">
@@ -7195,7 +7338,8 @@
       <c r="M110" s="13" t="n"/>
       <c r="N110" s="13" t="n"/>
       <c r="O110" s="13" t="n"/>
-      <c r="P110" s="24" t="n"/>
+      <c r="P110" s="13" t="n"/>
+      <c r="Q110" s="24" t="n"/>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="8" t="n"/>
@@ -7213,7 +7357,8 @@
       <c r="M111" s="9" t="n"/>
       <c r="N111" s="9" t="n"/>
       <c r="O111" s="9" t="n"/>
-      <c r="P111" s="22" t="n"/>
+      <c r="P111" s="9" t="n"/>
+      <c r="Q111" s="22" t="n"/>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="12" t="n"/>
@@ -7231,7 +7376,8 @@
       <c r="M112" s="13" t="n"/>
       <c r="N112" s="13" t="n"/>
       <c r="O112" s="13" t="n"/>
-      <c r="P112" s="24" t="n"/>
+      <c r="P112" s="13" t="n"/>
+      <c r="Q112" s="24" t="n"/>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="8" t="n"/>
@@ -7249,7 +7395,8 @@
       <c r="M113" s="9" t="n"/>
       <c r="N113" s="9" t="n"/>
       <c r="O113" s="9" t="n"/>
-      <c r="P113" s="22" t="n"/>
+      <c r="P113" s="9" t="n"/>
+      <c r="Q113" s="22" t="n"/>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="12" t="n"/>
@@ -7267,7 +7414,8 @@
       <c r="M114" s="13" t="n"/>
       <c r="N114" s="13" t="n"/>
       <c r="O114" s="13" t="n"/>
-      <c r="P114" s="24" t="n"/>
+      <c r="P114" s="13" t="n"/>
+      <c r="Q114" s="24" t="n"/>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="8" t="n"/>
@@ -7285,7 +7433,8 @@
       <c r="M115" s="9" t="n"/>
       <c r="N115" s="9" t="n"/>
       <c r="O115" s="9" t="n"/>
-      <c r="P115" s="22" t="n"/>
+      <c r="P115" s="9" t="n"/>
+      <c r="Q115" s="22" t="n"/>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="12" t="n"/>
@@ -7303,7 +7452,8 @@
       <c r="M116" s="13" t="n"/>
       <c r="N116" s="13" t="n"/>
       <c r="O116" s="13" t="n"/>
-      <c r="P116" s="24" t="n"/>
+      <c r="P116" s="13" t="n"/>
+      <c r="Q116" s="24" t="n"/>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="8" t="n"/>
@@ -7321,7 +7471,8 @@
       <c r="M117" s="9" t="n"/>
       <c r="N117" s="9" t="n"/>
       <c r="O117" s="9" t="n"/>
-      <c r="P117" s="22" t="n"/>
+      <c r="P117" s="9" t="n"/>
+      <c r="Q117" s="22" t="n"/>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="12" t="n"/>
@@ -7339,7 +7490,8 @@
       <c r="M118" s="13" t="n"/>
       <c r="N118" s="13" t="n"/>
       <c r="O118" s="13" t="n"/>
-      <c r="P118" s="24" t="n"/>
+      <c r="P118" s="13" t="n"/>
+      <c r="Q118" s="24" t="n"/>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="8" t="n"/>
@@ -7357,7 +7509,8 @@
       <c r="M119" s="9" t="n"/>
       <c r="N119" s="9" t="n"/>
       <c r="O119" s="9" t="n"/>
-      <c r="P119" s="22" t="n"/>
+      <c r="P119" s="9" t="n"/>
+      <c r="Q119" s="22" t="n"/>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="12" t="n"/>
@@ -7375,7 +7528,8 @@
       <c r="M120" s="13" t="n"/>
       <c r="N120" s="13" t="n"/>
       <c r="O120" s="13" t="n"/>
-      <c r="P120" s="24" t="n"/>
+      <c r="P120" s="13" t="n"/>
+      <c r="Q120" s="24" t="n"/>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="8" t="n"/>
@@ -7393,7 +7547,8 @@
       <c r="M121" s="9" t="n"/>
       <c r="N121" s="9" t="n"/>
       <c r="O121" s="9" t="n"/>
-      <c r="P121" s="22" t="n"/>
+      <c r="P121" s="9" t="n"/>
+      <c r="Q121" s="22" t="n"/>
     </row>
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="12" t="n"/>
@@ -7411,7 +7566,8 @@
       <c r="M122" s="13" t="n"/>
       <c r="N122" s="13" t="n"/>
       <c r="O122" s="13" t="n"/>
-      <c r="P122" s="24" t="n"/>
+      <c r="P122" s="13" t="n"/>
+      <c r="Q122" s="24" t="n"/>
     </row>
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="8" t="n"/>
@@ -7429,7 +7585,8 @@
       <c r="M123" s="9" t="n"/>
       <c r="N123" s="9" t="n"/>
       <c r="O123" s="9" t="n"/>
-      <c r="P123" s="22" t="n"/>
+      <c r="P123" s="9" t="n"/>
+      <c r="Q123" s="22" t="n"/>
     </row>
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="12" t="n"/>
@@ -7447,7 +7604,8 @@
       <c r="M124" s="13" t="n"/>
       <c r="N124" s="13" t="n"/>
       <c r="O124" s="13" t="n"/>
-      <c r="P124" s="24" t="n"/>
+      <c r="P124" s="13" t="n"/>
+      <c r="Q124" s="24" t="n"/>
     </row>
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="8" t="n"/>
@@ -7465,7 +7623,8 @@
       <c r="M125" s="9" t="n"/>
       <c r="N125" s="9" t="n"/>
       <c r="O125" s="9" t="n"/>
-      <c r="P125" s="22" t="n"/>
+      <c r="P125" s="9" t="n"/>
+      <c r="Q125" s="22" t="n"/>
     </row>
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="12" t="n"/>
@@ -7483,7 +7642,8 @@
       <c r="M126" s="13" t="n"/>
       <c r="N126" s="13" t="n"/>
       <c r="O126" s="13" t="n"/>
-      <c r="P126" s="24" t="n"/>
+      <c r="P126" s="13" t="n"/>
+      <c r="Q126" s="24" t="n"/>
     </row>
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="8" t="n"/>
@@ -7501,7 +7661,8 @@
       <c r="M127" s="9" t="n"/>
       <c r="N127" s="9" t="n"/>
       <c r="O127" s="9" t="n"/>
-      <c r="P127" s="22" t="n"/>
+      <c r="P127" s="9" t="n"/>
+      <c r="Q127" s="22" t="n"/>
     </row>
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="12" t="n"/>
@@ -7519,7 +7680,8 @@
       <c r="M128" s="13" t="n"/>
       <c r="N128" s="13" t="n"/>
       <c r="O128" s="13" t="n"/>
-      <c r="P128" s="24" t="n"/>
+      <c r="P128" s="13" t="n"/>
+      <c r="Q128" s="24" t="n"/>
     </row>
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="8" t="n"/>
@@ -7537,7 +7699,8 @@
       <c r="M129" s="9" t="n"/>
       <c r="N129" s="9" t="n"/>
       <c r="O129" s="9" t="n"/>
-      <c r="P129" s="22" t="n"/>
+      <c r="P129" s="9" t="n"/>
+      <c r="Q129" s="22" t="n"/>
     </row>
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="12" t="n"/>
@@ -7555,7 +7718,8 @@
       <c r="M130" s="13" t="n"/>
       <c r="N130" s="13" t="n"/>
       <c r="O130" s="13" t="n"/>
-      <c r="P130" s="24" t="n"/>
+      <c r="P130" s="13" t="n"/>
+      <c r="Q130" s="24" t="n"/>
     </row>
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="8" t="n"/>
@@ -7573,7 +7737,8 @@
       <c r="M131" s="9" t="n"/>
       <c r="N131" s="9" t="n"/>
       <c r="O131" s="9" t="n"/>
-      <c r="P131" s="22" t="n"/>
+      <c r="P131" s="9" t="n"/>
+      <c r="Q131" s="22" t="n"/>
     </row>
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="12" t="n"/>
@@ -7591,7 +7756,8 @@
       <c r="M132" s="13" t="n"/>
       <c r="N132" s="13" t="n"/>
       <c r="O132" s="13" t="n"/>
-      <c r="P132" s="24" t="n"/>
+      <c r="P132" s="13" t="n"/>
+      <c r="Q132" s="24" t="n"/>
     </row>
     <row r="133" ht="22" customHeight="1">
       <c r="A133" s="8" t="n"/>
@@ -7609,7 +7775,8 @@
       <c r="M133" s="9" t="n"/>
       <c r="N133" s="9" t="n"/>
       <c r="O133" s="9" t="n"/>
-      <c r="P133" s="22" t="n"/>
+      <c r="P133" s="9" t="n"/>
+      <c r="Q133" s="22" t="n"/>
     </row>
     <row r="134" ht="22" customHeight="1">
       <c r="A134" s="12" t="n"/>
@@ -7627,7 +7794,8 @@
       <c r="M134" s="13" t="n"/>
       <c r="N134" s="13" t="n"/>
       <c r="O134" s="13" t="n"/>
-      <c r="P134" s="24" t="n"/>
+      <c r="P134" s="13" t="n"/>
+      <c r="Q134" s="24" t="n"/>
     </row>
     <row r="135" ht="22" customHeight="1">
       <c r="A135" s="8" t="n"/>
@@ -7645,7 +7813,8 @@
       <c r="M135" s="9" t="n"/>
       <c r="N135" s="9" t="n"/>
       <c r="O135" s="9" t="n"/>
-      <c r="P135" s="22" t="n"/>
+      <c r="P135" s="9" t="n"/>
+      <c r="Q135" s="22" t="n"/>
     </row>
     <row r="136" ht="22" customHeight="1">
       <c r="A136" s="12" t="n"/>
@@ -7663,7 +7832,8 @@
       <c r="M136" s="13" t="n"/>
       <c r="N136" s="13" t="n"/>
       <c r="O136" s="13" t="n"/>
-      <c r="P136" s="24" t="n"/>
+      <c r="P136" s="13" t="n"/>
+      <c r="Q136" s="24" t="n"/>
     </row>
     <row r="137" ht="22" customHeight="1">
       <c r="A137" s="8" t="n"/>
@@ -7681,7 +7851,8 @@
       <c r="M137" s="9" t="n"/>
       <c r="N137" s="9" t="n"/>
       <c r="O137" s="9" t="n"/>
-      <c r="P137" s="22" t="n"/>
+      <c r="P137" s="9" t="n"/>
+      <c r="Q137" s="22" t="n"/>
     </row>
     <row r="138" ht="22" customHeight="1">
       <c r="A138" s="12" t="n"/>
@@ -7699,7 +7870,8 @@
       <c r="M138" s="13" t="n"/>
       <c r="N138" s="13" t="n"/>
       <c r="O138" s="13" t="n"/>
-      <c r="P138" s="24" t="n"/>
+      <c r="P138" s="13" t="n"/>
+      <c r="Q138" s="24" t="n"/>
     </row>
     <row r="139" ht="22" customHeight="1">
       <c r="A139" s="8" t="n"/>
@@ -7717,7 +7889,8 @@
       <c r="M139" s="9" t="n"/>
       <c r="N139" s="9" t="n"/>
       <c r="O139" s="9" t="n"/>
-      <c r="P139" s="22" t="n"/>
+      <c r="P139" s="9" t="n"/>
+      <c r="Q139" s="22" t="n"/>
     </row>
     <row r="140" ht="22" customHeight="1">
       <c r="A140" s="12" t="n"/>
@@ -7735,14 +7908,15 @@
       <c r="M140" s="13" t="n"/>
       <c r="N140" s="13" t="n"/>
       <c r="O140" s="13" t="n"/>
-      <c r="P140" s="24" t="n"/>
+      <c r="P140" s="13" t="n"/>
+      <c r="Q140" s="24" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="3">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:N2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="P5:P109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_설계팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_설계팀_입력_2026.xlsx
@@ -243,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -528,6 +528,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1302,7 +1311,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="102" t="inlineStr">
+      <c r="A1" s="105" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 설계팀 │ 2026</t>
         </is>
@@ -1325,7 +1334,7 @@
       <c r="Q1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="103" t="inlineStr">
+      <c r="A2" s="106" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 설계팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1343,11 +1352,13 @@
       <c r="L2" s="16" t="n"/>
       <c r="M2" s="16" t="n"/>
       <c r="N2" s="17" t="n"/>
-      <c r="O2" s="104" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:46</t>
-        </is>
-      </c>
+      <c r="O2" s="107" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:58</t>
+        </is>
+      </c>
+      <c r="P2" s="16" t="n"/>
+      <c r="Q2" s="17" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_설계팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_설계팀_입력_2026.xlsx
@@ -648,30 +648,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -685,86 +670,46 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PO유형 (발주 성격)
+        <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -775,19 +720,11 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 영업단계 (Sales Pipeline)
+        <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -802,55 +739,31 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
-        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 담당자
+        <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
-        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -859,19 +772,11 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
-        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 시작일
+        <t>▣ 부서 시작일
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-05-10
 • 허용: 26-5-10, 260510, 2026.5.10 (자동 정규화)
@@ -883,19 +788,11 @@
   ▸ 날짜 → 시작 (부서 진척률 50% 인식)
 • v3.1 검사기 운영: 진척률 % 대신 시작·완료일로 추적
   (2주 단위 빠른 작업 사이클이라 % 입력이 비효율)</t>
-        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 완료일
+        <t>▣ 부서 완료일
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-05-24
 • 허용: 26-5-24, 260524, 2026.5.24 (자동 정규화)
@@ -908,19 +805,11 @@
 • 입력 시: PMS 2_진행현황에 자동 표시 +
   전체 진척률 = (완료 부서 수) / (참여 부서 수) 자동 계산
 • '제외' 부서는 분모에서 제외됨</t>
-        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 의뢰 입고예정일 (가공의뢰 후 예정)
+        <t>▣ 의뢰 입고예정일 (가공의뢰 후 예정)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-07-15
 • 가공의뢰 발주 시 외부업체와 약속한
@@ -929,19 +818,11 @@
   ▸ 의뢰 시 예정일 입력
   ▸ 실제 입고일과 비교 → 지연 여부 추적
   ▸ 비워두면: 미발주 또는 일정 미정</t>
-        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 의뢰 입고일 (가공의뢰 결과)
+        <t>▣ 의뢰 입고일 (가공의뢰 결과)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD
 • 가공의뢰한 부품·가공품이
@@ -950,45 +831,28 @@
   ▸ 입고일 ≤ 예정일 → 정시
   ▸ 입고일 &gt; 예정일 → 지연
   ▸ 입고일 = 빈 칸  → 미입고 (진행중)</t>
-        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 작업 상태
+        <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 메모 (부서 자유 입력)
+        <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -1549,7 +1413,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>T-260407-3</t>
+          <t>T-260407-2</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -1659,7 +1523,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>T-260303-2</t>
+          <t>T-260303-1</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -1769,7 +1633,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>T-260409-2</t>
+          <t>T-260409-1</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -1824,7 +1688,7 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>T-260409-3</t>
+          <t>T-260409-2</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -1879,7 +1743,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>T-260410-2</t>
+          <t>T-260410-1</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -1934,7 +1798,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>T-260410-3</t>
+          <t>T-260410-2</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -1989,7 +1853,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>T-260403-6</t>
+          <t>T-260403-5</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -2044,7 +1908,7 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>T-260408-7</t>
+          <t>T-260408-6</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -2099,7 +1963,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>T-260408-8</t>
+          <t>T-260408-7</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -2154,7 +2018,7 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>T-260408-9</t>
+          <t>T-260408-8</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -2209,7 +2073,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>T-260408-10</t>
+          <t>T-260408-9</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -2264,7 +2128,7 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>T-260406-2</t>
+          <t>T-260406-1</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -2319,7 +2183,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>T-260406-3</t>
+          <t>T-260406-2</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -2374,7 +2238,7 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>T-260406-4</t>
+          <t>T-260406-3</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -2429,7 +2293,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>T-260406-5</t>
+          <t>T-260406-4</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -2484,7 +2348,7 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>T-260406-6</t>
+          <t>T-260406-5</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
@@ -2539,7 +2403,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>T-260406-7</t>
+          <t>T-260406-6</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -2594,7 +2458,7 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>T-260406-12</t>
+          <t>T-260406-11</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -2649,7 +2513,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>T-260406-13</t>
+          <t>T-260406-12</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -2704,7 +2568,7 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>T-260406-14</t>
+          <t>T-260406-13</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
@@ -2759,7 +2623,7 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>T-260406-15</t>
+          <t>T-260406-14</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -2924,7 +2788,7 @@
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>T-260327-2</t>
+          <t>T-260327-1</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
@@ -2979,7 +2843,7 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>T-260327-3</t>
+          <t>T-260327-2</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -3034,7 +2898,7 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>T-260327-4</t>
+          <t>T-260327-3</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
@@ -3089,7 +2953,7 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>T-260327-5</t>
+          <t>T-260327-4</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -3144,7 +3008,7 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>T-260327-6</t>
+          <t>T-260327-5</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
@@ -3199,7 +3063,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>T-260327-7</t>
+          <t>T-260327-6</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -3309,7 +3173,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>T-260331-2</t>
+          <t>T-260331-1</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -3364,7 +3228,7 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>T-260324-5</t>
+          <t>T-260324-4</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
@@ -3419,7 +3283,7 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>T-260401-4</t>
+          <t>T-260401-3</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -3584,7 +3448,7 @@
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>T-260323-2</t>
+          <t>T-260323-1</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
@@ -3639,7 +3503,7 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>T-260323-3</t>
+          <t>T-260323-2</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -3694,7 +3558,7 @@
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>T-260323-4</t>
+          <t>T-260323-3</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
@@ -3749,7 +3613,7 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>T-260323-5</t>
+          <t>T-260323-4</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
@@ -3804,7 +3668,7 @@
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>T-260323-6</t>
+          <t>T-260323-5</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
@@ -3859,7 +3723,7 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>T-260406-16</t>
+          <t>T-260406-15</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
@@ -3969,7 +3833,7 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>T-260408-2</t>
+          <t>T-260408-1</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
@@ -4024,7 +3888,7 @@
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>T-260408-3</t>
+          <t>T-260408-2</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
@@ -4079,7 +3943,7 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>T-260408-4</t>
+          <t>T-260408-3</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
@@ -4134,7 +3998,7 @@
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>T-260406-8</t>
+          <t>T-260406-7</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
@@ -4189,7 +4053,7 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>T-260406-9</t>
+          <t>T-260406-8</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
@@ -4244,7 +4108,7 @@
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>T-260406-10</t>
+          <t>T-260406-9</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
@@ -4299,7 +4163,7 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>T-260406-11</t>
+          <t>T-260406-10</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
@@ -4354,7 +4218,7 @@
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>T-260407-2</t>
+          <t>T-260407-1</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
@@ -4409,7 +4273,7 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>T-260409-4</t>
+          <t>T-260409-3</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
@@ -4464,7 +4328,7 @@
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>T-260409-5</t>
+          <t>T-260409-4</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
@@ -4519,7 +4383,7 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>T-260409-6</t>
+          <t>T-260409-5</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
@@ -4629,7 +4493,7 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>T-260324-8</t>
+          <t>T-260324-7</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
@@ -4684,7 +4548,7 @@
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>T-260407-4</t>
+          <t>T-260407-3</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
@@ -4739,7 +4603,7 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>T-260324-10</t>
+          <t>T-260324-9</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
@@ -4794,7 +4658,7 @@
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>T-260410-4</t>
+          <t>T-260410-3</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
@@ -4904,7 +4768,7 @@
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>T-260413-2</t>
+          <t>T-260413-1</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
@@ -4959,7 +4823,7 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>T-260413-3</t>
+          <t>T-260413-2</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
@@ -5014,7 +4878,7 @@
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>T-260413-4</t>
+          <t>T-260413-3</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
@@ -5069,7 +4933,7 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>T-260413-5</t>
+          <t>T-260413-4</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
@@ -5124,7 +4988,7 @@
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>T-260409-7</t>
+          <t>T-260409-6</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
@@ -5179,7 +5043,7 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>T-260409-8</t>
+          <t>T-260409-7</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
@@ -5234,7 +5098,7 @@
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>T-260409-9</t>
+          <t>T-260409-8</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
@@ -5289,7 +5153,7 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>T-260409-10</t>
+          <t>T-260409-9</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
@@ -5344,7 +5208,7 @@
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>T-260409-11</t>
+          <t>T-260409-10</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
@@ -5454,7 +5318,7 @@
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>T-260407-5</t>
+          <t>T-260407-4</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
@@ -5509,7 +5373,7 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>T-260413-6</t>
+          <t>T-260413-5</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
@@ -5564,7 +5428,7 @@
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>T-260413-7</t>
+          <t>T-260413-6</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
@@ -5619,7 +5483,7 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>T-260413-8</t>
+          <t>T-260413-7</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
@@ -5674,7 +5538,7 @@
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>T-260413-9</t>
+          <t>T-260413-8</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
@@ -5729,7 +5593,7 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>T-260413-10</t>
+          <t>T-260413-9</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
@@ -5784,7 +5648,7 @@
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>T-260413-11</t>
+          <t>T-260413-10</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
@@ -5839,7 +5703,7 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>T-260331-3</t>
+          <t>T-260331-2</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
@@ -6004,7 +5868,7 @@
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>T-260324-9</t>
+          <t>T-260324-8</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
@@ -6059,7 +5923,7 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>T-260413-12</t>
+          <t>T-260413-11</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
@@ -6114,7 +5978,7 @@
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>T-260413-17</t>
+          <t>T-260413-16</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
@@ -6169,7 +6033,7 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>T-260413-18</t>
+          <t>T-260413-17</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
@@ -6224,7 +6088,7 @@
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>T-260413-19</t>
+          <t>T-260413-18</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
@@ -6334,7 +6198,7 @@
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>T-260415-2</t>
+          <t>T-260415-1</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
@@ -6389,7 +6253,7 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>T-260415-3</t>
+          <t>T-260415-2</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
@@ -6444,7 +6308,7 @@
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>T-260413-13</t>
+          <t>T-260413-12</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
@@ -6499,7 +6363,7 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>T-260413-14</t>
+          <t>T-260413-13</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
@@ -6554,7 +6418,7 @@
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>T-260413-15</t>
+          <t>T-260413-14</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
@@ -6609,7 +6473,7 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>T-260413-16</t>
+          <t>T-260413-15</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
@@ -6664,7 +6528,7 @@
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>T-260408-5</t>
+          <t>T-260408-4</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
@@ -6719,7 +6583,7 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>T-260408-6</t>
+          <t>T-260408-5</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
@@ -6829,7 +6693,7 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>T-260414-2</t>
+          <t>T-260414-1</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
@@ -6884,7 +6748,7 @@
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>T-260413-20</t>
+          <t>T-260413-19</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
@@ -6939,7 +6803,7 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>T-260413-21</t>
+          <t>T-260413-20</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
@@ -6994,7 +6858,7 @@
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>T-260414-3</t>
+          <t>T-260414-2</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
@@ -7049,7 +6913,7 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>T-260226-2</t>
+          <t>T-260226-1</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
@@ -7104,7 +6968,7 @@
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>T-260226-3</t>
+          <t>T-260226-2</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
@@ -7214,7 +7078,7 @@
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>T-260331-12</t>
+          <t>T-260331-11</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
@@ -7320,7 +7184,7 @@
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>T-260425-2</t>
+          <t>T-260425-1</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
